--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24617,7 +24617,7 @@
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-05 12:41（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-06 12:51（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24617,7 +24617,7 @@
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-06 12:51（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-07 12:55（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預售案清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$524</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$525</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J526"/>
+  <dimension ref="A1:J527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10896,12 +10896,20 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>日和淳</t>
-        </is>
-      </c>
-      <c r="E226" s="2" t="inlineStr"/>
+          <t>日健昌</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F226" s="2" t="inlineStr"/>
-      <c r="G226" s="2" t="inlineStr"/>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區昌盛街105號</t>
+        </is>
+      </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -10909,12 +10917,12 @@
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -10936,28 +10944,20 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>昀集富昱</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>日和淳</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr"/>
       <c r="F227" s="2" t="inlineStr"/>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區五工二路86巷36號</t>
-        </is>
-      </c>
+      <c r="G227" s="2" t="inlineStr"/>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
@@ -10984,20 +10984,28 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>春城麗都</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr"/>
+          <t>昀集富昱</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F228" s="2" t="inlineStr"/>
-      <c r="G228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區五工二路86巷36號</t>
+        </is>
+      </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
@@ -11024,28 +11032,20 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>本格明水</t>
-        </is>
-      </c>
-      <c r="E229" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>春城麗都</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr"/>
       <c r="F229" s="2" t="inlineStr"/>
-      <c r="G229" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區新知一路77號</t>
-        </is>
-      </c>
+      <c r="G229" s="2" t="inlineStr"/>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
@@ -11072,23 +11072,23 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>河成心湛</t>
+          <t>本格明水</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F230" s="2" t="inlineStr"/>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中華路一段26巷</t>
+          <t>新北市新莊區新知一路77號</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
@@ -11120,18 +11120,18 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>玄泰蔦居</t>
+          <t>河成心湛</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中原段212、213、214地號</t>
+          <t>新北市新莊區中華路一段26巷</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>百邑富都匯</t>
+          <t>玄泰蔦居</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -11179,7 +11179,7 @@
       <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中央路、中華路口</t>
+          <t>新北市新莊區中原段212、213、214地號</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>皇鼎心莊</t>
+          <t>百邑富都匯</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -11227,7 +11227,7 @@
       <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區民安路157號</t>
+          <t>新北市新莊區中央路、中華路口</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11264,18 +11264,18 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>碧瑤建設中平路案(尚未取得建照)</t>
+          <t>皇鼎心莊</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中平路、榮華路二段</t>
+          <t>新北市新莊區民安路157號</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>碧瑤建設瓊林路案(尚未取得建照)</t>
+          <t>碧瑤建設中平路案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -11323,12 +11323,12 @@
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區瓊林路</t>
+          <t>新北市新莊區中平路、榮華路二段</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
@@ -11360,18 +11360,18 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>碧瑤敦灃</t>
+          <t>碧瑤建設瓊林路案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區副都心段一小段228、231、242地號</t>
+          <t>新北市新莊區瓊林路</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -11408,23 +11408,23 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>禾蓮心中美</t>
+          <t>碧瑤敦灃</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港路148號</t>
+          <t>新北市新莊區副都心段一小段228、231、242地號</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
@@ -11456,16 +11456,20 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>自由之丘</t>
+          <t>禾蓮心中美</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr"/>
-      <c r="G238" s="2" t="inlineStr"/>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區中港路148號</t>
+        </is>
+      </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11473,7 +11477,7 @@
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
@@ -11500,7 +11504,7 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>西勝時星</t>
+          <t>自由之丘</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -11544,28 +11548,24 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>豐盛</t>
+          <t>西勝時星</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr"/>
-      <c r="G240" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區豐盛二街、新樹路699巷</t>
-        </is>
-      </c>
+      <c r="G240" s="2" t="inlineStr"/>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
@@ -11592,24 +11592,28 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>這一站，幸福</t>
+          <t>豐盛</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr"/>
-      <c r="G241" s="2" t="inlineStr"/>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區豐盛二街、新樹路699巷</t>
+        </is>
+      </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
@@ -11636,10 +11640,14 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>邦瓏雍玥</t>
-        </is>
-      </c>
-      <c r="E242" s="2" t="inlineStr"/>
+          <t>這一站，幸福</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F242" s="2" t="inlineStr"/>
       <c r="G242" s="2" t="inlineStr"/>
       <c r="H242" s="2" t="inlineStr">
@@ -11676,20 +11684,12 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>馥華之道</t>
-        </is>
-      </c>
-      <c r="E243" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>邦瓏雍玥</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr"/>
       <c r="F243" s="2" t="inlineStr"/>
-      <c r="G243" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區福營路、福營路270號交叉口</t>
-        </is>
-      </c>
+      <c r="G243" s="2" t="inlineStr"/>
       <c r="H243" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J243" s="2" t="inlineStr">
@@ -11724,23 +11724,23 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>麗寶ALL IN ONE</t>
+          <t>馥華之道</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr"/>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中央路558號</t>
+          <t>新北市新莊區福營路、福營路270號交叉口</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
@@ -11767,23 +11767,23 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>林口區</t>
+          <t>新莊區</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Classy Home</t>
+          <t>麗寶ALL IN ONE</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr"/>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路與民族路口</t>
+          <t>新北市新莊區中央路558號</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -11820,24 +11820,28 @@
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>中光極</t>
+          <t>Classy Home</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr"/>
-      <c r="G246" s="2" t="inlineStr"/>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區忠孝路與民族路口</t>
+        </is>
+      </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J246" s="2" t="inlineStr">
@@ -11864,20 +11868,16 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>九揚華樂</t>
+          <t>中光極</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr"/>
-      <c r="G247" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區力行段955地號</t>
-        </is>
-      </c>
+      <c r="G247" s="2" t="inlineStr"/>
       <c r="H247" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>亞昕天匯</t>
+          <t>九揚華樂</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -11923,7 +11923,7 @@
       <c r="F248" s="2" t="inlineStr"/>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路及信義路交叉口</t>
+          <t>新北市林口區力行段955地號</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -11960,23 +11960,23 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>亞昕昕銀座</t>
+          <t>亞昕天匯</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr"/>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段636號</t>
+          <t>新北市林口區文化二路及信義路交叉口</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>亞昕森匯</t>
+          <t>亞昕昕銀座</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -12019,7 +12019,7 @@
       <c r="F250" s="2" t="inlineStr"/>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段及信義路交叉口</t>
+          <t>新北市林口區文化三路一段636號</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12056,23 +12056,23 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>亞昕．寓邸</t>
+          <t>亞昕森匯</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr"/>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段、文化二路二段178巷18弄</t>
+          <t>新北市林口區文化二路二段及信義路交叉口</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>仁愛金鑽</t>
+          <t>亞昕．寓邸</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區仁愛路一段、新生街口</t>
+          <t>新北市林口區文化二路二段、文化二路二段178巷18弄</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
@@ -12152,18 +12152,18 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>優學</t>
+          <t>仁愛金鑽</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區佳林路</t>
+          <t>新北市林口區仁愛路一段、新生街口</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -12200,23 +12200,23 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>原昕吾旭</t>
+          <t>優學</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區麗林段 644 、656地號</t>
+          <t>新北市林口區佳林路</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr">
@@ -12248,12 +12248,20 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>原森</t>
-        </is>
-      </c>
-      <c r="E255" s="2" t="inlineStr"/>
+          <t>原昕吾旭</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>萬/戶</t>
+        </is>
+      </c>
       <c r="F255" s="2" t="inlineStr"/>
-      <c r="G255" s="2" t="inlineStr"/>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區麗林段 644 、656地號</t>
+        </is>
+      </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12261,12 +12269,12 @@
       </c>
       <c r="I255" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -12288,20 +12296,12 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>原森TWIN TOWERS</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>原森</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr"/>
       <c r="F256" s="2" t="inlineStr"/>
-      <c r="G256" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區文化三路及仁愛二路口</t>
-        </is>
-      </c>
+      <c r="G256" s="2" t="inlineStr"/>
       <c r="H256" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12309,12 +12309,12 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>和洲艾美</t>
+          <t>原森TWIN TOWERS</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -12347,7 +12347,7 @@
       <c r="F257" s="2" t="inlineStr"/>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化一路二段、寶林路口</t>
+          <t>新北市林口區文化三路及仁愛二路口</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>大新青慕</t>
+          <t>和洲艾美</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -12395,7 +12395,7 @@
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區中華路、文化二路二段口</t>
+          <t>新北市林口區文化一路二段、寶林路口</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>宏樸 曉霧</t>
+          <t>大新青慕</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -12443,7 +12443,7 @@
       <c r="F259" s="2" t="inlineStr"/>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區八德路500巷、惠民街30巷口</t>
+          <t>新北市林口區中華路、文化二路二段口</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>宏樸日心說</t>
+          <t>宏樸 曉霧</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -12491,12 +12491,12 @@
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區民享路與中北三街口</t>
+          <t>新北市林口區八德路500巷、惠民街30巷口</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr">
@@ -12528,20 +12528,28 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>家悦美</t>
-        </is>
-      </c>
-      <c r="E261" s="2" t="inlineStr"/>
+          <t>宏樸日心說</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F261" s="2" t="inlineStr"/>
-      <c r="G261" s="2" t="inlineStr"/>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區民享路與中北三街口</t>
+        </is>
+      </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J261" s="2" t="inlineStr">
@@ -12568,20 +12576,12 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>家睦中山</t>
-        </is>
-      </c>
-      <c r="E262" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>家悦美</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr"/>
       <c r="F262" s="2" t="inlineStr"/>
-      <c r="G262" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區中山路151號旁</t>
-        </is>
-      </c>
+      <c r="G262" s="2" t="inlineStr"/>
       <c r="H262" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>富創得AI新創園區</t>
+          <t>家睦中山</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -12627,7 +12627,7 @@
       <c r="F263" s="2" t="inlineStr"/>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區工四路20號</t>
+          <t>新北市林口區中山路151號旁</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>富堡晶鑄</t>
+          <t>富創得AI新創園區</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -12675,7 +12675,7 @@
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段39巷及三民路</t>
+          <t>新北市林口區工四路20號</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -12712,12 +12712,20 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>富浤一響</t>
-        </is>
-      </c>
-      <c r="E265" s="2" t="inlineStr"/>
+          <t>富堡晶鑄</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F265" s="2" t="inlineStr"/>
-      <c r="G265" s="2" t="inlineStr"/>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區文化三路一段39巷及三民路</t>
+        </is>
+      </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12725,7 +12733,7 @@
       </c>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J265" s="2" t="inlineStr">
@@ -12752,28 +12760,20 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>寬隱</t>
-        </is>
-      </c>
-      <c r="E266" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>富浤一響</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr"/>
       <c r="F266" s="2" t="inlineStr"/>
-      <c r="G266" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區東明二街98號</t>
-        </is>
-      </c>
+      <c r="G266" s="2" t="inlineStr"/>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>小.學堂</t>
+          <t>寬隱</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -12811,12 +12811,12 @@
       <c r="F267" s="2" t="inlineStr"/>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區力行段 499 地號</t>
+          <t>新北市林口區東明二街98號</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>山侘一生</t>
+          <t>小.學堂</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -12859,7 +12859,7 @@
       <c r="F268" s="2" t="inlineStr"/>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區建林段645地號</t>
+          <t>新北市林口區力行段 499 地號</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>新潤世界都心</t>
+          <t>山侘一生</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -12907,7 +12907,7 @@
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段168號旁</t>
+          <t>新北市林口區建林段645地號</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -12944,18 +12944,18 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>易捷聿白</t>
+          <t>新潤世界都心</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr"/>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區惠民街30巷25號旁</t>
+          <t>新北市林口區文化三路二段168號旁</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>春木日輝</t>
+          <t>易捷聿白</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -13003,7 +13003,7 @@
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區民富街</t>
+          <t>新北市林口區惠民街30巷25號旁</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13040,23 +13040,23 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>森聯摩天41</t>
+          <t>春木日輝</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F272" s="2" t="inlineStr"/>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段69號</t>
+          <t>新北市林口區民富街</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I272" s="2" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>森鉅M-林境</t>
+          <t>森聯摩天41</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       <c r="F273" s="2" t="inlineStr"/>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區麗林段 512 地號</t>
+          <t>新北市林口區文化三路一段69號</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
@@ -13136,16 +13136,20 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>森鉅M-逸境</t>
+          <t>森鉅M-林境</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr"/>
-      <c r="G274" s="2" t="inlineStr"/>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區麗林段 512 地號</t>
+        </is>
+      </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13153,7 +13157,7 @@
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
@@ -13180,20 +13184,16 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>源峰上境</t>
+          <t>森鉅M-逸境</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr"/>
-      <c r="G275" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區松柏路80號</t>
-        </is>
-      </c>
+      <c r="G275" s="2" t="inlineStr"/>
       <c r="H275" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
@@ -13228,18 +13228,18 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>潤鴻日麗</t>
+          <t>源峰上境</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr"/>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段及信義路交叉口</t>
+          <t>新北市林口區松柏路80號</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13276,18 +13276,18 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>瑞德豐錦</t>
+          <t>潤鴻日麗</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區竹林路309巷</t>
+          <t>新北市林口區文化二路二段及信義路交叉口</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>璽來登帝璽</t>
+          <t>瑞德豐錦</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -13335,7 +13335,7 @@
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區三民路、八德路口</t>
+          <t>新北市林口區竹林路309巷</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>盛德誠</t>
+          <t>璽來登帝璽</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -13383,7 +13383,7 @@
       <c r="F279" s="2" t="inlineStr"/>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區南勢四街、過崙街口</t>
+          <t>新北市林口區三民路、八德路口</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -13420,12 +13420,20 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>福樺中央大樓</t>
-        </is>
-      </c>
-      <c r="E280" s="2" t="inlineStr"/>
+          <t>盛德誠</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F280" s="2" t="inlineStr"/>
-      <c r="G280" s="2" t="inlineStr"/>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區南勢四街、過崙街口</t>
+        </is>
+      </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13433,7 +13441,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
@@ -13460,14 +13468,10 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>福樺富貴中山</t>
-        </is>
-      </c>
-      <c r="E281" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>福樺中央大樓</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr"/>
       <c r="F281" s="2" t="inlineStr"/>
       <c r="G281" s="2" t="inlineStr"/>
       <c r="H281" s="2" t="inlineStr">
@@ -13504,20 +13508,16 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>福樺富貴莊園</t>
+          <t>福樺富貴中山</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr"/>
-      <c r="G282" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區文化二路一段</t>
-        </is>
-      </c>
+      <c r="G282" s="2" t="inlineStr"/>
       <c r="H282" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13525,7 +13525,7 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>立軒天蒔</t>
+          <t>福樺富貴莊園</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -13563,7 +13563,7 @@
       <c r="F283" s="2" t="inlineStr"/>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段與吉祥路交叉口</t>
+          <t>新北市林口區文化二路一段</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -13600,12 +13600,20 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>立陽頤興</t>
-        </is>
-      </c>
-      <c r="E284" s="2" t="inlineStr"/>
+          <t>立軒天蒔</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F284" s="2" t="inlineStr"/>
-      <c r="G284" s="2" t="inlineStr"/>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區文化二路二段與吉祥路交叉口</t>
+        </is>
+      </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13613,7 +13621,7 @@
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
@@ -13640,20 +13648,12 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>竹城.日和</t>
-        </is>
-      </c>
-      <c r="E285" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>立陽頤興</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr"/>
       <c r="F285" s="2" t="inlineStr"/>
-      <c r="G285" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區建林段1261地號</t>
-        </is>
-      </c>
+      <c r="G285" s="2" t="inlineStr"/>
       <c r="H285" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
@@ -13688,7 +13688,7 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>築禾琢玥</t>
+          <t>竹城.日和</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -13699,7 +13699,7 @@
       <c r="F286" s="2" t="inlineStr"/>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區南勢三街</t>
+          <t>新北市林口區建林段1261地號</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -13736,18 +13736,18 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>群和 FUTURE LINK</t>
+          <t>築禾琢玥</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr"/>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區力行段11地號</t>
+          <t>新北市林口區南勢三街</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -13784,23 +13784,23 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>翫美A9</t>
+          <t>群和 FUTURE LINK</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr"/>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段39巷</t>
+          <t>新北市林口區力行段11地號</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
@@ -13832,23 +13832,23 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>聯虹珺玥</t>
+          <t>翫美A9</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr"/>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區竹林一路.</t>
+          <t>新北市林口區文化三路一段39巷</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
@@ -13880,18 +13880,18 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>聿翔沐風</t>
+          <t>聯虹珺玥</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路、民族路口</t>
+          <t>新北市林口區竹林一路.</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -13928,18 +13928,18 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
+          <t>聿翔沐風</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr"/>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路604巷</t>
+          <t>新北市林口區忠孝路、民族路口</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -13976,18 +13976,18 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>謙旭</t>
+          <t>聿見美璟</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr"/>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區仁愛路一段</t>
+          <t>新北市林口區忠孝路604巷</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>證源富匠</t>
+          <t>謙旭</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -14035,12 +14035,12 @@
       <c r="F293" s="2" t="inlineStr"/>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區林口路</t>
+          <t>新北市林口區仁愛路一段</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr">
@@ -14072,23 +14072,23 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>證源富承</t>
+          <t>證源富匠</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr"/>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區林口路158號對面</t>
+          <t>新北市林口區林口路</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>長耀 IPARK</t>
+          <t>證源富承</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -14131,7 +14131,7 @@
       <c r="F295" s="2" t="inlineStr"/>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段617巷及民族路交叉口</t>
+          <t>新北市林口區林口路158號對面</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -14168,23 +14168,23 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>長耀中山路案</t>
+          <t>長耀 IPARK</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F296" s="2" t="inlineStr"/>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段與中山路口交叉口</t>
+          <t>新北市林口區文化三路一段617巷及民族路交叉口</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I296" s="2" t="inlineStr">
@@ -14216,23 +14216,23 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>長耀加</t>
+          <t>長耀中山路案</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr"/>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段555巷</t>
+          <t>新北市林口區文化三路二段與中山路口交叉口</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>長耀里</t>
+          <t>長耀加</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -14275,7 +14275,7 @@
       <c r="F298" s="2" t="inlineStr"/>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區力行段137地號</t>
+          <t>新北市林口區文化三路一段555巷</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -14312,18 +14312,18 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>長虹天聚</t>
+          <t>長耀里</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr"/>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區中山路與民權路交叉口</t>
+          <t>新北市林口區力行段137地號</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -14360,18 +14360,18 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>頤昌松玥</t>
+          <t>長虹天聚</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr"/>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段211巷</t>
+          <t>新北市林口區中山路與民權路交叉口</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -14398,22 +14398,30 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>板橋雙和線</t>
+          <t>新莊林口線</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>中和區</t>
+          <t>林口區</t>
         </is>
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>偉鉅中山双匯</t>
-        </is>
-      </c>
-      <c r="E301" s="2" t="inlineStr"/>
+          <t>頤昌松玥</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F301" s="2" t="inlineStr"/>
-      <c r="G301" s="2" t="inlineStr"/>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區文化三路二段211巷</t>
+        </is>
+      </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -14421,12 +14429,12 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -14448,14 +14456,10 @@
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>偉鉅雙捷韻</t>
-        </is>
-      </c>
-      <c r="E302" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>偉鉅中山双匯</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr"/>
       <c r="F302" s="2" t="inlineStr"/>
       <c r="G302" s="2" t="inlineStr"/>
       <c r="H302" s="2" t="inlineStr">
@@ -14470,7 +14474,7 @@
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14492,20 +14496,16 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>双捷橙品</t>
+          <t>偉鉅雙捷韻</t>
         </is>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr"/>
-      <c r="G303" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景平路723號旁</t>
-        </is>
-      </c>
+      <c r="G303" s="2" t="inlineStr"/>
       <c r="H303" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -14513,12 +14513,12 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14540,23 +14540,23 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>君奕華品</t>
+          <t>双捷橙品</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr"/>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景新街57巷11號</t>
+          <t>新北市中和區景平路723號旁</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
@@ -14588,23 +14588,23 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>和典永峰</t>
+          <t>君奕華品</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr"/>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區立人街14巷77號</t>
+          <t>新北市中和區景新街57巷11號</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
@@ -14636,18 +14636,18 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>和御</t>
+          <t>和典永峰</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr"/>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路與新生街口</t>
+          <t>新北市中和區立人街14巷77號</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -14684,7 +14684,7 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>和雅琚</t>
+          <t>和御</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
@@ -14695,7 +14695,7 @@
       <c r="F307" s="2" t="inlineStr"/>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區福祥路85巷口</t>
+          <t>新北市中和區連城路與新生街口</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>大同新紀元</t>
+          <t>和雅琚</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -14743,7 +14743,7 @@
       <c r="F308" s="2" t="inlineStr"/>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路、錦和路口</t>
+          <t>新北市中和區福祥路85巷口</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -14780,18 +14780,18 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>好植</t>
+          <t>大同新紀元</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr"/>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景新街2號</t>
+          <t>新北市中和區連城路、錦和路口</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>宜安三六</t>
+          <t>好植</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -14839,12 +14839,12 @@
       <c r="F310" s="2" t="inlineStr"/>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區保健路72號</t>
+          <t>新北市中和區景新街2號</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I310" s="2" t="inlineStr">
@@ -14876,25 +14876,33 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>寶亞世界公舘</t>
-        </is>
-      </c>
-      <c r="E311" s="2" t="inlineStr"/>
+          <t>宜安三六</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F311" s="2" t="inlineStr"/>
-      <c r="G311" s="2" t="inlineStr"/>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區保健路72號</t>
+        </is>
+      </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J311" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -14916,14 +14924,10 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>將捷Ai PARK</t>
-        </is>
-      </c>
-      <c r="E312" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>寶亞世界公舘</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr"/>
       <c r="F312" s="2" t="inlineStr"/>
       <c r="G312" s="2" t="inlineStr"/>
       <c r="H312" s="2" t="inlineStr">
@@ -14938,7 +14942,7 @@
       </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -14960,28 +14964,24 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠A基地</t>
+          <t>將捷Ai PARK</t>
         </is>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr"/>
-      <c r="G313" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區環河西路三段、永和路</t>
-        </is>
-      </c>
+      <c r="G313" s="2" t="inlineStr"/>
       <c r="H313" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I313" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J313" s="2" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠B基地</t>
+          <t>左岸明珠A基地</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I314" s="2" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>忻揚馥群</t>
+          <t>左岸明珠B基地</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -15067,12 +15067,12 @@
       <c r="F315" s="2" t="inlineStr"/>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區南山路247號</t>
+          <t>新北市中和區環河西路三段、永和路</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I315" s="2" t="inlineStr">
@@ -15104,29 +15104,33 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>昇陽國旭</t>
+          <t>忻揚馥群</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr"/>
-      <c r="G316" s="2" t="inlineStr"/>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區南山路247號</t>
+        </is>
+      </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J316" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -15148,33 +15152,29 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>景安旭</t>
+          <t>昇陽國旭</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr"/>
-      <c r="G317" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景新街112號</t>
-        </is>
-      </c>
+      <c r="G317" s="2" t="inlineStr"/>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J317" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15196,20 +15196,28 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>東瑩玥光-涵光區</t>
-        </is>
-      </c>
-      <c r="E318" s="2" t="inlineStr"/>
+          <t>景安旭</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F318" s="2" t="inlineStr"/>
-      <c r="G318" s="2" t="inlineStr"/>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區景新街112號</t>
+        </is>
+      </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J318" s="2" t="inlineStr">
@@ -15236,7 +15244,7 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>欽禾</t>
+          <t>東瑩玥光-涵光區</t>
         </is>
       </c>
       <c r="E319" s="2" t="inlineStr"/>
@@ -15276,7 +15284,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>永邦恒美</t>
+          <t>欽禾</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr"/>
@@ -15316,14 +15324,10 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>漢寶捷運學府No.5</t>
-        </is>
-      </c>
-      <c r="E321" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>永邦恒美</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr"/>
       <c r="F321" s="2" t="inlineStr"/>
       <c r="G321" s="2" t="inlineStr"/>
       <c r="H321" s="2" t="inlineStr">
@@ -15360,28 +15364,24 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>漢皇方圓</t>
+          <t>漢寶捷運學府No.5</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr"/>
-      <c r="G322" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區中和路410號</t>
-        </is>
-      </c>
+      <c r="G322" s="2" t="inlineStr"/>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J322" s="2" t="inlineStr">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>綻賞</t>
+          <t>漢皇方圓</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
@@ -15419,12 +15419,12 @@
       <c r="F323" s="2" t="inlineStr"/>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路309號</t>
+          <t>新北市中和區中和路410號</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I323" s="2" t="inlineStr">
@@ -15456,16 +15456,20 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>蒲楊雙和</t>
+          <t>綻賞</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr"/>
-      <c r="G324" s="2" t="inlineStr"/>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連城路309號</t>
+        </is>
+      </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15473,7 +15477,7 @@
       </c>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J324" s="2" t="inlineStr">
@@ -15500,28 +15504,24 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>藏富HOUSE</t>
+          <t>蒲楊雙和</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr"/>
-      <c r="G325" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景平路159巷</t>
-        </is>
-      </c>
+      <c r="G325" s="2" t="inlineStr"/>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J325" s="2" t="inlineStr">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>虹爵琢悅</t>
+          <t>藏富HOUSE</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -15559,12 +15559,12 @@
       <c r="F326" s="2" t="inlineStr"/>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連勝街26巷8號</t>
+          <t>新北市中和區景平路159巷</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I326" s="2" t="inlineStr">
@@ -15596,16 +15596,20 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>遠雄CASA 凱莎莊園</t>
+          <t>虹爵琢悅</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr"/>
-      <c r="G327" s="2" t="inlineStr"/>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連勝街26巷8號</t>
+        </is>
+      </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15613,7 +15617,7 @@
       </c>
       <c r="I327" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J327" s="2" t="inlineStr">
@@ -15640,20 +15644,16 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>金玖民有琚</t>
+          <t>遠雄CASA 凱莎莊園</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr"/>
-      <c r="G328" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區民有街49號</t>
-        </is>
-      </c>
+      <c r="G328" s="2" t="inlineStr"/>
       <c r="H328" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J328" s="2" t="inlineStr">
@@ -15683,23 +15683,23 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>HELLO WIN迎家</t>
+          <t>金玖民有琚</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr"/>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街22巷2號</t>
+          <t>新北市中和區民有街49號</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -15736,16 +15736,20 @@
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>三輝白昀</t>
+          <t>HELLO WIN迎家</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr"/>
-      <c r="G330" s="2" t="inlineStr"/>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松柏街22巷2號</t>
+        </is>
+      </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15753,7 +15757,7 @@
       </c>
       <c r="I330" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J330" s="2" t="inlineStr">
@@ -15780,20 +15784,16 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>上上寀</t>
+          <t>三輝白昀</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr"/>
-      <c r="G331" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江三路、華江二路口</t>
-        </is>
-      </c>
+      <c r="G331" s="2" t="inlineStr"/>
       <c r="H331" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15801,7 +15801,7 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J331" s="2" t="inlineStr">
@@ -15828,18 +15828,18 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>京東賞</t>
+          <t>上上寀</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr"/>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路二段521號</t>
+          <t>新北市板橋區華江三路、華江二路口</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -15876,23 +15876,23 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>協和新中興</t>
+          <t>京東賞</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr"/>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區金門街287巷</t>
+          <t>新北市板橋區中山路二段521號</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I333" s="2" t="inlineStr">
@@ -15924,18 +15924,18 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>和岩誼居</t>
+          <t>協和新中興</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr"/>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區存德街15號</t>
+          <t>新北市板橋區金門街287巷</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
@@ -15972,24 +15972,28 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>城德華福</t>
+          <t>和岩誼居</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr"/>
-      <c r="G335" s="2" t="inlineStr"/>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區存德街15號</t>
+        </is>
+      </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I335" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J335" s="2" t="inlineStr">
@@ -16016,20 +16020,16 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>大業</t>
+          <t>城德華福</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr"/>
-      <c r="G336" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江一路</t>
-        </is>
-      </c>
+      <c r="G336" s="2" t="inlineStr"/>
       <c r="H336" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -16037,7 +16037,7 @@
       </c>
       <c r="I336" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J336" s="2" t="inlineStr">
@@ -16064,12 +16064,20 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>寶格利</t>
-        </is>
-      </c>
-      <c r="E337" s="2" t="inlineStr"/>
+          <t>大業</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F337" s="2" t="inlineStr"/>
-      <c r="G337" s="2" t="inlineStr"/>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區華江一路</t>
+        </is>
+      </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -16077,12 +16085,12 @@
       </c>
       <c r="I337" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -16104,33 +16112,25 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>心晴好</t>
-        </is>
-      </c>
-      <c r="E338" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>寶格利</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr"/>
       <c r="F338" s="2" t="inlineStr"/>
-      <c r="G338" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區縣民大道一段</t>
-        </is>
-      </c>
+      <c r="G338" s="2" t="inlineStr"/>
       <c r="H338" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J338" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -16152,7 +16152,7 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>悠森學</t>
+          <t>心晴好</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
@@ -16163,12 +16163,12 @@
       <c r="F339" s="2" t="inlineStr"/>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路325巷41號</t>
+          <t>新北市板橋區縣民大道一段</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I339" s="2" t="inlineStr">
@@ -16200,7 +16200,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>文化風華</t>
+          <t>悠森學</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -16211,12 +16211,12 @@
       <c r="F340" s="2" t="inlineStr"/>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段與華江一路口</t>
+          <t>新北市板橋區中正路325巷41號</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I340" s="2" t="inlineStr">
@@ -16248,18 +16248,18 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>新板東京</t>
+          <t>文化風華</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F341" s="2" t="inlineStr"/>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區民生路二段183號旁</t>
+          <t>新北市板橋區文化路二段與華江一路口</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -16296,23 +16296,23 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>新潤世界城</t>
+          <t>新板東京</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr"/>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅東路</t>
+          <t>新北市板橋區民生路二段183號旁</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I342" s="2" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>新濠一閱</t>
+          <t>新潤世界城</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
@@ -16355,7 +16355,7 @@
       <c r="F343" s="2" t="inlineStr"/>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與文新路交叉口</t>
+          <t>新北市板橋區南雅東路</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
@@ -16392,18 +16392,18 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>日安PARK</t>
+          <t>新濠一閱</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr"/>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、香社一路、香社二路</t>
+          <t>新北市板橋區環河西路四段與文新路交叉口</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16440,23 +16440,23 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>日安TOKYO</t>
+          <t>日安PARK</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr"/>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、藝文二街、板城路</t>
+          <t>新北市板橋區藝文街、香社一路、香社二路</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I345" s="2" t="inlineStr">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>晶合豐川</t>
+          <t>日安TOKYO</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -16499,7 +16499,7 @@
       <c r="F346" s="2" t="inlineStr"/>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區長安街168巷10弄</t>
+          <t>新北市板橋區藝文街、藝文二街、板城路</t>
         </is>
       </c>
       <c r="H346" s="2" t="inlineStr">
@@ -16536,18 +16536,18 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>松柏大院</t>
+          <t>晶合豐川</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F347" s="2" t="inlineStr"/>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街</t>
+          <t>新北市板橋區長安街168巷10弄</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
@@ -16584,18 +16584,18 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>板橋璞園的家</t>
+          <t>松柏大院</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr"/>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區田單北街61號</t>
+          <t>新北市板橋區松柏街</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
@@ -16632,7 +16632,7 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>歐英萬</t>
+          <t>板橋璞園的家</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -16643,7 +16643,7 @@
       <c r="F349" s="2" t="inlineStr"/>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區三民路二段72號</t>
+          <t>新北市板橋區田單北街61號</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -16680,18 +16680,18 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>永康真</t>
+          <t>歐英萬</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F350" s="2" t="inlineStr"/>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大華街72號旁</t>
+          <t>新北市板橋區三民路二段72號</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -16728,24 +16728,28 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>永雄府中心</t>
+          <t>永康真</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F351" s="2" t="inlineStr"/>
-      <c r="G351" s="2" t="inlineStr"/>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區大華街72號旁</t>
+        </is>
+      </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I351" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J351" s="2" t="inlineStr">
@@ -16772,7 +16776,7 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>江翠Park</t>
+          <t>永雄府中心</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -16816,28 +16820,24 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景1號</t>
+          <t>江翠Park</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr"/>
-      <c r="G353" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段、 華江三路</t>
-        </is>
-      </c>
+      <c r="G353" s="2" t="inlineStr"/>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I353" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J353" s="2" t="inlineStr">
@@ -16864,18 +16864,18 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景2號</t>
+          <t>甲山林帝景1號</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F354" s="2" t="inlineStr"/>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、大漢街</t>
+          <t>新北市板橋區環河西路四段、 華江三路</t>
         </is>
       </c>
       <c r="H354" s="2" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景6號</t>
+          <t>甲山林帝景2號</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -16923,7 +16923,7 @@
       <c r="F355" s="2" t="inlineStr"/>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
+          <t>新北市板橋區環河西路四段、大漢街</t>
         </is>
       </c>
       <c r="H355" s="2" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景7號</t>
+          <t>甲山林帝景6號</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -16971,7 +16971,7 @@
       <c r="F356" s="2" t="inlineStr"/>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段及華江三路口</t>
+          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
@@ -17008,23 +17008,23 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>甲山林濱河帝景</t>
+          <t>甲山林帝景7號</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr"/>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
+          <t>新北市板橋區文化路二段及華江三路口</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I357" s="2" t="inlineStr">
@@ -17056,23 +17056,23 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>祥泓湛</t>
+          <t>甲山林濱河帝景</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr"/>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大觀路三段62巷3號</t>
+          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I358" s="2" t="inlineStr">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>立信天朗</t>
+          <t>祥泓湛</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -17115,7 +17115,7 @@
       <c r="F359" s="2" t="inlineStr"/>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區新月一街與中正路交叉口</t>
+          <t>新北市板橋區大觀路三段62巷3號</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
@@ -17152,20 +17152,28 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>立信帝國花園廣場</t>
-        </is>
-      </c>
-      <c r="E360" s="2" t="inlineStr"/>
+          <t>立信天朗</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F360" s="2" t="inlineStr"/>
-      <c r="G360" s="2" t="inlineStr"/>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區新月一街與中正路交叉口</t>
+        </is>
+      </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I360" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J360" s="2" t="inlineStr">
@@ -17192,28 +17200,20 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>立信御景</t>
-        </is>
-      </c>
-      <c r="E361" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>立信帝國花園廣場</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr"/>
       <c r="F361" s="2" t="inlineStr"/>
-      <c r="G361" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段(新都段)</t>
-        </is>
-      </c>
+      <c r="G361" s="2" t="inlineStr"/>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J361" s="2" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>立信晴朗</t>
+          <t>立信御景</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -17251,12 +17251,12 @@
       <c r="F362" s="2" t="inlineStr"/>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路與新月三街口</t>
+          <t>新北市板橋區環河西路四段(新都段)</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr">
@@ -17288,7 +17288,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>立信雙星</t>
+          <t>立信晴朗</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -17299,7 +17299,7 @@
       <c r="F363" s="2" t="inlineStr"/>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路600號對面</t>
+          <t>新北市板橋區中正路與新月三街口</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
@@ -17336,18 +17336,18 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>立信首馥</t>
+          <t>立信雙星</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr"/>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江三路、華江六路交叉口</t>
+          <t>新北市板橋區華江一路600號對面</t>
         </is>
       </c>
       <c r="H364" s="2" t="inlineStr">
@@ -17384,18 +17384,18 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>統創曜</t>
+          <t>立信首馥</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr"/>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
+          <t>新北市板橋區華江三路、華江六路交叉口</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>耑芃</t>
+          <t>統創曜</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -17443,12 +17443,12 @@
       <c r="F366" s="2" t="inlineStr"/>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅南路二段68號</t>
+          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr">
@@ -17480,23 +17480,23 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>芯哲園</t>
+          <t>耑芃</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F367" s="2" t="inlineStr"/>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
+          <t>新北市板橋區南雅南路二段68號</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I367" s="2" t="inlineStr">
@@ -17528,23 +17528,23 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>達永冬慶</t>
+          <t>芯哲園</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr"/>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段65號</t>
+          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I368" s="2" t="inlineStr">
@@ -17576,24 +17576,28 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>遠揚之森A⁺</t>
+          <t>達永冬慶</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr"/>
-      <c r="G369" s="2" t="inlineStr"/>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區文化路二段65號</t>
+        </is>
+      </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I369" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J369" s="2" t="inlineStr">
@@ -17620,28 +17624,24 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>遠雄信義段案</t>
+          <t>遠揚之森A⁺</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr"/>
-      <c r="G370" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區信義段217地號</t>
-        </is>
-      </c>
+      <c r="G370" s="2" t="inlineStr"/>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr">
@@ -17668,7 +17668,7 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>鑄見</t>
+          <t>遠雄信義段案</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -17679,12 +17679,12 @@
       <c r="F371" s="2" t="inlineStr"/>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松江街</t>
+          <t>新北市板橋區信義段217地號</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr">
@@ -17716,12 +17716,20 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>香榭京宴</t>
-        </is>
-      </c>
-      <c r="E372" s="2" t="inlineStr"/>
+          <t>鑄見</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F372" s="2" t="inlineStr"/>
-      <c r="G372" s="2" t="inlineStr"/>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松江街</t>
+        </is>
+      </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17729,7 +17737,7 @@
       </c>
       <c r="I372" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J372" s="2" t="inlineStr">
@@ -17751,25 +17759,17 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>M PLUS</t>
-        </is>
-      </c>
-      <c r="E373" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>香榭京宴</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr"/>
       <c r="F373" s="2" t="inlineStr"/>
-      <c r="G373" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區環河東路一段152號</t>
-        </is>
-      </c>
+      <c r="G373" s="2" t="inlineStr"/>
       <c r="H373" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J373" s="2" t="inlineStr">
@@ -17804,12 +17804,20 @@
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>友座豐禾</t>
-        </is>
-      </c>
-      <c r="E374" s="2" t="inlineStr"/>
+          <t>M PLUS</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F374" s="2" t="inlineStr"/>
-      <c r="G374" s="2" t="inlineStr"/>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區環河東路一段152號</t>
+        </is>
+      </c>
       <c r="H374" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17817,7 +17825,7 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J374" s="2" t="inlineStr">
@@ -17844,20 +17852,12 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>家格綻綻</t>
-        </is>
-      </c>
-      <c r="E375" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>友座豐禾</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr"/>
       <c r="F375" s="2" t="inlineStr"/>
-      <c r="G375" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區中正路607號</t>
-        </is>
-      </c>
+      <c r="G375" s="2" t="inlineStr"/>
       <c r="H375" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J375" s="2" t="inlineStr">
@@ -17892,23 +17892,23 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>敦南宴</t>
+          <t>家格綻綻</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr"/>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區永利路216巷</t>
+          <t>新北市永和區中正路607號</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I376" s="2" t="inlineStr">
@@ -17940,7 +17940,7 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>新碩永傳</t>
+          <t>敦南宴</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -17951,12 +17951,12 @@
       <c r="F377" s="2" t="inlineStr"/>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中正路388號旁</t>
+          <t>新北市永和區永利路216巷</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I377" s="2" t="inlineStr">
@@ -17988,7 +17988,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>漢寶臺大苑</t>
+          <t>新碩永傳</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -17999,12 +17999,12 @@
       <c r="F378" s="2" t="inlineStr"/>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區成功路一段132號</t>
+          <t>新北市永和區中正路388號旁</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I378" s="2" t="inlineStr">
@@ -18036,20 +18036,28 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>漢皇River Sky</t>
-        </is>
-      </c>
-      <c r="E379" s="2" t="inlineStr"/>
+          <t>漢寶臺大苑</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F379" s="2" t="inlineStr"/>
-      <c r="G379" s="2" t="inlineStr"/>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區成功路一段132號</t>
+        </is>
+      </c>
       <c r="H379" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I379" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J379" s="2" t="inlineStr">
@@ -18076,28 +18084,20 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>蒲陽建設復興街案(尚未取得建照)</t>
-        </is>
-      </c>
-      <c r="E380" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>漢皇River Sky</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr"/>
       <c r="F380" s="2" t="inlineStr"/>
-      <c r="G380" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區復興街</t>
-        </is>
-      </c>
+      <c r="G380" s="2" t="inlineStr"/>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J380" s="2" t="inlineStr">
@@ -18124,7 +18124,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
+          <t>蒲陽建設復興街案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
@@ -18135,12 +18135,12 @@
       <c r="F381" s="2" t="inlineStr"/>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中山路一段28巷口旁</t>
+          <t>新北市永和區復興街</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I381" s="2" t="inlineStr">
@@ -18172,16 +18172,20 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>頂溪捷運站~黃金綠建築,1~2房</t>
+          <t>頂溪大苑</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr"/>
-      <c r="G382" s="2" t="inlineStr"/>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區中山路一段28巷口旁</t>
+        </is>
+      </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18189,7 +18193,7 @@
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J382" s="2" t="inlineStr">
@@ -18206,30 +18210,26 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>頂溪捷運站~黃金綠建築,1~2房</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr"/>
-      <c r="G383" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街</t>
-        </is>
-      </c>
+      <c r="G383" s="2" t="inlineStr"/>
       <c r="H383" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr">
@@ -18264,12 +18264,20 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>文心慕慕</t>
-        </is>
-      </c>
-      <c r="E384" s="2" t="inlineStr"/>
+          <t>富都康莊</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F384" s="2" t="inlineStr"/>
-      <c r="G384" s="2" t="inlineStr"/>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街</t>
+        </is>
+      </c>
       <c r="H384" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18277,7 +18285,7 @@
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J384" s="2" t="inlineStr">
@@ -18304,14 +18312,10 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>東煒大局</t>
-        </is>
-      </c>
-      <c r="E385" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>文心慕慕</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr"/>
       <c r="F385" s="2" t="inlineStr"/>
       <c r="G385" s="2" t="inlineStr"/>
       <c r="H385" s="2" t="inlineStr">
@@ -18348,28 +18352,24 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>汐止華品</t>
+          <t>東煒大局</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr"/>
-      <c r="G386" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區保一街與保一街8巷交叉口</t>
-        </is>
-      </c>
+      <c r="G386" s="2" t="inlineStr"/>
       <c r="H386" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J386" s="2" t="inlineStr">
@@ -18396,23 +18396,23 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>汐科爵鼎</t>
+          <t>汐止華品</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr"/>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區水源路二段190號旁</t>
+          <t>新北市汐止區保一街與保一街8巷交叉口</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I387" s="2" t="inlineStr">
@@ -18444,16 +18444,20 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>美麗山林</t>
+          <t>汐科爵鼎</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr"/>
-      <c r="G388" s="2" t="inlineStr"/>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區水源路二段190號旁</t>
+        </is>
+      </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18461,7 +18465,7 @@
       </c>
       <c r="I388" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J388" s="2" t="inlineStr">
@@ -18488,28 +18492,24 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>美麗山林-華廈區</t>
+          <t>美麗山林</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr"/>
-      <c r="G389" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區水源路二段125巷</t>
-        </is>
-      </c>
+      <c r="G389" s="2" t="inlineStr"/>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J389" s="2" t="inlineStr">
@@ -18536,7 +18536,7 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>金湖漾</t>
+          <t>美麗山林-華廈區</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
@@ -18547,12 +18547,12 @@
       <c r="F390" s="2" t="inlineStr"/>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區民族二街30巷22號</t>
+          <t>新北市汐止區水源路二段125巷</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I390" s="2" t="inlineStr">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>雄鷹天映湖</t>
+          <t>金湖漾</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
@@ -18595,12 +18595,12 @@
       <c r="F391" s="2" t="inlineStr"/>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區湖東街5巷50號</t>
+          <t>新北市汐止區民族二街30巷22號</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I391" s="2" t="inlineStr">
@@ -18632,24 +18632,28 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>雲禾月</t>
+          <t>雄鷹天映湖</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr"/>
-      <c r="G392" s="2" t="inlineStr"/>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區湖東街5巷50號</t>
+        </is>
+      </c>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J392" s="2" t="inlineStr">
@@ -18671,12 +18675,12 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>淡水區</t>
+          <t>汐止區</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>京美晴朗</t>
+          <t>雲禾月</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
@@ -18720,20 +18724,16 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>兆美萬海</t>
+          <t>京美晴朗</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr"/>
-      <c r="G394" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區望高樓段535、535-1地號</t>
-        </is>
-      </c>
+      <c r="G394" s="2" t="inlineStr"/>
       <c r="H394" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18741,7 +18741,7 @@
       </c>
       <c r="I394" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J394" s="2" t="inlineStr">
@@ -18768,12 +18768,20 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>光全御苑</t>
-        </is>
-      </c>
-      <c r="E395" s="2" t="inlineStr"/>
+          <t>兆美萬海</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F395" s="2" t="inlineStr"/>
-      <c r="G395" s="2" t="inlineStr"/>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區望高樓段535、535-1地號</t>
+        </is>
+      </c>
       <c r="H395" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18781,12 +18789,12 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J395" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -18808,20 +18816,12 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>台北別墅</t>
-        </is>
-      </c>
-      <c r="E396" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>光全御苑</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr"/>
       <c r="F396" s="2" t="inlineStr"/>
-      <c r="G396" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區尚頂一街</t>
-        </is>
-      </c>
+      <c r="G396" s="2" t="inlineStr"/>
       <c r="H396" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18829,12 +18829,12 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -18856,7 +18856,7 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>合康植芯</t>
+          <t>台北別墅</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
@@ -18867,7 +18867,7 @@
       <c r="F397" s="2" t="inlineStr"/>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路三段202巷65弄</t>
+          <t>新北市淡水區尚頂一街</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -18904,12 +18904,20 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>合謙劃時代</t>
-        </is>
-      </c>
-      <c r="E398" s="2" t="inlineStr"/>
+          <t>合康植芯</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F398" s="2" t="inlineStr"/>
-      <c r="G398" s="2" t="inlineStr"/>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區濱海路三段202巷65弄</t>
+        </is>
+      </c>
       <c r="H398" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18917,7 +18925,7 @@
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J398" s="2" t="inlineStr">
@@ -18944,20 +18952,12 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>合謙耀時代</t>
-        </is>
-      </c>
-      <c r="E399" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>合謙劃時代</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr"/>
       <c r="F399" s="2" t="inlineStr"/>
-      <c r="G399" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市段185地號</t>
-        </is>
-      </c>
+      <c r="G399" s="2" t="inlineStr"/>
       <c r="H399" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J399" s="2" t="inlineStr">
@@ -18992,7 +18992,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>向陽</t>
+          <t>合謙耀時代</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
@@ -19003,7 +19003,7 @@
       <c r="F400" s="2" t="inlineStr"/>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
+          <t>新北市淡水區新市段185地號</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -19040,7 +19040,7 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>員邦徊</t>
+          <t>向陽</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -19051,7 +19051,7 @@
       <c r="F401" s="2" t="inlineStr"/>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路72巷</t>
+          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -19088,23 +19088,23 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>嘉潤家泰氧之森</t>
+          <t>員邦徊</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr"/>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路88號</t>
+          <t>新北市淡水區坪頂路72巷</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I402" s="2" t="inlineStr">
@@ -19136,23 +19136,23 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>富麗ONE</t>
+          <t>嘉潤家泰氧之森</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr"/>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區新市段118地號</t>
+          <t>新北市淡水區坪頂路88號</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I403" s="2" t="inlineStr">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>將捷建設紅樹林案</t>
+          <t>富麗ONE</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -19195,12 +19195,12 @@
       <c r="F404" s="2" t="inlineStr"/>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
+          <t>新北市淡水區新市段118地號</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I404" s="2" t="inlineStr">
@@ -19232,23 +19232,23 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>山河帝寶</t>
+          <t>將捷建設紅樹林案</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr"/>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
+          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I405" s="2" t="inlineStr">
@@ -19280,18 +19280,18 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>新海城</t>
+          <t>山河帝寶</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr"/>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路二段、新市二路</t>
+          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
@@ -19328,16 +19328,20 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>新海城2夢想市</t>
+          <t>新海城</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr"/>
-      <c r="G407" s="2" t="inlineStr"/>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區沙崙路二段、新市二路</t>
+        </is>
+      </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19345,7 +19349,7 @@
       </c>
       <c r="I407" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J407" s="2" t="inlineStr">
@@ -19372,28 +19376,24 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>村泉蒔美</t>
+          <t>新海城2夢想市</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr"/>
-      <c r="G408" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區中正東路二段143巷12弄</t>
-        </is>
-      </c>
+      <c r="G408" s="2" t="inlineStr"/>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr">
@@ -19420,7 +19420,7 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>水問山</t>
+          <t>村泉蒔美</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
@@ -19431,7 +19431,7 @@
       <c r="F409" s="2" t="inlineStr"/>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段143巷2弄</t>
+          <t>新北市淡水區中正東路二段143巷12弄</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -19468,23 +19468,23 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>水美慕河</t>
+          <t>水問山</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr"/>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路一段47號</t>
+          <t>新北市淡水區中正東路二段143巷2弄</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I410" s="2" t="inlineStr">
@@ -19516,18 +19516,18 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>湯泉紅樹林</t>
+          <t>水美慕河</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr"/>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段5巷35號</t>
+          <t>新北市淡水區中正東路一段47號</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -19564,7 +19564,7 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>石上青</t>
+          <t>湯泉紅樹林</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -19575,7 +19575,7 @@
       <c r="F412" s="2" t="inlineStr"/>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區八勢一街36號</t>
+          <t>新北市淡水區中正東路二段5巷35號</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>致茂橋豐</t>
+          <t>石上青</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
@@ -19623,7 +19623,7 @@
       <c r="F413" s="2" t="inlineStr"/>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路一段</t>
+          <t>新北市淡水區八勢一街36號</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -19660,18 +19660,18 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>藝沐汀</t>
+          <t>致茂橋豐</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr"/>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區民族路、自強路305巷</t>
+          <t>新北市淡水區沙崙路一段</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -19708,16 +19708,20 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>馥人灣-新濠門</t>
+          <t>藝沐汀</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr"/>
-      <c r="G415" s="2" t="inlineStr"/>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區民族路、自強路305巷</t>
+        </is>
+      </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19725,7 +19729,7 @@
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J415" s="2" t="inlineStr">
@@ -19752,20 +19756,16 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>鴻灃COMO</t>
+          <t>馥人灣-新濠門</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr"/>
-      <c r="G416" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
-        </is>
-      </c>
+      <c r="G416" s="2" t="inlineStr"/>
       <c r="H416" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J416" s="2" t="inlineStr">
@@ -19785,33 +19785,33 @@
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>A20-合磊天沐</t>
+          <t>鴻灃COMO</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr"/>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -19848,16 +19848,20 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>The Nexus 新識界</t>
+          <t>A20-合磊天沐</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr"/>
-      <c r="G418" s="2" t="inlineStr"/>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+        </is>
+      </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19865,7 +19869,7 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J418" s="2" t="inlineStr">
@@ -19892,7 +19896,7 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>一品閣</t>
+          <t>The Nexus 新識界</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
@@ -19936,20 +19940,16 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>中麗若隱</t>
+          <t>一品閣</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr"/>
-      <c r="G420" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
-        </is>
-      </c>
+      <c r="G420" s="2" t="inlineStr"/>
       <c r="H420" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J420" s="2" t="inlineStr">
@@ -19984,7 +19984,7 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>享JIA</t>
+          <t>中麗若隱</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
@@ -19995,7 +19995,7 @@
       <c r="F421" s="2" t="inlineStr"/>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區青山一路157號旁</t>
+          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -20032,18 +20032,18 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>保利首綻</t>
+          <t>享JIA</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr"/>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐路225號對面</t>
+          <t>桃園市中壢區青山一路157號旁</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -20080,16 +20080,20 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>勤樸悅圓</t>
+          <t>保利首綻</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr"/>
-      <c r="G423" s="2" t="inlineStr"/>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐路225號對面</t>
+        </is>
+      </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20097,7 +20101,7 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr">
@@ -20124,20 +20128,16 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>君臨塘詩-慕荷</t>
+          <t>勤樸悅圓</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr"/>
-      <c r="G424" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
-        </is>
-      </c>
+      <c r="G424" s="2" t="inlineStr"/>
       <c r="H424" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr">
@@ -20172,18 +20172,18 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>和發采采</t>
+          <t>君臨塘詩-慕荷</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr"/>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區新生路二段378之2號對面</t>
+          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -20220,18 +20220,18 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>品坤學</t>
+          <t>和發采采</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr"/>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區環西路二段25巷11號旁</t>
+          <t>桃園市中壢區新生路二段378之2號對面</t>
         </is>
       </c>
       <c r="H426" s="2" t="inlineStr">
@@ -20268,16 +20268,20 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>大亮FIKA</t>
+          <t>品坤學</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr"/>
-      <c r="G427" s="2" t="inlineStr"/>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區環西路二段25巷11號旁</t>
+        </is>
+      </c>
       <c r="H427" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20285,7 +20289,7 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J427" s="2" t="inlineStr">
@@ -20312,10 +20316,14 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>大清上景</t>
-        </is>
-      </c>
-      <c r="E428" s="2" t="inlineStr"/>
+          <t>大亮FIKA</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F428" s="2" t="inlineStr"/>
       <c r="G428" s="2" t="inlineStr"/>
       <c r="H428" s="2" t="inlineStr">
@@ -20352,20 +20360,12 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>大清星湛-璞樂</t>
-        </is>
-      </c>
-      <c r="E429" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>大清上景</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr"/>
       <c r="F429" s="2" t="inlineStr"/>
-      <c r="G429" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區水青路520號對面</t>
-        </is>
-      </c>
+      <c r="G429" s="2" t="inlineStr"/>
       <c r="H429" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20373,7 +20373,7 @@
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J429" s="2" t="inlineStr">
@@ -20400,16 +20400,20 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>大清璞樂</t>
+          <t>大清星湛-璞樂</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr"/>
-      <c r="G430" s="2" t="inlineStr"/>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區水青路520號對面</t>
+        </is>
+      </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20417,7 +20421,7 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J430" s="2" t="inlineStr">
@@ -20444,7 +20448,7 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>大睦I-CITY(A19)</t>
+          <t>大清璞樂</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
@@ -20488,10 +20492,14 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>大睦站前首席</t>
-        </is>
-      </c>
-      <c r="E432" s="2" t="inlineStr"/>
+          <t>大睦I-CITY(A19)</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F432" s="2" t="inlineStr"/>
       <c r="G432" s="2" t="inlineStr"/>
       <c r="H432" s="2" t="inlineStr">
@@ -20528,14 +20536,10 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>大華畔</t>
-        </is>
-      </c>
-      <c r="E433" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>大睦站前首席</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr"/>
       <c r="F433" s="2" t="inlineStr"/>
       <c r="G433" s="2" t="inlineStr"/>
       <c r="H433" s="2" t="inlineStr">
@@ -20572,20 +20576,16 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>威均君藏</t>
+          <t>大華畔</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr"/>
-      <c r="G434" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
-        </is>
-      </c>
+      <c r="G434" s="2" t="inlineStr"/>
       <c r="H434" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20593,7 +20593,7 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J434" s="2" t="inlineStr">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>威均天璽</t>
+          <t>威均君藏</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
@@ -20631,7 +20631,7 @@
       <c r="F435" s="2" t="inlineStr"/>
       <c r="G435" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區領航北路二段、永春路口</t>
+          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
         </is>
       </c>
       <c r="H435" s="2" t="inlineStr">
@@ -20668,12 +20668,20 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>宇惠曦</t>
-        </is>
-      </c>
-      <c r="E436" s="2" t="inlineStr"/>
+          <t>威均天璽</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F436" s="2" t="inlineStr"/>
-      <c r="G436" s="2" t="inlineStr"/>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區領航北路二段、永春路口</t>
+        </is>
+      </c>
       <c r="H436" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20681,7 +20689,7 @@
       </c>
       <c r="I436" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J436" s="2" t="inlineStr">
@@ -20708,14 +20716,10 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>宜誠丽左岸</t>
-        </is>
-      </c>
-      <c r="E437" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>宇惠曦</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr"/>
       <c r="F437" s="2" t="inlineStr"/>
       <c r="G437" s="2" t="inlineStr"/>
       <c r="H437" s="2" t="inlineStr">
@@ -20752,7 +20756,7 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>宜誠泱</t>
+          <t>宜誠丽左岸</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
@@ -20796,10 +20800,14 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>宜雄湛</t>
-        </is>
-      </c>
-      <c r="E439" s="2" t="inlineStr"/>
+          <t>宜誠泱</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F439" s="2" t="inlineStr"/>
       <c r="G439" s="2" t="inlineStr"/>
       <c r="H439" s="2" t="inlineStr">
@@ -20836,7 +20844,7 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>宜雄湛</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr"/>
@@ -20876,14 +20884,10 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>寶台天馳</t>
-        </is>
-      </c>
-      <c r="E441" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>家瑞No.2</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr"/>
       <c r="F441" s="2" t="inlineStr"/>
       <c r="G441" s="2" t="inlineStr"/>
       <c r="H441" s="2" t="inlineStr">
@@ -20920,20 +20924,16 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>廣川市</t>
+          <t>寶台天馳</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr"/>
-      <c r="G442" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區聖德路一段、崇德二路口</t>
-        </is>
-      </c>
+      <c r="G442" s="2" t="inlineStr"/>
       <c r="H442" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
@@ -20968,12 +20968,20 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>弘鼎金家園</t>
-        </is>
-      </c>
-      <c r="E443" s="2" t="inlineStr"/>
+          <t>廣川市</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F443" s="2" t="inlineStr"/>
-      <c r="G443" s="2" t="inlineStr"/>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+        </is>
+      </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20981,7 +20989,7 @@
       </c>
       <c r="I443" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J443" s="2" t="inlineStr">
@@ -21008,14 +21016,10 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>悅新艾玥</t>
-        </is>
-      </c>
-      <c r="E444" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>弘鼎金家園</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr"/>
       <c r="F444" s="2" t="inlineStr"/>
       <c r="G444" s="2" t="inlineStr"/>
       <c r="H444" s="2" t="inlineStr">
@@ -21052,7 +21056,7 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>憶聲智匯科技園區</t>
+          <t>悅新艾玥</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
@@ -21096,20 +21100,16 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>新大萃</t>
+          <t>憶聲智匯科技園區</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F446" s="2" t="inlineStr"/>
-      <c r="G446" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔五街</t>
-        </is>
-      </c>
+      <c r="G446" s="2" t="inlineStr"/>
       <c r="H446" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21117,7 +21117,7 @@
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J446" s="2" t="inlineStr">
@@ -21144,12 +21144,20 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>昆旺青茵悦</t>
-        </is>
-      </c>
-      <c r="E447" s="2" t="inlineStr"/>
+          <t>新大萃</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F447" s="2" t="inlineStr"/>
-      <c r="G447" s="2" t="inlineStr"/>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔五街</t>
+        </is>
+      </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21157,7 +21165,7 @@
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
@@ -21184,28 +21192,20 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>昭揚天朗</t>
-        </is>
-      </c>
-      <c r="E448" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>昆旺青茵悦</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr"/>
       <c r="F448" s="2" t="inlineStr"/>
-      <c r="G448" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
-        </is>
-      </c>
+      <c r="G448" s="2" t="inlineStr"/>
       <c r="H448" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
@@ -21232,20 +21232,28 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>晶采學</t>
-        </is>
-      </c>
-      <c r="E449" s="2" t="inlineStr"/>
+          <t>昭揚天朗</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F449" s="2" t="inlineStr"/>
-      <c r="G449" s="2" t="inlineStr"/>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
+        </is>
+      </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr">
@@ -21272,7 +21280,7 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>柏宣天擎</t>
+          <t>晶采學</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr"/>
@@ -21312,14 +21320,10 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>樂MORE</t>
-        </is>
-      </c>
-      <c r="E451" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>柏宣天擎</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr"/>
       <c r="F451" s="2" t="inlineStr"/>
       <c r="G451" s="2" t="inlineStr"/>
       <c r="H451" s="2" t="inlineStr">
@@ -21356,10 +21360,14 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>正發廠王NO.3</t>
-        </is>
-      </c>
-      <c r="E452" s="2" t="inlineStr"/>
+          <t>樂MORE</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F452" s="2" t="inlineStr"/>
       <c r="G452" s="2" t="inlineStr"/>
       <c r="H452" s="2" t="inlineStr">
@@ -21396,20 +21404,12 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>深耕17</t>
-        </is>
-      </c>
-      <c r="E453" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>正發廠王NO.3</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr"/>
       <c r="F453" s="2" t="inlineStr"/>
-      <c r="G453" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區啟文路二段176巷21號對面</t>
-        </is>
-      </c>
+      <c r="G453" s="2" t="inlineStr"/>
       <c r="H453" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J453" s="2" t="inlineStr">
@@ -21444,16 +21444,20 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>湘榭別墅</t>
+          <t>深耕17</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr"/>
-      <c r="G454" s="2" t="inlineStr"/>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區啟文路二段176巷21號對面</t>
+        </is>
+      </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21461,7 +21465,7 @@
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J454" s="2" t="inlineStr">
@@ -21488,20 +21492,16 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>澍之丘</t>
+          <t>湘榭別墅</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr"/>
-      <c r="G455" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區月桃路615巷</t>
-        </is>
-      </c>
+      <c r="G455" s="2" t="inlineStr"/>
       <c r="H455" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21509,7 +21509,7 @@
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr">
@@ -21536,16 +21536,20 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>璟城A22</t>
+          <t>澍之丘</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr"/>
-      <c r="G456" s="2" t="inlineStr"/>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區月桃路615巷</t>
+        </is>
+      </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21553,7 +21557,7 @@
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J456" s="2" t="inlineStr">
@@ -21580,7 +21584,7 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>皇普園首之道</t>
+          <t>璟城A22</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
@@ -21624,20 +21628,16 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>皇普賦隱</t>
+          <t>皇普園首之道</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr"/>
-      <c r="G458" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔二街</t>
-        </is>
-      </c>
+      <c r="G458" s="2" t="inlineStr"/>
       <c r="H458" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">
@@ -21672,16 +21672,20 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>益展有福</t>
+          <t>皇普賦隱</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr"/>
-      <c r="G459" s="2" t="inlineStr"/>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔二街</t>
+        </is>
+      </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21689,7 +21693,7 @@
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr">
@@ -21716,7 +21720,7 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>立信悦榕</t>
+          <t>益展有福</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
@@ -21738,7 +21742,7 @@
       </c>
       <c r="J460" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -21760,7 +21764,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>站前新鋭</t>
+          <t>立信悦榕</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -21782,7 +21786,7 @@
       </c>
       <c r="J461" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -21804,7 +21808,7 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>綠意領航1號</t>
+          <t>站前新鋭</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -21848,7 +21852,7 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>聚泰雲藝</t>
+          <t>綠意領航1號</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
@@ -21892,20 +21896,16 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>聯懋杉苑</t>
+          <t>聚泰雲藝</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr"/>
-      <c r="G464" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區靠近興西二路及興北二路</t>
-        </is>
-      </c>
+      <c r="G464" s="2" t="inlineStr"/>
       <c r="H464" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21913,7 +21913,7 @@
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J464" s="2" t="inlineStr">
@@ -21940,16 +21940,20 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>聯懋杉苑</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F465" s="2" t="inlineStr"/>
-      <c r="G465" s="2" t="inlineStr"/>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區靠近興西二路及興北二路</t>
+        </is>
+      </c>
       <c r="H465" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21957,7 +21961,7 @@
       </c>
       <c r="I465" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J465" s="2" t="inlineStr">
@@ -21984,7 +21988,7 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>菁美學</t>
+          <t>荷沐莊園</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
@@ -22028,7 +22032,7 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-THE ONE</t>
+          <t>菁美學</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
@@ -22072,7 +22076,7 @@
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-綠景苑</t>
+          <t>藍海帝國-THE ONE</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
@@ -22116,10 +22120,14 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>誠鑫19</t>
-        </is>
-      </c>
-      <c r="E469" s="2" t="inlineStr"/>
+          <t>藍海帝國-綠景苑</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F469" s="2" t="inlineStr"/>
       <c r="G469" s="2" t="inlineStr"/>
       <c r="H469" s="2" t="inlineStr">
@@ -22156,14 +22164,10 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>路易威登</t>
-        </is>
-      </c>
-      <c r="E470" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>誠鑫19</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr"/>
       <c r="F470" s="2" t="inlineStr"/>
       <c r="G470" s="2" t="inlineStr"/>
       <c r="H470" s="2" t="inlineStr">
@@ -22200,7 +22204,7 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>鑫利川-三城</t>
+          <t>路易威登</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
@@ -22244,7 +22248,7 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>閣美學</t>
+          <t>鑫利川-三城</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
@@ -22288,7 +22292,7 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>青城之愛3</t>
+          <t>閣美學</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
@@ -22332,7 +22336,7 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>鴻廣川湛</t>
+          <t>青城之愛3</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -22376,20 +22380,16 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>鴻踞樸藝</t>
+          <t>鴻廣川湛</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr"/>
-      <c r="G475" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區興北一路及興東路 交叉口</t>
-        </is>
-      </c>
+      <c r="G475" s="2" t="inlineStr"/>
       <c r="H475" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="I475" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J475" s="2" t="inlineStr">
@@ -22419,21 +22419,25 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>三鶯澤苑</t>
+          <t>鴻踞樸藝</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr"/>
-      <c r="G476" s="2" t="inlineStr"/>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興北一路及興東路 交叉口</t>
+        </is>
+      </c>
       <c r="H476" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22441,7 +22445,7 @@
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J476" s="2" t="inlineStr">
@@ -22468,20 +22472,16 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>上順麗</t>
+          <t>三鶯澤苑</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr"/>
-      <c r="G477" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區客運一段340地號</t>
-        </is>
-      </c>
+      <c r="G477" s="2" t="inlineStr"/>
       <c r="H477" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22489,7 +22489,7 @@
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J477" s="2" t="inlineStr">
@@ -22516,16 +22516,20 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>中麗北極星</t>
+          <t>上順麗</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr"/>
-      <c r="G478" s="2" t="inlineStr"/>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區客運一段340地號</t>
+        </is>
+      </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22533,7 +22537,7 @@
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr">
@@ -22560,7 +22564,7 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>京懋敦和</t>
+          <t>中麗北極星</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
@@ -22604,7 +22608,7 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>佳暘青見</t>
+          <t>京懋敦和</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
@@ -22648,20 +22652,16 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>偉築新豐州</t>
+          <t>佳暘青見</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr"/>
-      <c r="G481" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區青峰路二段117~129號</t>
-        </is>
-      </c>
+      <c r="G481" s="2" t="inlineStr"/>
       <c r="H481" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22669,7 +22669,7 @@
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J481" s="2" t="inlineStr">
@@ -22696,16 +22696,20 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>傳佳樂</t>
+          <t>偉築新豐州</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr"/>
-      <c r="G482" s="2" t="inlineStr"/>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區青峰路二段117~129號</t>
+        </is>
+      </c>
       <c r="H482" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22713,7 +22717,7 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr">
@@ -22740,7 +22744,7 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>元基至善2</t>
+          <t>傳佳樂</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
@@ -22784,7 +22788,7 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>力璞翔-豐禾</t>
+          <t>元基至善2</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
@@ -22806,7 +22810,7 @@
       </c>
       <c r="J484" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -22828,20 +22832,16 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>合展悦恬</t>
+          <t>力璞翔-豐禾</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr"/>
-      <c r="G485" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G485" s="2" t="inlineStr"/>
       <c r="H485" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22849,12 +22849,12 @@
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -22876,18 +22876,18 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>合陽逸境</t>
+          <t>合展悦恬</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr"/>
       <c r="G486" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區青峰段273號地號</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H486" s="2" t="inlineStr">
@@ -22924,18 +22924,18 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>名川琢域</t>
+          <t>合陽逸境</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr"/>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
+          <t>桃園市大園區青峰段273號地號</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -22972,18 +22972,18 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅</t>
+          <t>名川琢域</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr"/>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區內海墘段 110-84</t>
+          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -23020,12 +23020,20 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅Villa</t>
-        </is>
-      </c>
-      <c r="E489" s="2" t="inlineStr"/>
+          <t>垽赫海漾星墅</t>
+        </is>
+      </c>
+      <c r="E489" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F489" s="2" t="inlineStr"/>
-      <c r="G489" s="2" t="inlineStr"/>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區內海墘段 110-84</t>
+        </is>
+      </c>
       <c r="H489" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23033,7 +23041,7 @@
       </c>
       <c r="I489" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J489" s="2" t="inlineStr">
@@ -23060,20 +23068,12 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
-        </is>
-      </c>
-      <c r="E490" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>垽赫海漾星墅Villa</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr"/>
       <c r="F490" s="2" t="inlineStr"/>
-      <c r="G490" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園七街9號對面</t>
-        </is>
-      </c>
+      <c r="G490" s="2" t="inlineStr"/>
       <c r="H490" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23081,7 +23081,7 @@
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J490" s="2" t="inlineStr">
@@ -23108,16 +23108,20 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>大地玥</t>
+          <t>大地昕</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr"/>
-      <c r="G491" s="2" t="inlineStr"/>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區園七街9號對面</t>
+        </is>
+      </c>
       <c r="H491" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23125,7 +23129,7 @@
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J491" s="2" t="inlineStr">
@@ -23152,7 +23156,7 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>大地．呈</t>
+          <t>大地玥</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
@@ -23196,7 +23200,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>大禾苑</t>
+          <t>大地．呈</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
@@ -23240,7 +23244,7 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>威均帝璽</t>
+          <t>大禾苑</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
@@ -23284,20 +23288,16 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>宗佳領御</t>
+          <t>威均帝璽</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr"/>
-      <c r="G495" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區中路與科七街</t>
-        </is>
-      </c>
+      <c r="G495" s="2" t="inlineStr"/>
       <c r="H495" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J495" s="2" t="inlineStr">
@@ -23332,16 +23332,20 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>宜誠玉環</t>
+          <t>宗佳領御</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr"/>
-      <c r="G496" s="2" t="inlineStr"/>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區中路與科七街</t>
+        </is>
+      </c>
       <c r="H496" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23349,7 +23353,7 @@
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J496" s="2" t="inlineStr">
@@ -23376,7 +23380,7 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>家綻</t>
+          <t>宜誠玉環</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
@@ -23420,20 +23424,16 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>家綻2</t>
+          <t>家綻</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr"/>
-      <c r="G498" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區柴梳崙路268巷</t>
-        </is>
-      </c>
+      <c r="G498" s="2" t="inlineStr"/>
       <c r="H498" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23441,7 +23441,7 @@
       </c>
       <c r="I498" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J498" s="2" t="inlineStr">
@@ -23468,16 +23468,20 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>富總日日</t>
+          <t>家綻2</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr"/>
-      <c r="G499" s="2" t="inlineStr"/>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區柴梳崙路268巷</t>
+        </is>
+      </c>
       <c r="H499" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23485,7 +23489,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr">
@@ -23512,10 +23516,14 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>山榆.柏悅</t>
-        </is>
-      </c>
-      <c r="E500" s="2" t="inlineStr"/>
+          <t>富總日日</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F500" s="2" t="inlineStr"/>
       <c r="G500" s="2" t="inlineStr"/>
       <c r="H500" s="2" t="inlineStr">
@@ -23530,7 +23538,7 @@
       </c>
       <c r="J500" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -23552,20 +23560,12 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>山榆柏悅</t>
-        </is>
-      </c>
-      <c r="E501" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>山榆.柏悅</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr"/>
       <c r="F501" s="2" t="inlineStr"/>
-      <c r="G501" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區永園路二段152號旁</t>
-        </is>
-      </c>
+      <c r="G501" s="2" t="inlineStr"/>
       <c r="H501" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23573,12 +23573,12 @@
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J501" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -23600,16 +23600,20 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>川洋青勻</t>
+          <t>山榆柏悅</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr"/>
-      <c r="G502" s="2" t="inlineStr"/>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區永園路二段152號旁</t>
+        </is>
+      </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23617,7 +23621,7 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
@@ -23644,7 +23648,7 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>御禾院</t>
+          <t>川洋青勻</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
@@ -23688,20 +23692,16 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>悦恬</t>
+          <t>御禾院</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F504" s="2" t="inlineStr"/>
-      <c r="G504" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G504" s="2" t="inlineStr"/>
       <c r="H504" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J504" s="2" t="inlineStr">
@@ -23736,7 +23736,7 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>日勝好日子</t>
+          <t>悦恬</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
@@ -23747,7 +23747,7 @@
       <c r="F505" s="2" t="inlineStr"/>
       <c r="G505" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區後館路1巷旁</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H505" s="2" t="inlineStr">
@@ -23784,7 +23784,7 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>日青悠</t>
+          <t>日勝好日子</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
@@ -23795,7 +23795,7 @@
       <c r="F506" s="2" t="inlineStr"/>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區五青路63巷257號旁</t>
+          <t>桃園市大園區後館路1巷旁</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
@@ -23832,12 +23832,20 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>松合苑5</t>
-        </is>
-      </c>
-      <c r="E507" s="2" t="inlineStr"/>
+          <t>日青悠</t>
+        </is>
+      </c>
+      <c r="E507" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F507" s="2" t="inlineStr"/>
-      <c r="G507" s="2" t="inlineStr"/>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區五青路63巷257號旁</t>
+        </is>
+      </c>
       <c r="H507" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23845,7 +23853,7 @@
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J507" s="2" t="inlineStr">
@@ -23872,20 +23880,12 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>璟都新世界</t>
-        </is>
-      </c>
-      <c r="E508" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>松合苑5</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr"/>
       <c r="F508" s="2" t="inlineStr"/>
-      <c r="G508" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區大觀路及環區北路口</t>
-        </is>
-      </c>
+      <c r="G508" s="2" t="inlineStr"/>
       <c r="H508" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23893,7 +23893,7 @@
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr">
@@ -23920,16 +23920,20 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>福興豐璟</t>
+          <t>璟都新世界</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F509" s="2" t="inlineStr"/>
-      <c r="G509" s="2" t="inlineStr"/>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區大觀路及環區北路口</t>
+        </is>
+      </c>
       <c r="H509" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23937,7 +23941,7 @@
       </c>
       <c r="I509" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J509" s="2" t="inlineStr">
@@ -23964,7 +23968,7 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>立程·晴美</t>
+          <t>福興豐璟</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
@@ -24008,20 +24012,16 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>立程‧晴美</t>
+          <t>立程·晴美</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F511" s="2" t="inlineStr"/>
-      <c r="G511" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區學七街69-1號</t>
-        </is>
-      </c>
+      <c r="G511" s="2" t="inlineStr"/>
       <c r="H511" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24029,7 +24029,7 @@
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J511" s="2" t="inlineStr">
@@ -24056,23 +24056,23 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>立程建設客運二段案</t>
+          <t>立程‧晴美</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr"/>
       <c r="G512" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區學七街69-1號旁</t>
+          <t>桃園市大園區學七街69-1號</t>
         </is>
       </c>
       <c r="H512" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I512" s="2" t="inlineStr">
@@ -24104,29 +24104,33 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>立鴻晶硯</t>
+          <t>立程建設客運二段案</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr"/>
-      <c r="G513" s="2" t="inlineStr"/>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區學七街69-1號旁</t>
+        </is>
+      </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J513" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -24148,7 +24152,7 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>臥墨池</t>
+          <t>立鴻晶硯</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
@@ -24170,7 +24174,7 @@
       </c>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24192,7 +24196,7 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>臻璞</t>
+          <t>臥墨池</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
@@ -24236,7 +24240,7 @@
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>興禾  築美學</t>
+          <t>臻璞</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -24280,20 +24284,16 @@
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>航綻甜心</t>
+          <t>興禾  築美學</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F517" s="2" t="inlineStr"/>
-      <c r="G517" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路與科五路交叉口</t>
-        </is>
-      </c>
+      <c r="G517" s="2" t="inlineStr"/>
       <c r="H517" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24301,7 +24301,7 @@
       </c>
       <c r="I517" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J517" s="2" t="inlineStr">
@@ -24328,16 +24328,20 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>英堡日朗</t>
+          <t>航綻甜心</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F518" s="2" t="inlineStr"/>
-      <c r="G518" s="2" t="inlineStr"/>
+      <c r="G518" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路與科五路交叉口</t>
+        </is>
+      </c>
       <c r="H518" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24345,7 +24349,7 @@
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J518" s="2" t="inlineStr">
@@ -24372,20 +24376,16 @@
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>薪成家II</t>
+          <t>英堡日朗</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr"/>
-      <c r="G519" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路597號</t>
-        </is>
-      </c>
+      <c r="G519" s="2" t="inlineStr"/>
       <c r="H519" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="I519" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J519" s="2" t="inlineStr">
@@ -24420,16 +24420,20 @@
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>逸偉A+</t>
+          <t>薪成家II</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr"/>
-      <c r="G520" s="2" t="inlineStr"/>
+      <c r="G520" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路597號</t>
+        </is>
+      </c>
       <c r="H520" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24437,7 +24441,7 @@
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J520" s="2" t="inlineStr">
@@ -24464,10 +24468,14 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>遠雄仰森</t>
-        </is>
-      </c>
-      <c r="E521" s="2" t="inlineStr"/>
+          <t>逸偉A+</t>
+        </is>
+      </c>
+      <c r="E521" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F521" s="2" t="inlineStr"/>
       <c r="G521" s="2" t="inlineStr"/>
       <c r="H521" s="2" t="inlineStr">
@@ -24504,14 +24512,10 @@
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>鈞貴極美II</t>
-        </is>
-      </c>
-      <c r="E522" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>遠雄仰森</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr"/>
       <c r="F522" s="2" t="inlineStr"/>
       <c r="G522" s="2" t="inlineStr"/>
       <c r="H522" s="2" t="inlineStr">
@@ -24548,7 +24552,7 @@
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>高誠君品</t>
+          <t>鈞貴極美II</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
@@ -24592,10 +24596,14 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>龍築靜玥</t>
-        </is>
-      </c>
-      <c r="E524" s="2" t="inlineStr"/>
+          <t>高誠君品</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F524" s="2" t="inlineStr"/>
       <c r="G524" s="2" t="inlineStr"/>
       <c r="H524" s="2" t="inlineStr">
@@ -24614,15 +24622,55 @@
         </is>
       </c>
     </row>
-    <row r="526">
-      <c r="A526" s="3" t="inlineStr">
-        <is>
-          <t>最後更新：2026-09-07 12:55（台灣時間）　共 523 筆　資料來源：好房網、樂屋網</t>
+    <row r="525">
+      <c r="A525" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B525" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C525" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D525" s="2" t="inlineStr">
+        <is>
+          <t>龍築靜玥</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr"/>
+      <c r="F525" s="2" t="inlineStr"/>
+      <c r="G525" s="2" t="inlineStr"/>
+      <c r="H525" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I525" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J525" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="3" t="inlineStr">
+        <is>
+          <t>最後更新：2026-09-08 12:51（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J524"/>
+  <autoFilter ref="A1:J525"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24665,7 +24665,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-08 12:51（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-09 12:54（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -1077,15 +1077,11 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>新北市三重區大同南路172巷</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -1093,7 +1089,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4351,9 +4347,17 @@
           <t>合嘉楓疆</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>新北市泰山區和平街及楓樹街交叉口</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -4361,7 +4365,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -4441,11 +4445,15 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>新北市泰山區明志路一段215號</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -4453,7 +4461,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -4485,11 +4493,15 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>新北市泰山區明志路一段168號</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -4497,7 +4509,7 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -4617,11 +4629,15 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>新北市泰山區莊泰路與義東街口</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -4629,7 +4645,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -7607,9 +7623,17 @@
           <t>欣好蒔光</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr"/>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>新北市樹林區柑園街一段170號對面</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7617,7 +7641,7 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
@@ -7649,11 +7673,15 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr"/>
-      <c r="G156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>新北市樹林區西圳街二段12號旁</t>
+        </is>
+      </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7661,7 +7689,7 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
@@ -7688,16 +7716,20 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>騰翔樹与苑</t>
+          <t>騰翔 樹与苑</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr"/>
-      <c r="G157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>新北市樹林區民權街68號旁</t>
+        </is>
+      </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7705,7 +7737,7 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
@@ -7829,11 +7861,15 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區鳳七路與龍三路口</t>
+        </is>
+      </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7841,7 +7877,7 @@
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -7921,11 +7957,15 @@
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr"/>
-      <c r="G162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區國中街與高職東街交叉口</t>
+        </is>
+      </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -7933,7 +7973,7 @@
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
@@ -8103,9 +8143,17 @@
           <t>國華綻</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區鶯桃路182巷96弄</t>
+        </is>
+      </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8113,7 +8161,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
@@ -8191,9 +8239,17 @@
           <t>富霖富鄰</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr"/>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F168" s="2" t="inlineStr"/>
-      <c r="G168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區永吉段 570 地號</t>
+        </is>
+      </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8201,7 +8257,7 @@
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
@@ -8325,11 +8381,15 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F171" s="2" t="inlineStr"/>
-      <c r="G171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區鶯桃路413巷</t>
+        </is>
+      </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8337,7 +8397,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
@@ -8369,11 +8429,15 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr"/>
-      <c r="G172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區鶯歌路285旁</t>
+        </is>
+      </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8381,7 +8445,7 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
@@ -8509,11 +8573,15 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr"/>
-      <c r="G175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>新北市鶯歌區鶯桃路二段與鳳吉一街路口</t>
+        </is>
+      </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -8521,7 +8589,7 @@
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
@@ -16301,23 +16369,19 @@
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr"/>
-      <c r="G342" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區民生路二段183號旁</t>
-        </is>
-      </c>
+      <c r="G342" s="2" t="inlineStr"/>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I342" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J342" s="2" t="inlineStr">
@@ -20321,11 +20385,15 @@
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr"/>
-      <c r="G428" s="2" t="inlineStr"/>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區永順一街30號旁</t>
+        </is>
+      </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20333,7 +20401,7 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J428" s="2" t="inlineStr">
@@ -20761,11 +20829,15 @@
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr"/>
-      <c r="G438" s="2" t="inlineStr"/>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區豐興段235地號</t>
+        </is>
+      </c>
       <c r="H438" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20773,7 +20845,7 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr">
@@ -20929,11 +21001,15 @@
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr"/>
-      <c r="G442" s="2" t="inlineStr"/>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青溪段450地號</t>
+        </is>
+      </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20941,7 +21017,7 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
@@ -21365,11 +21441,15 @@
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr"/>
-      <c r="G452" s="2" t="inlineStr"/>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區民溪三路209巷25號</t>
+        </is>
+      </c>
       <c r="H452" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21377,7 +21457,7 @@
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J452" s="2" t="inlineStr">
@@ -21901,11 +21981,15 @@
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr"/>
-      <c r="G464" s="2" t="inlineStr"/>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區元生三街</t>
+        </is>
+      </c>
       <c r="H464" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21913,7 +21997,7 @@
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J464" s="2" t="inlineStr">
@@ -23113,15 +23197,11 @@
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr"/>
-      <c r="G491" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園七街9號對面</t>
-        </is>
-      </c>
+      <c r="G491" s="2" t="inlineStr"/>
       <c r="H491" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23129,7 +23209,7 @@
       </c>
       <c r="I491" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J491" s="2" t="inlineStr">
@@ -23473,15 +23553,11 @@
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr"/>
-      <c r="G499" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區柴梳崙路268巷</t>
-        </is>
-      </c>
+      <c r="G499" s="2" t="inlineStr"/>
       <c r="H499" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23489,7 +23565,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr">
@@ -24665,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-09 12:54（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-10 12:55（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-10 12:55（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-11 12:51（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-11 12:51（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-12 12:45（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-12 12:45（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-13 12:58（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -18344,7 +18344,7 @@
       </c>
       <c r="H384" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I384" s="2" t="inlineStr">
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-13 12:58（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-14 13:08（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-14 13:08（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-15 13:04（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-15 13:04（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-16 12:59（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-16 12:59（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-17 13:02（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-17 13:02（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-18 12:54（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-18 12:54（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-19 12:47（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-19 12:47（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-20 13:03（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-20 13:03（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-21 13:08（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-21 13:08（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-22 13:10（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-22 13:10（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-23 12:55（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-23 12:55（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-24 13:03（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-24 13:03（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-25 13:07（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-25 13:07（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-26 13:11（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24741,7 +24741,7 @@
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-26 13:11（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-27 13:28（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預售案清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$525</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$526</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J527"/>
+  <dimension ref="A1:J528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9036,29 +9036,33 @@
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>御中央Ⅱ</t>
+          <t>康橋旭</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr"/>
-      <c r="G185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>新北市新店區華城路505號</t>
+        </is>
+      </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -9080,20 +9084,16 @@
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>敦南之森</t>
+          <t>御中央Ⅱ</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr"/>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>新北市新店區永安街45號</t>
-        </is>
-      </c>
+      <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -9128,18 +9128,18 @@
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>敦泰苑</t>
+          <t>敦南之森</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr"/>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區黎明路8號</t>
+          <t>新北市新店區永安街45號</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>昇峰安曼</t>
+          <t>敦泰苑</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       <c r="F188" s="2" t="inlineStr"/>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區安康路二段</t>
+          <t>新北市新店區黎明路8號</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>東基M1</t>
+          <t>昇峰安曼</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -9235,7 +9235,7 @@
       <c r="F189" s="2" t="inlineStr"/>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區寶安街</t>
+          <t>新北市新店區安康路二段</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>樂菲莊園-波爾多2</t>
+          <t>東基M1</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -9283,12 +9283,12 @@
       <c r="F190" s="2" t="inlineStr"/>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區央北二路289號</t>
+          <t>新北市新店區寶安街</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -9320,18 +9320,18 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>波爾多</t>
+          <t>樂菲莊園-波爾多2</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr"/>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區溪園路/央北三路口</t>
+          <t>新北市新店區央北二路289號</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9368,24 +9368,28 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>波爾多2樂菲莊園</t>
+          <t>波爾多</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr"/>
-      <c r="G192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>新北市新店區溪園路/央北三路口</t>
+        </is>
+      </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
@@ -9412,20 +9416,16 @@
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>湯泉綠中海</t>
+          <t>波爾多2樂菲莊園</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr"/>
-      <c r="G193" s="2" t="inlineStr">
-        <is>
-          <t>新北市新店區安祥路、祥和路口</t>
-        </is>
-      </c>
+      <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
@@ -9460,18 +9460,18 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>知馨</t>
+          <t>湯泉綠中海</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區中央三街85號</t>
+          <t>新北市新店區安祥路、祥和路口</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>碧澄市</t>
+          <t>知馨</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -9519,7 +9519,7 @@
       <c r="F195" s="2" t="inlineStr"/>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>新北市新店區青山路311號對面</t>
+          <t>新北市新店區中央三街85號</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -9551,28 +9551,28 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>深坑區</t>
+          <t>新店區</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>宏博建設紅葉街案</t>
+          <t>碧澄市</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>新北市深坑區紅葉街</t>
+          <t>新北市新店區青山路311號對面</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -9594,34 +9594,38 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>新莊林口線</t>
+          <t>新店深坑線</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>八里區</t>
+          <t>深坑區</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>勤樸天翔</t>
+          <t>宏博建設紅葉街案</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr"/>
-      <c r="G197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>新北市深坑區紅葉街</t>
+        </is>
+      </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
@@ -9648,7 +9652,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>勤樸天逸</t>
+          <t>勤樸天翔</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -9692,7 +9696,7 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>四季Lavie</t>
+          <t>勤樸天逸</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -9714,7 +9718,7 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -9736,20 +9740,16 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>城市君臨</t>
+          <t>四季Lavie</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr"/>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t>新北市八里區文昌二街37號斜對面</t>
-        </is>
-      </c>
+      <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -9757,12 +9757,12 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>大新田幸福之森</t>
+          <t>城市君臨</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       <c r="F201" s="2" t="inlineStr"/>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>新北市八里區十三行路</t>
+          <t>新北市八里區文昌二街37號斜對面</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -9832,23 +9832,23 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>日初</t>
+          <t>大新田幸福之森</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>新北市八里區中山路三段、訊塘二路交叉口</t>
+          <t>新北市八里區十三行路</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>百欣豐光</t>
+          <t>日初</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -9891,12 +9891,12 @@
       <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>新北市八里區中山路二段323巷27號</t>
+          <t>新北市八里區中山路三段、訊塘二路交叉口</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr">
@@ -9928,16 +9928,20 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>紐約心光</t>
+          <t>百欣豐光</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr"/>
-      <c r="G204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>新北市八里區中山路二段323巷27號</t>
+        </is>
+      </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -9945,7 +9949,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
@@ -9972,28 +9976,24 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>蒔光．墅</t>
+          <t>紐約心光</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr"/>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>新北市八里區賢一街與中山路一段交叉口</t>
-        </is>
-      </c>
+      <c r="G205" s="2" t="inlineStr"/>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
@@ -10020,20 +10020,28 @@
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>豐邑港麗</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr"/>
+          <t>蒔光．墅</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>萬/戶</t>
+        </is>
+      </c>
       <c r="F206" s="2" t="inlineStr"/>
-      <c r="G206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>新北市八里區賢一街與中山路一段交叉口</t>
+        </is>
+      </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
@@ -10060,20 +10068,12 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>馥桂園</t>
-        </is>
-      </c>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>豐邑港麗</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr"/>
       <c r="F207" s="2" t="inlineStr"/>
-      <c r="G207" s="2" t="inlineStr">
-        <is>
-          <t>新北市八里區龍米路二段117巷22~26號</t>
-        </is>
-      </c>
+      <c r="G207" s="2" t="inlineStr"/>
       <c r="H207" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -10081,7 +10081,7 @@
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J207" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>新莊區</t>
+          <t>八里區</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>亞昕商匯中心</t>
+          <t>馥桂園</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -10119,7 +10119,7 @@
       <c r="F208" s="2" t="inlineStr"/>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區富貴路、昌仁路口</t>
+          <t>新北市八里區龍米路二段117巷22~26號</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>亞昕森中央</t>
+          <t>亞昕商匯中心</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>勝旺家</t>
+          <t>亞昕森中央</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       <c r="F210" s="2" t="inlineStr"/>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區福美街172巷</t>
+          <t>新北市新莊區富貴路、昌仁路口</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>勝旺新</t>
+          <t>勝旺家</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -10263,12 +10263,12 @@
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區福德三街</t>
+          <t>新北市新莊區福美街172巷</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I211" s="2" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>合勤共生宅台北保健館</t>
+          <t>勝旺新</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -10311,7 +10311,7 @@
       <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區長青街15號</t>
+          <t>新北市新莊區福德三街</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10348,23 +10348,23 @@
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>國家壹號廣場</t>
+          <t>合勤共生宅台北保健館</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr"/>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中央路</t>
+          <t>新北市新莊區長青街15號</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I213" s="2" t="inlineStr">
@@ -10396,7 +10396,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>國王大道KING PARK</t>
+          <t>國家壹號廣場</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -10407,7 +10407,7 @@
       <c r="F214" s="2" t="inlineStr"/>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中原路</t>
+          <t>新北市新莊區中央路</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -10444,16 +10444,20 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>國鉅富</t>
+          <t>國王大道KING PARK</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F215" s="2" t="inlineStr"/>
-      <c r="G215" s="2" t="inlineStr"/>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區中原路</t>
+        </is>
+      </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -10461,7 +10465,7 @@
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J215" s="2" t="inlineStr">
@@ -10488,7 +10492,7 @@
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>大將美樹</t>
+          <t>國鉅富</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -10532,28 +10536,24 @@
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>宸熙丰悦</t>
+          <t>大將美樹</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr"/>
-      <c r="G217" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區中正路260號</t>
-        </is>
-      </c>
+      <c r="G217" s="2" t="inlineStr"/>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J217" s="2" t="inlineStr">
@@ -10580,18 +10580,18 @@
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>富都新玉</t>
+          <t>宸熙丰悦</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港一街</t>
+          <t>新北市新莊區中正路260號</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>富都新玉-富都區</t>
+          <t>富都新玉</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -10639,12 +10639,12 @@
       <c r="F219" s="2" t="inlineStr"/>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港一街(中港國小對面)</t>
+          <t>新北市新莊區中港一街</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>富都新玉-新玉區</t>
+          <t>富都新玉-富都區</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -10687,7 +10687,7 @@
       <c r="F220" s="2" t="inlineStr"/>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港一街(中港國小對面).</t>
+          <t>新北市新莊區中港一街(中港國小對面)</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -10724,18 +10724,18 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>富都馨</t>
+          <t>富都新玉-新玉區</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區昌德街上</t>
+          <t>新北市新莊區中港一街(中港國小對面).</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>寰宇一號</t>
+          <t>富都馨</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       <c r="F222" s="2" t="inlineStr"/>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區新北大道三段、新知八路、新知十路</t>
+          <t>新北市新莊區昌德街上</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
@@ -10820,23 +10820,23 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>文華苑</t>
+          <t>寰宇一號</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr"/>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中原路及中華路口</t>
+          <t>新北市新莊區新北大道三段、新知八路、新知十路</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
@@ -10868,18 +10868,18 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>新月大河</t>
+          <t>文華苑</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區瓊林路55號旁</t>
+          <t>新北市新莊區中原路及中華路口</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -10916,23 +10916,23 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>日健居</t>
+          <t>新月大河</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr"/>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港路188號</t>
+          <t>新北市新莊區瓊林路55號旁</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>日健昌</t>
+          <t>日健居</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -10975,12 +10975,12 @@
       <c r="F226" s="2" t="inlineStr"/>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區昌盛街105號</t>
+          <t>新北市新莊區中港路188號</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -11012,12 +11012,20 @@
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>日和淳</t>
-        </is>
-      </c>
-      <c r="E227" s="2" t="inlineStr"/>
+          <t>日健昌</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F227" s="2" t="inlineStr"/>
-      <c r="G227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區昌盛街105號</t>
+        </is>
+      </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11025,12 +11033,12 @@
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -11052,28 +11060,20 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>昀集富昱</t>
-        </is>
-      </c>
-      <c r="E228" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>日和淳</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr"/>
       <c r="F228" s="2" t="inlineStr"/>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區五工二路86巷36號</t>
-        </is>
-      </c>
+      <c r="G228" s="2" t="inlineStr"/>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
@@ -11100,20 +11100,28 @@
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>春城麗都</t>
-        </is>
-      </c>
-      <c r="E229" s="2" t="inlineStr"/>
+          <t>昀集富昱</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F229" s="2" t="inlineStr"/>
-      <c r="G229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區五工二路86巷36號</t>
+        </is>
+      </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr">
@@ -11140,28 +11148,20 @@
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>本格明水</t>
-        </is>
-      </c>
-      <c r="E230" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>春城麗都</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr"/>
       <c r="F230" s="2" t="inlineStr"/>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區新知一路77號</t>
-        </is>
-      </c>
+      <c r="G230" s="2" t="inlineStr"/>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
@@ -11188,23 +11188,23 @@
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>河成心湛</t>
+          <t>本格明水</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F231" s="2" t="inlineStr"/>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中華路一段26巷</t>
+          <t>新北市新莊區新知一路77號</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr">
@@ -11236,18 +11236,18 @@
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>玄泰蔦居</t>
+          <t>河成心湛</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr"/>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中原段212、213、214地號</t>
+          <t>新北市新莊區中華路一段26巷</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>百邑富都匯</t>
+          <t>玄泰蔦居</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -11295,7 +11295,7 @@
       <c r="F233" s="2" t="inlineStr"/>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中央路、中華路口</t>
+          <t>新北市新莊區中原段212、213、214地號</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>皇鼎心莊</t>
+          <t>百邑富都匯</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -11343,7 +11343,7 @@
       <c r="F234" s="2" t="inlineStr"/>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區民安路157號</t>
+          <t>新北市新莊區中央路、中華路口</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -11380,18 +11380,18 @@
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>碧瑤建設中平路案(尚未取得建照)</t>
+          <t>皇鼎心莊</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr"/>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中平路、榮華路二段</t>
+          <t>新北市新莊區民安路157號</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>碧瑤建設瓊林路案(尚未取得建照)</t>
+          <t>碧瑤建設中平路案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       <c r="F236" s="2" t="inlineStr"/>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區瓊林路</t>
+          <t>新北市新莊區中平路、榮華路二段</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
@@ -11476,18 +11476,18 @@
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>碧瑤敦灃</t>
+          <t>碧瑤建設瓊林路案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr"/>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區副都心段一小段228、231、242地號</t>
+          <t>新北市新莊區瓊林路</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -11524,23 +11524,23 @@
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>禾蓮心中美</t>
+          <t>碧瑤敦灃</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中港路148號</t>
+          <t>新北市新莊區副都心段一小段228、231、242地號</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
@@ -11572,16 +11572,20 @@
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>自由之丘</t>
+          <t>禾蓮心中美</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F239" s="2" t="inlineStr"/>
-      <c r="G239" s="2" t="inlineStr"/>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區中港路148號</t>
+        </is>
+      </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11589,7 +11593,7 @@
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J239" s="2" t="inlineStr">
@@ -11616,7 +11620,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>西勝時星</t>
+          <t>自由之丘</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -11660,28 +11664,24 @@
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>豐盛</t>
+          <t>西勝時星</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr"/>
-      <c r="G241" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區豐盛二街、新樹路699巷</t>
-        </is>
-      </c>
+      <c r="G241" s="2" t="inlineStr"/>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J241" s="2" t="inlineStr">
@@ -11708,24 +11708,28 @@
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>這一站，幸福</t>
+          <t>豐盛</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr"/>
-      <c r="G242" s="2" t="inlineStr"/>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>新北市新莊區豐盛二街、新樹路699巷</t>
+        </is>
+      </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J242" s="2" t="inlineStr">
@@ -11752,10 +11756,14 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>邦瓏雍玥</t>
-        </is>
-      </c>
-      <c r="E243" s="2" t="inlineStr"/>
+          <t>這一站，幸福</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F243" s="2" t="inlineStr"/>
       <c r="G243" s="2" t="inlineStr"/>
       <c r="H243" s="2" t="inlineStr">
@@ -11792,20 +11800,12 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>馥華之道</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>邦瓏雍玥</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr"/>
       <c r="F244" s="2" t="inlineStr"/>
-      <c r="G244" s="2" t="inlineStr">
-        <is>
-          <t>新北市新莊區福營路、福營路270號交叉口</t>
-        </is>
-      </c>
+      <c r="G244" s="2" t="inlineStr"/>
       <c r="H244" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="I244" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J244" s="2" t="inlineStr">
@@ -11840,23 +11840,23 @@
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>麗寶ALL IN ONE</t>
+          <t>馥華之道</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F245" s="2" t="inlineStr"/>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>新北市新莊區中央路558號</t>
+          <t>新北市新莊區福營路、福營路270號交叉口</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
@@ -11883,23 +11883,23 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>林口區</t>
+          <t>新莊區</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Classy Home</t>
+          <t>麗寶ALL IN ONE</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr"/>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路與民族路口</t>
+          <t>新北市新莊區中央路558號</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -11936,24 +11936,28 @@
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>中光極</t>
+          <t>Classy Home</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr"/>
-      <c r="G247" s="2" t="inlineStr"/>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區忠孝路與民族路口</t>
+        </is>
+      </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J247" s="2" t="inlineStr">
@@ -11980,20 +11984,16 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>九揚華樂</t>
+          <t>中光極</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F248" s="2" t="inlineStr"/>
-      <c r="G248" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區力行段955地號</t>
-        </is>
-      </c>
+      <c r="G248" s="2" t="inlineStr"/>
       <c r="H248" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12001,7 +12001,7 @@
       </c>
       <c r="I248" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J248" s="2" t="inlineStr">
@@ -12028,7 +12028,7 @@
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>亞昕天匯</t>
+          <t>九揚華樂</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -12039,7 +12039,7 @@
       <c r="F249" s="2" t="inlineStr"/>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路及信義路交叉口</t>
+          <t>新北市林口區力行段955地號</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -12076,23 +12076,23 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>亞昕昕銀座</t>
+          <t>亞昕天匯</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr"/>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段636號</t>
+          <t>新北市林口區文化二路及信義路交叉口</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>亞昕森匯</t>
+          <t>亞昕昕銀座</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -12135,7 +12135,7 @@
       <c r="F251" s="2" t="inlineStr"/>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段及信義路交叉口</t>
+          <t>新北市林口區文化三路一段636號</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12172,23 +12172,23 @@
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>亞昕．寓邸</t>
+          <t>亞昕森匯</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr"/>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段、文化二路二段178巷18弄</t>
+          <t>新北市林口區文化二路二段及信義路交叉口</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I252" s="2" t="inlineStr">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>仁愛金鑽</t>
+          <t>亞昕．寓邸</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -12231,12 +12231,12 @@
       <c r="F253" s="2" t="inlineStr"/>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區仁愛路一段、新生街口</t>
+          <t>新北市林口區文化二路二段、文化二路二段178巷18弄</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr">
@@ -12268,18 +12268,18 @@
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>優學</t>
+          <t>仁愛金鑽</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F254" s="2" t="inlineStr"/>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區佳林路</t>
+          <t>新北市林口區仁愛路一段、新生街口</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -12316,23 +12316,23 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>原昕吾旭</t>
+          <t>優學</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr"/>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區麗林段 644 、656地號</t>
+          <t>新北市林口區佳林路</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr">
@@ -12364,12 +12364,20 @@
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>原森</t>
-        </is>
-      </c>
-      <c r="E256" s="2" t="inlineStr"/>
+          <t>原昕吾旭</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>萬/戶</t>
+        </is>
+      </c>
       <c r="F256" s="2" t="inlineStr"/>
-      <c r="G256" s="2" t="inlineStr"/>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區麗林段 644 、656地號</t>
+        </is>
+      </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12377,12 +12385,12 @@
       </c>
       <c r="I256" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -12404,20 +12412,12 @@
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>原森TWIN TOWERS</t>
-        </is>
-      </c>
-      <c r="E257" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>原森</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr"/>
       <c r="F257" s="2" t="inlineStr"/>
-      <c r="G257" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區文化三路及仁愛二路口</t>
-        </is>
-      </c>
+      <c r="G257" s="2" t="inlineStr"/>
       <c r="H257" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12425,12 +12425,12 @@
       </c>
       <c r="I257" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>和洲艾美</t>
+          <t>原森TWIN TOWERS</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -12463,7 +12463,7 @@
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化一路二段、寶林路口</t>
+          <t>新北市林口區文化三路及仁愛二路口</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>大新青慕</t>
+          <t>和洲艾美</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -12511,7 +12511,7 @@
       <c r="F259" s="2" t="inlineStr"/>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區中華路、文化二路二段口</t>
+          <t>新北市林口區文化一路二段、寶林路口</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>宏樸 曉霧</t>
+          <t>大新青慕</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -12559,7 +12559,7 @@
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區八德路500巷、惠民街30巷口</t>
+          <t>新北市林口區中華路、文化二路二段口</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>宏樸日心說</t>
+          <t>宏樸 曉霧</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -12607,12 +12607,12 @@
       <c r="F261" s="2" t="inlineStr"/>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區民享路與中北三街口</t>
+          <t>新北市林口區八德路500巷、惠民街30巷口</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I261" s="2" t="inlineStr">
@@ -12644,20 +12644,28 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>家悦美</t>
-        </is>
-      </c>
-      <c r="E262" s="2" t="inlineStr"/>
+          <t>宏樸日心說</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F262" s="2" t="inlineStr"/>
-      <c r="G262" s="2" t="inlineStr"/>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區民享路與中北三街口</t>
+        </is>
+      </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J262" s="2" t="inlineStr">
@@ -12684,20 +12692,12 @@
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>家睦中山</t>
-        </is>
-      </c>
-      <c r="E263" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>家悦美</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr"/>
       <c r="F263" s="2" t="inlineStr"/>
-      <c r="G263" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區中山路151號旁</t>
-        </is>
-      </c>
+      <c r="G263" s="2" t="inlineStr"/>
       <c r="H263" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J263" s="2" t="inlineStr">
@@ -12732,7 +12732,7 @@
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>富創得AI新創園區</t>
+          <t>家睦中山</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -12743,7 +12743,7 @@
       <c r="F264" s="2" t="inlineStr"/>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區工四路20號</t>
+          <t>新北市林口區中山路151號旁</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>富堡晶鑄</t>
+          <t>富創得AI新創園區</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       <c r="F265" s="2" t="inlineStr"/>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段39巷及三民路</t>
+          <t>新北市林口區工四路20號</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -12828,12 +12828,20 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>富浤一響</t>
-        </is>
-      </c>
-      <c r="E266" s="2" t="inlineStr"/>
+          <t>富堡晶鑄</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F266" s="2" t="inlineStr"/>
-      <c r="G266" s="2" t="inlineStr"/>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區文化三路一段39巷及三民路</t>
+        </is>
+      </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -12841,7 +12849,7 @@
       </c>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J266" s="2" t="inlineStr">
@@ -12868,28 +12876,20 @@
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>寬隱</t>
-        </is>
-      </c>
-      <c r="E267" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>富浤一響</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr"/>
       <c r="F267" s="2" t="inlineStr"/>
-      <c r="G267" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區東明二街98號</t>
-        </is>
-      </c>
+      <c r="G267" s="2" t="inlineStr"/>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J267" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>小.學堂</t>
+          <t>寬隱</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -12927,12 +12927,12 @@
       <c r="F268" s="2" t="inlineStr"/>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區力行段 499 地號</t>
+          <t>新北市林口區東明二街98號</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>山侘一生</t>
+          <t>小.學堂</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -12975,7 +12975,7 @@
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區建林段645地號</t>
+          <t>新北市林口區力行段 499 地號</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>新潤世界都心</t>
+          <t>山侘一生</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -13023,7 +13023,7 @@
       <c r="F270" s="2" t="inlineStr"/>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段168號旁</t>
+          <t>新北市林口區建林段645地號</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13060,18 +13060,18 @@
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>易捷聿白</t>
+          <t>新潤世界都心</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr"/>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區惠民街30巷25號旁</t>
+          <t>新北市林口區文化三路二段168號旁</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>春木日輝</t>
+          <t>易捷聿白</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -13119,7 +13119,7 @@
       <c r="F272" s="2" t="inlineStr"/>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區民富街</t>
+          <t>新北市林口區惠民街30巷25號旁</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13156,23 +13156,23 @@
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>森聯摩天41</t>
+          <t>春木日輝</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr"/>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段69號</t>
+          <t>新北市林口區民富街</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>森鉅M-林境</t>
+          <t>森聯摩天41</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -13215,12 +13215,12 @@
       <c r="F274" s="2" t="inlineStr"/>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區麗林段 512 地號</t>
+          <t>新北市林口區文化三路一段69號</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
@@ -13252,16 +13252,20 @@
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>森鉅M-逸境</t>
+          <t>森鉅M-林境</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr"/>
-      <c r="G275" s="2" t="inlineStr"/>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區麗林段 512 地號</t>
+        </is>
+      </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13269,7 +13273,7 @@
       </c>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J275" s="2" t="inlineStr">
@@ -13296,20 +13300,16 @@
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>源峰上境</t>
+          <t>森鉅M-逸境</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr"/>
-      <c r="G276" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區松柏路80號</t>
-        </is>
-      </c>
+      <c r="G276" s="2" t="inlineStr"/>
       <c r="H276" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13317,7 +13317,7 @@
       </c>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J276" s="2" t="inlineStr">
@@ -13344,18 +13344,18 @@
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>潤鴻日麗</t>
+          <t>源峰上境</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F277" s="2" t="inlineStr"/>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段及信義路交叉口</t>
+          <t>新北市林口區松柏路80號</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -13392,18 +13392,18 @@
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>瑞德豐錦</t>
+          <t>潤鴻日麗</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區竹林路309巷</t>
+          <t>新北市林口區文化二路二段及信義路交叉口</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>璽來登帝璽</t>
+          <t>瑞德豐錦</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -13451,7 +13451,7 @@
       <c r="F279" s="2" t="inlineStr"/>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區三民路、八德路口</t>
+          <t>新北市林口區竹林路309巷</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>盛德誠</t>
+          <t>璽來登帝璽</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -13499,7 +13499,7 @@
       <c r="F280" s="2" t="inlineStr"/>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區南勢四街、過崙街口</t>
+          <t>新北市林口區三民路、八德路口</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -13536,12 +13536,20 @@
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>福樺中央大樓</t>
-        </is>
-      </c>
-      <c r="E281" s="2" t="inlineStr"/>
+          <t>盛德誠</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F281" s="2" t="inlineStr"/>
-      <c r="G281" s="2" t="inlineStr"/>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區南勢四街、過崙街口</t>
+        </is>
+      </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13549,7 +13557,7 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
@@ -13576,14 +13584,10 @@
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>福樺富貴中山</t>
-        </is>
-      </c>
-      <c r="E282" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>福樺中央大樓</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr"/>
       <c r="F282" s="2" t="inlineStr"/>
       <c r="G282" s="2" t="inlineStr"/>
       <c r="H282" s="2" t="inlineStr">
@@ -13620,20 +13624,16 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>福樺富貴莊園</t>
+          <t>福樺富貴中山</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr"/>
-      <c r="G283" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區文化二路一段</t>
-        </is>
-      </c>
+      <c r="G283" s="2" t="inlineStr"/>
       <c r="H283" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13641,7 +13641,7 @@
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>立軒天蒔</t>
+          <t>福樺富貴莊園</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -13679,7 +13679,7 @@
       <c r="F284" s="2" t="inlineStr"/>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化二路二段與吉祥路交叉口</t>
+          <t>新北市林口區文化二路一段</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -13716,12 +13716,20 @@
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>立陽頤興</t>
-        </is>
-      </c>
-      <c r="E285" s="2" t="inlineStr"/>
+          <t>立軒天蒔</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F285" s="2" t="inlineStr"/>
-      <c r="G285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區文化二路二段與吉祥路交叉口</t>
+        </is>
+      </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13729,7 +13737,7 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
@@ -13756,20 +13764,12 @@
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>竹城.日和</t>
-        </is>
-      </c>
-      <c r="E286" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>立陽頤興</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr"/>
       <c r="F286" s="2" t="inlineStr"/>
-      <c r="G286" s="2" t="inlineStr">
-        <is>
-          <t>新北市林口區建林段1261地號</t>
-        </is>
-      </c>
+      <c r="G286" s="2" t="inlineStr"/>
       <c r="H286" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -13777,7 +13777,7 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>築禾琢玥</t>
+          <t>竹城.日和</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -13815,7 +13815,7 @@
       <c r="F287" s="2" t="inlineStr"/>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區南勢三街</t>
+          <t>新北市林口區建林段1261地號</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -13852,18 +13852,18 @@
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>群和 FUTURE LINK</t>
+          <t>築禾琢玥</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F288" s="2" t="inlineStr"/>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區力行段11地號</t>
+          <t>新北市林口區南勢三街</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -13900,23 +13900,23 @@
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>翫美A9</t>
+          <t>群和 FUTURE LINK</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr"/>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段39巷</t>
+          <t>新北市林口區力行段11地號</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr">
@@ -13948,23 +13948,23 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>聯虹珺玥</t>
+          <t>翫美A9</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr"/>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區竹林一路.</t>
+          <t>新北市林口區文化三路一段39巷</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr">
@@ -13996,18 +13996,18 @@
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>聿翔沐風</t>
+          <t>聯虹珺玥</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr"/>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路、民族路口</t>
+          <t>新北市林口區竹林一路.</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -14044,18 +14044,18 @@
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>聿見美璟</t>
+          <t>聿翔沐風</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr"/>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區忠孝路604巷</t>
+          <t>新北市林口區忠孝路、民族路口</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
@@ -14092,18 +14092,18 @@
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>謙旭</t>
+          <t>聿見美璟</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr"/>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區仁愛路一段</t>
+          <t>新北市林口區忠孝路604巷</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>證源富匠</t>
+          <t>謙旭</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -14151,12 +14151,12 @@
       <c r="F294" s="2" t="inlineStr"/>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區林口路</t>
+          <t>新北市林口區仁愛路一段</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr">
@@ -14188,23 +14188,23 @@
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>證源富承</t>
+          <t>證源富匠</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr"/>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區林口路158號對面</t>
+          <t>新北市林口區林口路</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>長耀 IPARK</t>
+          <t>證源富承</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -14247,7 +14247,7 @@
       <c r="F296" s="2" t="inlineStr"/>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段617巷及民族路交叉口</t>
+          <t>新北市林口區林口路158號對面</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14284,23 +14284,23 @@
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>長耀中山路案</t>
+          <t>長耀 IPARK</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F297" s="2" t="inlineStr"/>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段與中山路口交叉口</t>
+          <t>新北市林口區文化三路一段617巷及民族路交叉口</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
@@ -14332,23 +14332,23 @@
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>長耀加</t>
+          <t>長耀中山路案</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr"/>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路一段555巷</t>
+          <t>新北市林口區文化三路二段與中山路口交叉口</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>長耀里</t>
+          <t>長耀加</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -14391,7 +14391,7 @@
       <c r="F299" s="2" t="inlineStr"/>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區力行段137地號</t>
+          <t>新北市林口區文化三路一段555巷</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -14428,18 +14428,18 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>長虹天聚</t>
+          <t>長耀里</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F300" s="2" t="inlineStr"/>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區中山路與民權路交叉口</t>
+          <t>新北市林口區力行段137地號</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -14476,18 +14476,18 @@
       </c>
       <c r="D301" s="2" t="inlineStr">
         <is>
-          <t>頤昌松玥</t>
+          <t>長虹天聚</t>
         </is>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr"/>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>新北市林口區文化三路二段211巷</t>
+          <t>新北市林口區中山路與民權路交叉口</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -14514,22 +14514,30 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>板橋雙和線</t>
+          <t>新莊林口線</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>中和區</t>
+          <t>林口區</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
         <is>
-          <t>偉鉅中山双匯</t>
-        </is>
-      </c>
-      <c r="E302" s="2" t="inlineStr"/>
+          <t>頤昌松玥</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F302" s="2" t="inlineStr"/>
-      <c r="G302" s="2" t="inlineStr"/>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>新北市林口區文化三路二段211巷</t>
+        </is>
+      </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -14537,12 +14545,12 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -14564,14 +14572,10 @@
       </c>
       <c r="D303" s="2" t="inlineStr">
         <is>
-          <t>偉鉅雙捷韻</t>
-        </is>
-      </c>
-      <c r="E303" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>偉鉅中山双匯</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr"/>
       <c r="F303" s="2" t="inlineStr"/>
       <c r="G303" s="2" t="inlineStr"/>
       <c r="H303" s="2" t="inlineStr">
@@ -14586,7 +14590,7 @@
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -14608,20 +14612,16 @@
       </c>
       <c r="D304" s="2" t="inlineStr">
         <is>
-          <t>双捷橙品</t>
+          <t>偉鉅雙捷韻</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F304" s="2" t="inlineStr"/>
-      <c r="G304" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景平路723號旁</t>
-        </is>
-      </c>
+      <c r="G304" s="2" t="inlineStr"/>
       <c r="H304" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -14629,12 +14629,12 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -14656,23 +14656,23 @@
       </c>
       <c r="D305" s="2" t="inlineStr">
         <is>
-          <t>君奕華品</t>
+          <t>双捷橙品</t>
         </is>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr"/>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景新街57巷11號</t>
+          <t>新北市中和區景平路723號旁</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
@@ -14704,23 +14704,23 @@
       </c>
       <c r="D306" s="2" t="inlineStr">
         <is>
-          <t>和典永峰</t>
+          <t>君奕華品</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr"/>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區立人街14巷77號</t>
+          <t>新北市中和區景新街57巷11號</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
@@ -14752,18 +14752,18 @@
       </c>
       <c r="D307" s="2" t="inlineStr">
         <is>
-          <t>和御</t>
+          <t>和典永峰</t>
         </is>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr"/>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路與新生街口</t>
+          <t>新北市中和區立人街14巷77號</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -14800,7 +14800,7 @@
       </c>
       <c r="D308" s="2" t="inlineStr">
         <is>
-          <t>和雅琚</t>
+          <t>和御</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -14811,7 +14811,7 @@
       <c r="F308" s="2" t="inlineStr"/>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區福祥路85巷口</t>
+          <t>新北市中和區連城路與新生街口</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="D309" s="2" t="inlineStr">
         <is>
-          <t>大同新紀元</t>
+          <t>和雅琚</t>
         </is>
       </c>
       <c r="E309" s="2" t="inlineStr">
@@ -14859,7 +14859,7 @@
       <c r="F309" s="2" t="inlineStr"/>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路、錦和路口</t>
+          <t>新北市中和區福祥路85巷口</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -14896,18 +14896,18 @@
       </c>
       <c r="D310" s="2" t="inlineStr">
         <is>
-          <t>好植</t>
+          <t>大同新紀元</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr"/>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區景新街2號</t>
+          <t>新北市中和區連城路、錦和路口</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -14944,7 +14944,7 @@
       </c>
       <c r="D311" s="2" t="inlineStr">
         <is>
-          <t>宜安三六</t>
+          <t>好植</t>
         </is>
       </c>
       <c r="E311" s="2" t="inlineStr">
@@ -14955,12 +14955,12 @@
       <c r="F311" s="2" t="inlineStr"/>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區保健路72號</t>
+          <t>新北市中和區景新街2號</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr">
@@ -14992,25 +14992,33 @@
       </c>
       <c r="D312" s="2" t="inlineStr">
         <is>
-          <t>寶亞世界公舘</t>
-        </is>
-      </c>
-      <c r="E312" s="2" t="inlineStr"/>
+          <t>宜安三六</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F312" s="2" t="inlineStr"/>
-      <c r="G312" s="2" t="inlineStr"/>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區保健路72號</t>
+        </is>
+      </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -15032,14 +15040,10 @@
       </c>
       <c r="D313" s="2" t="inlineStr">
         <is>
-          <t>將捷Ai PARK</t>
-        </is>
-      </c>
-      <c r="E313" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>寶亞世界公舘</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr"/>
       <c r="F313" s="2" t="inlineStr"/>
       <c r="G313" s="2" t="inlineStr"/>
       <c r="H313" s="2" t="inlineStr">
@@ -15054,7 +15058,7 @@
       </c>
       <c r="J313" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -15076,28 +15080,24 @@
       </c>
       <c r="D314" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠A基地</t>
+          <t>將捷Ai PARK</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr"/>
-      <c r="G314" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區環河西路三段、永和路</t>
-        </is>
-      </c>
+      <c r="G314" s="2" t="inlineStr"/>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J314" s="2" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="D315" s="2" t="inlineStr">
         <is>
-          <t>左岸明珠B基地</t>
+          <t>左岸明珠A基地</t>
         </is>
       </c>
       <c r="E315" s="2" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I315" s="2" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="D316" s="2" t="inlineStr">
         <is>
-          <t>忻揚馥群</t>
+          <t>左岸明珠B基地</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -15183,12 +15183,12 @@
       <c r="F316" s="2" t="inlineStr"/>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區南山路247號</t>
+          <t>新北市中和區環河西路三段、永和路</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr">
@@ -15220,29 +15220,33 @@
       </c>
       <c r="D317" s="2" t="inlineStr">
         <is>
-          <t>昇陽國旭</t>
+          <t>忻揚馥群</t>
         </is>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr"/>
-      <c r="G317" s="2" t="inlineStr"/>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區南山路247號</t>
+        </is>
+      </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J317" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -15264,33 +15268,29 @@
       </c>
       <c r="D318" s="2" t="inlineStr">
         <is>
-          <t>景安旭</t>
+          <t>昇陽國旭</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr"/>
-      <c r="G318" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景新街112號</t>
-        </is>
-      </c>
+      <c r="G318" s="2" t="inlineStr"/>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J318" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -15312,20 +15312,28 @@
       </c>
       <c r="D319" s="2" t="inlineStr">
         <is>
-          <t>東瑩玥光-涵光區</t>
-        </is>
-      </c>
-      <c r="E319" s="2" t="inlineStr"/>
+          <t>景安旭</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F319" s="2" t="inlineStr"/>
-      <c r="G319" s="2" t="inlineStr"/>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區景新街112號</t>
+        </is>
+      </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I319" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J319" s="2" t="inlineStr">
@@ -15352,7 +15360,7 @@
       </c>
       <c r="D320" s="2" t="inlineStr">
         <is>
-          <t>欽禾</t>
+          <t>東瑩玥光-涵光區</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr"/>
@@ -15392,7 +15400,7 @@
       </c>
       <c r="D321" s="2" t="inlineStr">
         <is>
-          <t>永邦恒美</t>
+          <t>欽禾</t>
         </is>
       </c>
       <c r="E321" s="2" t="inlineStr"/>
@@ -15432,14 +15440,10 @@
       </c>
       <c r="D322" s="2" t="inlineStr">
         <is>
-          <t>漢寶捷運學府No.5</t>
-        </is>
-      </c>
-      <c r="E322" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>永邦恒美</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr"/>
       <c r="F322" s="2" t="inlineStr"/>
       <c r="G322" s="2" t="inlineStr"/>
       <c r="H322" s="2" t="inlineStr">
@@ -15476,28 +15480,24 @@
       </c>
       <c r="D323" s="2" t="inlineStr">
         <is>
-          <t>漢皇方圓</t>
+          <t>漢寶捷運學府No.5</t>
         </is>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F323" s="2" t="inlineStr"/>
-      <c r="G323" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區中和路410號</t>
-        </is>
-      </c>
+      <c r="G323" s="2" t="inlineStr"/>
       <c r="H323" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J323" s="2" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="D324" s="2" t="inlineStr">
         <is>
-          <t>綻賞</t>
+          <t>漢皇方圓</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -15535,12 +15535,12 @@
       <c r="F324" s="2" t="inlineStr"/>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連城路309號</t>
+          <t>新北市中和區中和路410號</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I324" s="2" t="inlineStr">
@@ -15572,16 +15572,20 @@
       </c>
       <c r="D325" s="2" t="inlineStr">
         <is>
-          <t>蒲楊雙和</t>
+          <t>綻賞</t>
         </is>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr"/>
-      <c r="G325" s="2" t="inlineStr"/>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連城路309號</t>
+        </is>
+      </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15589,7 +15593,7 @@
       </c>
       <c r="I325" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J325" s="2" t="inlineStr">
@@ -15616,28 +15620,24 @@
       </c>
       <c r="D326" s="2" t="inlineStr">
         <is>
-          <t>藏富HOUSE</t>
+          <t>蒲楊雙和</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr"/>
-      <c r="G326" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區景平路159巷</t>
-        </is>
-      </c>
+      <c r="G326" s="2" t="inlineStr"/>
       <c r="H326" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J326" s="2" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="D327" s="2" t="inlineStr">
         <is>
-          <t>虹爵琢悅</t>
+          <t>藏富HOUSE</t>
         </is>
       </c>
       <c r="E327" s="2" t="inlineStr">
@@ -15675,12 +15675,12 @@
       <c r="F327" s="2" t="inlineStr"/>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>新北市中和區連勝街26巷8號</t>
+          <t>新北市中和區景平路159巷</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I327" s="2" t="inlineStr">
@@ -15712,16 +15712,20 @@
       </c>
       <c r="D328" s="2" t="inlineStr">
         <is>
-          <t>遠雄CASA 凱莎莊園</t>
+          <t>虹爵琢悅</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr"/>
-      <c r="G328" s="2" t="inlineStr"/>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>新北市中和區連勝街26巷8號</t>
+        </is>
+      </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15729,7 +15733,7 @@
       </c>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J328" s="2" t="inlineStr">
@@ -15756,20 +15760,16 @@
       </c>
       <c r="D329" s="2" t="inlineStr">
         <is>
-          <t>金玖民有琚</t>
+          <t>遠雄CASA 凱莎莊園</t>
         </is>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr"/>
-      <c r="G329" s="2" t="inlineStr">
-        <is>
-          <t>新北市中和區民有街49號</t>
-        </is>
-      </c>
+      <c r="G329" s="2" t="inlineStr"/>
       <c r="H329" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="I329" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J329" s="2" t="inlineStr">
@@ -15799,23 +15799,23 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>板橋區</t>
+          <t>中和區</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
         <is>
-          <t>HELLO WIN迎家</t>
+          <t>金玖民有琚</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr"/>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街22巷2號</t>
+          <t>新北市中和區民有街49號</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
@@ -15852,16 +15852,20 @@
       </c>
       <c r="D331" s="2" t="inlineStr">
         <is>
-          <t>三輝白昀</t>
+          <t>HELLO WIN迎家</t>
         </is>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr"/>
-      <c r="G331" s="2" t="inlineStr"/>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松柏街22巷2號</t>
+        </is>
+      </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15869,7 +15873,7 @@
       </c>
       <c r="I331" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J331" s="2" t="inlineStr">
@@ -15896,20 +15900,16 @@
       </c>
       <c r="D332" s="2" t="inlineStr">
         <is>
-          <t>上上寀</t>
+          <t>三輝白昀</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr"/>
-      <c r="G332" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江三路、華江二路口</t>
-        </is>
-      </c>
+      <c r="G332" s="2" t="inlineStr"/>
       <c r="H332" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -15917,7 +15917,7 @@
       </c>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J332" s="2" t="inlineStr">
@@ -15944,18 +15944,18 @@
       </c>
       <c r="D333" s="2" t="inlineStr">
         <is>
-          <t>京東賞</t>
+          <t>上上寀</t>
         </is>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr"/>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中山路二段521號</t>
+          <t>新北市板橋區華江三路、華江二路口</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
@@ -15992,23 +15992,23 @@
       </c>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>協和新中興</t>
+          <t>京東賞</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr"/>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區金門街287巷</t>
+          <t>新北市板橋區中山路二段521號</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I334" s="2" t="inlineStr">
@@ -16040,18 +16040,18 @@
       </c>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>和岩誼居</t>
+          <t>協和新中興</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr"/>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區存德街15號</t>
+          <t>新北市板橋區金門街287巷</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
@@ -16088,24 +16088,28 @@
       </c>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>城德華福</t>
+          <t>和岩誼居</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr"/>
-      <c r="G336" s="2" t="inlineStr"/>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區存德街15號</t>
+        </is>
+      </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I336" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J336" s="2" t="inlineStr">
@@ -16132,20 +16136,16 @@
       </c>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>大業</t>
+          <t>城德華福</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F337" s="2" t="inlineStr"/>
-      <c r="G337" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區華江一路</t>
-        </is>
-      </c>
+      <c r="G337" s="2" t="inlineStr"/>
       <c r="H337" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="I337" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J337" s="2" t="inlineStr">
@@ -16180,12 +16180,20 @@
       </c>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>寶格利</t>
-        </is>
-      </c>
-      <c r="E338" s="2" t="inlineStr"/>
+          <t>大業</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F338" s="2" t="inlineStr"/>
-      <c r="G338" s="2" t="inlineStr"/>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區華江一路</t>
+        </is>
+      </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -16193,12 +16201,12 @@
       </c>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J338" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -16220,33 +16228,25 @@
       </c>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>心晴好</t>
-        </is>
-      </c>
-      <c r="E339" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>寶格利</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr"/>
       <c r="F339" s="2" t="inlineStr"/>
-      <c r="G339" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區縣民大道一段</t>
-        </is>
-      </c>
+      <c r="G339" s="2" t="inlineStr"/>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J339" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>悠森學</t>
+          <t>心晴好</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -16279,12 +16279,12 @@
       <c r="F340" s="2" t="inlineStr"/>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路325巷41號</t>
+          <t>新北市板橋區縣民大道一段</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I340" s="2" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>文化風華</t>
+          <t>悠森學</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
@@ -16327,12 +16327,12 @@
       <c r="F341" s="2" t="inlineStr"/>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段與華江一路口</t>
+          <t>新北市板橋區中正路325巷41號</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I341" s="2" t="inlineStr">
@@ -16364,24 +16364,28 @@
       </c>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>新板東京</t>
+          <t>文化風華</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr"/>
-      <c r="G342" s="2" t="inlineStr"/>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區文化路二段與華江一路口</t>
+        </is>
+      </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I342" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J342" s="2" t="inlineStr">
@@ -16408,20 +16412,16 @@
       </c>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>新潤世界城</t>
+          <t>新板東京</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr"/>
-      <c r="G343" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區南雅東路</t>
-        </is>
-      </c>
+      <c r="G343" s="2" t="inlineStr"/>
       <c r="H343" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -16429,7 +16429,7 @@
       </c>
       <c r="I343" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J343" s="2" t="inlineStr">
@@ -16456,7 +16456,7 @@
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>新濠一閱</t>
+          <t>新潤世界城</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -16467,7 +16467,7 @@
       <c r="F344" s="2" t="inlineStr"/>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與文新路交叉口</t>
+          <t>新北市板橋區南雅東路</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -16504,18 +16504,18 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>日安PARK</t>
+          <t>新濠一閱</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr"/>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、香社一路、香社二路</t>
+          <t>新北市板橋區環河西路四段與文新路交叉口</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -16552,23 +16552,23 @@
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>日安TOKYO</t>
+          <t>日安PARK</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr"/>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區藝文街、藝文二街、板城路</t>
+          <t>新北市板橋區藝文街、香社一路、香社二路</t>
         </is>
       </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I346" s="2" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>晶合豐川</t>
+          <t>日安TOKYO</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
@@ -16611,7 +16611,7 @@
       <c r="F347" s="2" t="inlineStr"/>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區長安街168巷10弄</t>
+          <t>新北市板橋區藝文街、藝文二街、板城路</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
@@ -16648,18 +16648,18 @@
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>松柏大院</t>
+          <t>晶合豐川</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr"/>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松柏街</t>
+          <t>新北市板橋區長安街168巷10弄</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
@@ -16696,18 +16696,18 @@
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>板橋璞園的家</t>
+          <t>松柏大院</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F349" s="2" t="inlineStr"/>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區田單北街61號</t>
+          <t>新北市板橋區松柏街</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>歐英萬</t>
+          <t>板橋璞園的家</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -16755,7 +16755,7 @@
       <c r="F350" s="2" t="inlineStr"/>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區三民路二段72號</t>
+          <t>新北市板橋區田單北街61號</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -16792,18 +16792,18 @@
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>永康真</t>
+          <t>歐英萬</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F351" s="2" t="inlineStr"/>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大華街72號旁</t>
+          <t>新北市板橋區三民路二段72號</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
@@ -16840,24 +16840,28 @@
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>永雄府中心</t>
+          <t>永康真</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr"/>
-      <c r="G352" s="2" t="inlineStr"/>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區大華街72號旁</t>
+        </is>
+      </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I352" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J352" s="2" t="inlineStr">
@@ -16884,7 +16888,7 @@
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>江翠Park</t>
+          <t>永雄府中心</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -16928,28 +16932,24 @@
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景1號</t>
+          <t>江翠Park</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F354" s="2" t="inlineStr"/>
-      <c r="G354" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段、 華江三路</t>
-        </is>
-      </c>
+      <c r="G354" s="2" t="inlineStr"/>
       <c r="H354" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I354" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J354" s="2" t="inlineStr">
@@ -16976,18 +16976,18 @@
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景2號</t>
+          <t>甲山林帝景1號</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F355" s="2" t="inlineStr"/>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、大漢街</t>
+          <t>新北市板橋區環河西路四段、 華江三路</t>
         </is>
       </c>
       <c r="H355" s="2" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景6號</t>
+          <t>甲山林帝景2號</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       <c r="F356" s="2" t="inlineStr"/>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
+          <t>新北市板橋區環河西路四段、大漢街</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
@@ -17072,7 +17072,7 @@
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>甲山林帝景7號</t>
+          <t>甲山林帝景6號</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -17083,7 +17083,7 @@
       <c r="F357" s="2" t="inlineStr"/>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段及華江三路口</t>
+          <t>新北市板橋區華江一路、華江三路 (123木頭公園旁)</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
@@ -17120,23 +17120,23 @@
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>甲山林濱河帝景</t>
+          <t>甲山林帝景7號</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr"/>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
+          <t>新北市板橋區文化路二段及華江三路口</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I358" s="2" t="inlineStr">
@@ -17168,23 +17168,23 @@
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>祥泓湛</t>
+          <t>甲山林濱河帝景</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr"/>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區大觀路三段62巷3號</t>
+          <t>新北市板橋區環河西路四段與萬板路交叉口</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I359" s="2" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>立信天朗</t>
+          <t>祥泓湛</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -17227,7 +17227,7 @@
       <c r="F360" s="2" t="inlineStr"/>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區新月一街與中正路交叉口</t>
+          <t>新北市板橋區大觀路三段62巷3號</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
@@ -17264,20 +17264,28 @@
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>立信帝國花園廣場</t>
-        </is>
-      </c>
-      <c r="E361" s="2" t="inlineStr"/>
+          <t>立信天朗</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F361" s="2" t="inlineStr"/>
-      <c r="G361" s="2" t="inlineStr"/>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區新月一街與中正路交叉口</t>
+        </is>
+      </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I361" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J361" s="2" t="inlineStr">
@@ -17304,28 +17312,20 @@
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>立信御景</t>
-        </is>
-      </c>
-      <c r="E362" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>立信帝國花園廣場</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr"/>
       <c r="F362" s="2" t="inlineStr"/>
-      <c r="G362" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區環河西路四段(新都段)</t>
-        </is>
-      </c>
+      <c r="G362" s="2" t="inlineStr"/>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J362" s="2" t="inlineStr">
@@ -17352,7 +17352,7 @@
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>立信晴朗</t>
+          <t>立信御景</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -17363,12 +17363,12 @@
       <c r="F363" s="2" t="inlineStr"/>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區中正路與新月三街口</t>
+          <t>新北市板橋區環河西路四段(新都段)</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I363" s="2" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>立信雙星</t>
+          <t>立信晴朗</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -17411,7 +17411,7 @@
       <c r="F364" s="2" t="inlineStr"/>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江一路600號對面</t>
+          <t>新北市板橋區中正路與新月三街口</t>
         </is>
       </c>
       <c r="H364" s="2" t="inlineStr">
@@ -17448,18 +17448,18 @@
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>立信首馥</t>
+          <t>立信雙星</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr"/>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區華江三路、華江六路交叉口</t>
+          <t>新北市板橋區華江一路600號對面</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
@@ -17496,18 +17496,18 @@
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>統創曜</t>
+          <t>立信首馥</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F366" s="2" t="inlineStr"/>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
+          <t>新北市板橋區華江三路、華江六路交叉口</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>耑芃</t>
+          <t>統創曜</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -17555,12 +17555,12 @@
       <c r="F367" s="2" t="inlineStr"/>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區南雅南路二段68號</t>
+          <t>新北市板橋區環河西路四段、長江路一段105巷口</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I367" s="2" t="inlineStr">
@@ -17592,23 +17592,23 @@
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>芯哲園</t>
+          <t>耑芃</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr"/>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
+          <t>新北市板橋區南雅南路二段68號</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I368" s="2" t="inlineStr">
@@ -17640,23 +17640,23 @@
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>達永冬慶</t>
+          <t>芯哲園</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr"/>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區文化路二段65號</t>
+          <t>新北市板橋區重慶路346巷與和平路交叉口</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I369" s="2" t="inlineStr">
@@ -17688,24 +17688,28 @@
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>遠揚之森A⁺</t>
+          <t>達永冬慶</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr"/>
-      <c r="G370" s="2" t="inlineStr"/>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區文化路二段65號</t>
+        </is>
+      </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I370" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J370" s="2" t="inlineStr">
@@ -17732,28 +17736,24 @@
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>遠雄信義段案</t>
+          <t>遠揚之森A⁺</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr"/>
-      <c r="G371" s="2" t="inlineStr">
-        <is>
-          <t>新北市板橋區信義段217地號</t>
-        </is>
-      </c>
+      <c r="G371" s="2" t="inlineStr"/>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J371" s="2" t="inlineStr">
@@ -17780,7 +17780,7 @@
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>鑄見</t>
+          <t>遠雄信義段案</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -17791,12 +17791,12 @@
       <c r="F372" s="2" t="inlineStr"/>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>新北市板橋區松江街</t>
+          <t>新北市板橋區信義段217地號</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I372" s="2" t="inlineStr">
@@ -17828,12 +17828,20 @@
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>香榭京宴</t>
-        </is>
-      </c>
-      <c r="E373" s="2" t="inlineStr"/>
+          <t>鑄見</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F373" s="2" t="inlineStr"/>
-      <c r="G373" s="2" t="inlineStr"/>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>新北市板橋區松江街</t>
+        </is>
+      </c>
       <c r="H373" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17841,7 +17849,7 @@
       </c>
       <c r="I373" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J373" s="2" t="inlineStr">
@@ -17863,25 +17871,17 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>永和區</t>
+          <t>板橋區</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>M PLUS</t>
-        </is>
-      </c>
-      <c r="E374" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>香榭京宴</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr"/>
       <c r="F374" s="2" t="inlineStr"/>
-      <c r="G374" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區環河東路一段152號</t>
-        </is>
-      </c>
+      <c r="G374" s="2" t="inlineStr"/>
       <c r="H374" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="I374" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J374" s="2" t="inlineStr">
@@ -17916,12 +17916,20 @@
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>友座豐禾</t>
-        </is>
-      </c>
-      <c r="E375" s="2" t="inlineStr"/>
+          <t>M PLUS</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F375" s="2" t="inlineStr"/>
-      <c r="G375" s="2" t="inlineStr"/>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區環河東路一段152號</t>
+        </is>
+      </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17929,7 +17937,7 @@
       </c>
       <c r="I375" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J375" s="2" t="inlineStr">
@@ -17956,20 +17964,12 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>家格綻綻</t>
-        </is>
-      </c>
-      <c r="E376" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>友座豐禾</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr"/>
       <c r="F376" s="2" t="inlineStr"/>
-      <c r="G376" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區中正路607號</t>
-        </is>
-      </c>
+      <c r="G376" s="2" t="inlineStr"/>
       <c r="H376" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -17977,7 +17977,7 @@
       </c>
       <c r="I376" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J376" s="2" t="inlineStr">
@@ -18004,23 +18004,23 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>敦南宴</t>
+          <t>家格綻綻</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr"/>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區永利路216巷</t>
+          <t>新北市永和區中正路607號</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I377" s="2" t="inlineStr">
@@ -18052,7 +18052,7 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>新碩永傳</t>
+          <t>敦南宴</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -18063,12 +18063,12 @@
       <c r="F378" s="2" t="inlineStr"/>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中正路388號旁</t>
+          <t>新北市永和區永利路216巷</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I378" s="2" t="inlineStr">
@@ -18100,7 +18100,7 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>漢寶臺大苑</t>
+          <t>新碩永傳</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -18111,12 +18111,12 @@
       <c r="F379" s="2" t="inlineStr"/>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區成功路一段132號</t>
+          <t>新北市永和區中正路388號旁</t>
         </is>
       </c>
       <c r="H379" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I379" s="2" t="inlineStr">
@@ -18148,20 +18148,28 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>漢皇River Sky</t>
-        </is>
-      </c>
-      <c r="E380" s="2" t="inlineStr"/>
+          <t>漢寶臺大苑</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F380" s="2" t="inlineStr"/>
-      <c r="G380" s="2" t="inlineStr"/>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區成功路一段132號</t>
+        </is>
+      </c>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I380" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J380" s="2" t="inlineStr">
@@ -18188,28 +18196,20 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>蒲陽建設復興街案(尚未取得建照)</t>
-        </is>
-      </c>
-      <c r="E381" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>漢皇River Sky</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr"/>
       <c r="F381" s="2" t="inlineStr"/>
-      <c r="G381" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區復興街</t>
-        </is>
-      </c>
+      <c r="G381" s="2" t="inlineStr"/>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I381" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J381" s="2" t="inlineStr">
@@ -18236,7 +18236,7 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
+          <t>蒲陽建設復興街案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
@@ -18247,12 +18247,12 @@
       <c r="F382" s="2" t="inlineStr"/>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中山路一段28巷口旁</t>
+          <t>新北市永和區復興街</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I382" s="2" t="inlineStr">
@@ -18284,16 +18284,20 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>頂溪捷運站~黃金綠建築,1~2房</t>
+          <t>頂溪大苑</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr"/>
-      <c r="G383" s="2" t="inlineStr"/>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區中山路一段28巷口旁</t>
+        </is>
+      </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18301,7 +18305,7 @@
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr">
@@ -18318,38 +18322,34 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>頂溪捷運站~黃金綠建築,1~2房</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F384" s="2" t="inlineStr"/>
-      <c r="G384" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街</t>
-        </is>
-      </c>
+      <c r="G384" s="2" t="inlineStr"/>
       <c r="H384" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I384" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J384" s="2" t="inlineStr">
@@ -18376,20 +18376,28 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>文心慕慕</t>
-        </is>
-      </c>
-      <c r="E385" s="2" t="inlineStr"/>
+          <t>富都康莊</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F385" s="2" t="inlineStr"/>
-      <c r="G385" s="2" t="inlineStr"/>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街</t>
+        </is>
+      </c>
       <c r="H385" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J385" s="2" t="inlineStr">
@@ -18416,14 +18424,10 @@
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>東煒大局</t>
-        </is>
-      </c>
-      <c r="E386" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>文心慕慕</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr"/>
       <c r="F386" s="2" t="inlineStr"/>
       <c r="G386" s="2" t="inlineStr"/>
       <c r="H386" s="2" t="inlineStr">
@@ -18460,28 +18464,24 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>汐止華品</t>
+          <t>東煒大局</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr"/>
-      <c r="G387" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區保一街與保一街8巷交叉口</t>
-        </is>
-      </c>
+      <c r="G387" s="2" t="inlineStr"/>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J387" s="2" t="inlineStr">
@@ -18508,23 +18508,23 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>汐科爵鼎</t>
+          <t>汐止華品</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr"/>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區水源路二段190號旁</t>
+          <t>新北市汐止區保一街與保一街8巷交叉口</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I388" s="2" t="inlineStr">
@@ -18556,16 +18556,20 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>美麗山林</t>
+          <t>汐科爵鼎</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr"/>
-      <c r="G389" s="2" t="inlineStr"/>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區水源路二段190號旁</t>
+        </is>
+      </c>
       <c r="H389" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18573,7 +18577,7 @@
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J389" s="2" t="inlineStr">
@@ -18600,28 +18604,24 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>美麗山林-華廈區</t>
+          <t>美麗山林</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr"/>
-      <c r="G390" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區水源路二段125巷</t>
-        </is>
-      </c>
+      <c r="G390" s="2" t="inlineStr"/>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I390" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J390" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>金湖漾</t>
+          <t>美麗山林-華廈區</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
@@ -18659,12 +18659,12 @@
       <c r="F391" s="2" t="inlineStr"/>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區民族二街30巷22號</t>
+          <t>新北市汐止區水源路二段125巷</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I391" s="2" t="inlineStr">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>雄鷹天映湖</t>
+          <t>金湖漾</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
@@ -18707,12 +18707,12 @@
       <c r="F392" s="2" t="inlineStr"/>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區湖東街5巷50號</t>
+          <t>新北市汐止區民族二街30巷22號</t>
         </is>
       </c>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I392" s="2" t="inlineStr">
@@ -18744,24 +18744,28 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>雲禾月</t>
+          <t>雄鷹天映湖</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr"/>
-      <c r="G393" s="2" t="inlineStr"/>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區湖東街5巷50號</t>
+        </is>
+      </c>
       <c r="H393" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I393" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J393" s="2" t="inlineStr">
@@ -18783,12 +18787,12 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>淡水區</t>
+          <t>汐止區</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>京美晴朗</t>
+          <t>雲禾月</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -18832,20 +18836,16 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>兆美萬海</t>
+          <t>京美晴朗</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr"/>
-      <c r="G395" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區望高樓段535、535-1地號</t>
-        </is>
-      </c>
+      <c r="G395" s="2" t="inlineStr"/>
       <c r="H395" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18853,7 +18853,7 @@
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J395" s="2" t="inlineStr">
@@ -18880,12 +18880,20 @@
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>光全御苑</t>
-        </is>
-      </c>
-      <c r="E396" s="2" t="inlineStr"/>
+          <t>兆美萬海</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F396" s="2" t="inlineStr"/>
-      <c r="G396" s="2" t="inlineStr"/>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區望高樓段535、535-1地號</t>
+        </is>
+      </c>
       <c r="H396" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18893,12 +18901,12 @@
       </c>
       <c r="I396" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J396" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -18920,20 +18928,12 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>台北別墅</t>
-        </is>
-      </c>
-      <c r="E397" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>光全御苑</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr"/>
       <c r="F397" s="2" t="inlineStr"/>
-      <c r="G397" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區尚頂一街</t>
-        </is>
-      </c>
+      <c r="G397" s="2" t="inlineStr"/>
       <c r="H397" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18941,12 +18941,12 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J397" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -18968,7 +18968,7 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>合康植芯</t>
+          <t>台北別墅</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -18979,7 +18979,7 @@
       <c r="F398" s="2" t="inlineStr"/>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路三段202巷65弄</t>
+          <t>新北市淡水區尚頂一街</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
@@ -19016,12 +19016,20 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>合謙劃時代</t>
-        </is>
-      </c>
-      <c r="E399" s="2" t="inlineStr"/>
+          <t>合康植芯</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F399" s="2" t="inlineStr"/>
-      <c r="G399" s="2" t="inlineStr"/>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區濱海路三段202巷65弄</t>
+        </is>
+      </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19029,7 +19037,7 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J399" s="2" t="inlineStr">
@@ -19056,20 +19064,12 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>合謙耀時代</t>
-        </is>
-      </c>
-      <c r="E400" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>合謙劃時代</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr"/>
       <c r="F400" s="2" t="inlineStr"/>
-      <c r="G400" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市段185地號</t>
-        </is>
-      </c>
+      <c r="G400" s="2" t="inlineStr"/>
       <c r="H400" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19077,7 +19077,7 @@
       </c>
       <c r="I400" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J400" s="2" t="inlineStr">
@@ -19104,7 +19104,7 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>向陽</t>
+          <t>合謙耀時代</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -19115,7 +19115,7 @@
       <c r="F401" s="2" t="inlineStr"/>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
+          <t>新北市淡水區新市段185地號</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>員邦徊</t>
+          <t>向陽</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -19163,7 +19163,7 @@
       <c r="F402" s="2" t="inlineStr"/>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路72巷</t>
+          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
@@ -19200,23 +19200,23 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>嘉潤家泰氧之森</t>
+          <t>員邦徊</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr"/>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路88號</t>
+          <t>新北市淡水區坪頂路72巷</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I403" s="2" t="inlineStr">
@@ -19248,23 +19248,23 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>富麗ONE</t>
+          <t>嘉潤家泰氧之森</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr"/>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區新市段118地號</t>
+          <t>新北市淡水區坪頂路88號</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I404" s="2" t="inlineStr">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>將捷建設紅樹林案</t>
+          <t>富麗ONE</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -19307,12 +19307,12 @@
       <c r="F405" s="2" t="inlineStr"/>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
+          <t>新北市淡水區新市段118地號</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I405" s="2" t="inlineStr">
@@ -19344,23 +19344,23 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>山河帝寶</t>
+          <t>將捷建設紅樹林案</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr"/>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
+          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I406" s="2" t="inlineStr">
@@ -19392,18 +19392,18 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>新海城</t>
+          <t>山河帝寶</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr"/>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路二段、新市二路</t>
+          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
@@ -19440,16 +19440,20 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>新海城2夢想市</t>
+          <t>新海城</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr"/>
-      <c r="G408" s="2" t="inlineStr"/>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區沙崙路二段、新市二路</t>
+        </is>
+      </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19457,7 +19461,7 @@
       </c>
       <c r="I408" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J408" s="2" t="inlineStr">
@@ -19484,28 +19488,24 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>村泉蒔美</t>
+          <t>新海城2夢想市</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr"/>
-      <c r="G409" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區中正東路二段143巷12弄</t>
-        </is>
-      </c>
+      <c r="G409" s="2" t="inlineStr"/>
       <c r="H409" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I409" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J409" s="2" t="inlineStr">
@@ -19532,7 +19532,7 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>水問山</t>
+          <t>村泉蒔美</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -19543,7 +19543,7 @@
       <c r="F410" s="2" t="inlineStr"/>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段143巷2弄</t>
+          <t>新北市淡水區中正東路二段143巷12弄</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -19580,23 +19580,23 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>水美慕河</t>
+          <t>水問山</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr"/>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路一段47號</t>
+          <t>新北市淡水區中正東路二段143巷2弄</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I411" s="2" t="inlineStr">
@@ -19628,18 +19628,18 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>湯泉紅樹林</t>
+          <t>水美慕河</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr"/>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段5巷35號</t>
+          <t>新北市淡水區中正東路一段47號</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -19676,7 +19676,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>石上青</t>
+          <t>湯泉紅樹林</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
@@ -19687,7 +19687,7 @@
       <c r="F413" s="2" t="inlineStr"/>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區八勢一街36號</t>
+          <t>新北市淡水區中正東路二段5巷35號</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>致茂橋豐</t>
+          <t>石上青</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
@@ -19735,7 +19735,7 @@
       <c r="F414" s="2" t="inlineStr"/>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路一段</t>
+          <t>新北市淡水區八勢一街36號</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -19772,18 +19772,18 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>藝沐汀</t>
+          <t>致茂橋豐</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr"/>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區民族路、自強路305巷</t>
+          <t>新北市淡水區沙崙路一段</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -19820,16 +19820,20 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>馥人灣-新濠門</t>
+          <t>藝沐汀</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F416" s="2" t="inlineStr"/>
-      <c r="G416" s="2" t="inlineStr"/>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區民族路、自強路305巷</t>
+        </is>
+      </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19837,7 +19841,7 @@
       </c>
       <c r="I416" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J416" s="2" t="inlineStr">
@@ -19864,20 +19868,16 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>鴻灃COMO</t>
+          <t>馥人灣-新濠門</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr"/>
-      <c r="G417" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
-        </is>
-      </c>
+      <c r="G417" s="2" t="inlineStr"/>
       <c r="H417" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19885,7 +19885,7 @@
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J417" s="2" t="inlineStr">
@@ -19897,33 +19897,33 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>A20-合磊天沐</t>
+          <t>鴻灃COMO</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr"/>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -19960,16 +19960,20 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>The Nexus 新識界</t>
+          <t>A20-合磊天沐</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr"/>
-      <c r="G419" s="2" t="inlineStr"/>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+        </is>
+      </c>
       <c r="H419" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19977,7 +19981,7 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J419" s="2" t="inlineStr">
@@ -20004,7 +20008,7 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>一品閣</t>
+          <t>The Nexus 新識界</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -20048,20 +20052,16 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>中麗若隱</t>
+          <t>一品閣</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr"/>
-      <c r="G421" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
-        </is>
-      </c>
+      <c r="G421" s="2" t="inlineStr"/>
       <c r="H421" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20069,7 +20069,7 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J421" s="2" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>享JIA</t>
+          <t>中麗若隱</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -20107,7 +20107,7 @@
       <c r="F422" s="2" t="inlineStr"/>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區青山一路157號旁</t>
+          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -20144,18 +20144,18 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>保利首綻</t>
+          <t>享JIA</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr"/>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐路225號對面</t>
+          <t>桃園市中壢區青山一路157號旁</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
@@ -20192,16 +20192,20 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>勤樸悅圓</t>
+          <t>保利首綻</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr"/>
-      <c r="G424" s="2" t="inlineStr"/>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐路225號對面</t>
+        </is>
+      </c>
       <c r="H424" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20209,7 +20213,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr">
@@ -20236,20 +20240,16 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>君臨塘詩-慕荷</t>
+          <t>勤樸悅圓</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr"/>
-      <c r="G425" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
-        </is>
-      </c>
+      <c r="G425" s="2" t="inlineStr"/>
       <c r="H425" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20257,7 +20257,7 @@
       </c>
       <c r="I425" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J425" s="2" t="inlineStr">
@@ -20284,18 +20284,18 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>和發采采</t>
+          <t>君臨塘詩-慕荷</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr"/>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區新生路二段378之2號對面</t>
+          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
         </is>
       </c>
       <c r="H426" s="2" t="inlineStr">
@@ -20332,18 +20332,18 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>品坤學</t>
+          <t>和發采采</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr"/>
       <c r="G427" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區環西路二段25巷11號旁</t>
+          <t>桃園市中壢區新生路二段378之2號對面</t>
         </is>
       </c>
       <c r="H427" s="2" t="inlineStr">
@@ -20380,18 +20380,18 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>大亮FIKA</t>
+          <t>品坤學</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr"/>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區永順一街30號旁</t>
+          <t>桃園市中壢區環西路二段25巷11號旁</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
@@ -20428,12 +20428,20 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>大清上景</t>
-        </is>
-      </c>
-      <c r="E429" s="2" t="inlineStr"/>
+          <t>大亮FIKA</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F429" s="2" t="inlineStr"/>
-      <c r="G429" s="2" t="inlineStr"/>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區永順一街30號旁</t>
+        </is>
+      </c>
       <c r="H429" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20441,7 +20449,7 @@
       </c>
       <c r="I429" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J429" s="2" t="inlineStr">
@@ -20468,20 +20476,12 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>大清星湛-璞樂</t>
-        </is>
-      </c>
-      <c r="E430" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>大清上景</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr"/>
       <c r="F430" s="2" t="inlineStr"/>
-      <c r="G430" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區水青路520號對面</t>
-        </is>
-      </c>
+      <c r="G430" s="2" t="inlineStr"/>
       <c r="H430" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="I430" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J430" s="2" t="inlineStr">
@@ -20516,16 +20516,20 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>大清璞樂</t>
+          <t>大清星湛-璞樂</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr"/>
-      <c r="G431" s="2" t="inlineStr"/>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區水青路520號對面</t>
+        </is>
+      </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20533,7 +20537,7 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J431" s="2" t="inlineStr">
@@ -20560,7 +20564,7 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>大睦I-CITY(A19)</t>
+          <t>大清璞樂</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
@@ -20604,10 +20608,14 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>大睦站前首席</t>
-        </is>
-      </c>
-      <c r="E433" s="2" t="inlineStr"/>
+          <t>大睦I-CITY(A19)</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F433" s="2" t="inlineStr"/>
       <c r="G433" s="2" t="inlineStr"/>
       <c r="H433" s="2" t="inlineStr">
@@ -20644,14 +20652,10 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>大華畔</t>
-        </is>
-      </c>
-      <c r="E434" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>大睦站前首席</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr"/>
       <c r="F434" s="2" t="inlineStr"/>
       <c r="G434" s="2" t="inlineStr"/>
       <c r="H434" s="2" t="inlineStr">
@@ -20688,20 +20692,16 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>威均君藏</t>
+          <t>大華畔</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F435" s="2" t="inlineStr"/>
-      <c r="G435" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
-        </is>
-      </c>
+      <c r="G435" s="2" t="inlineStr"/>
       <c r="H435" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20709,7 +20709,7 @@
       </c>
       <c r="I435" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J435" s="2" t="inlineStr">
@@ -20736,7 +20736,7 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>威均天璽</t>
+          <t>威均君藏</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
@@ -20747,7 +20747,7 @@
       <c r="F436" s="2" t="inlineStr"/>
       <c r="G436" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區領航北路二段、永春路口</t>
+          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
         </is>
       </c>
       <c r="H436" s="2" t="inlineStr">
@@ -20784,12 +20784,20 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>宇惠曦</t>
-        </is>
-      </c>
-      <c r="E437" s="2" t="inlineStr"/>
+          <t>威均天璽</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F437" s="2" t="inlineStr"/>
-      <c r="G437" s="2" t="inlineStr"/>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區領航北路二段、永春路口</t>
+        </is>
+      </c>
       <c r="H437" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20797,7 +20805,7 @@
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J437" s="2" t="inlineStr">
@@ -20824,20 +20832,12 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>宜誠丽左岸</t>
-        </is>
-      </c>
-      <c r="E438" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>宇惠曦</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr"/>
       <c r="F438" s="2" t="inlineStr"/>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區豐興段235地號</t>
-        </is>
-      </c>
+      <c r="G438" s="2" t="inlineStr"/>
       <c r="H438" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr">
@@ -20872,16 +20872,20 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>宜誠泱</t>
+          <t>宜誠丽左岸</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr"/>
-      <c r="G439" s="2" t="inlineStr"/>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區豐興段235地號</t>
+        </is>
+      </c>
       <c r="H439" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20889,7 +20893,7 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J439" s="2" t="inlineStr">
@@ -20916,10 +20920,14 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>宜雄湛</t>
-        </is>
-      </c>
-      <c r="E440" s="2" t="inlineStr"/>
+          <t>宜誠泱</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F440" s="2" t="inlineStr"/>
       <c r="G440" s="2" t="inlineStr"/>
       <c r="H440" s="2" t="inlineStr">
@@ -20956,7 +20964,7 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>宜雄湛</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr"/>
@@ -20996,20 +21004,12 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>寶台天馳</t>
-        </is>
-      </c>
-      <c r="E442" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>家瑞No.2</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr"/>
       <c r="F442" s="2" t="inlineStr"/>
-      <c r="G442" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青溪段450地號</t>
-        </is>
-      </c>
+      <c r="G442" s="2" t="inlineStr"/>
       <c r="H442" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21017,7 +21017,7 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>廣川市</t>
+          <t>寶台天馳</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
@@ -21055,7 +21055,7 @@
       <c r="F443" s="2" t="inlineStr"/>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+          <t>桃園市中壢區青溪段450地號</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
@@ -21092,12 +21092,20 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>弘鼎金家園</t>
-        </is>
-      </c>
-      <c r="E444" s="2" t="inlineStr"/>
+          <t>廣川市</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F444" s="2" t="inlineStr"/>
-      <c r="G444" s="2" t="inlineStr"/>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+        </is>
+      </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21105,7 +21113,7 @@
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J444" s="2" t="inlineStr">
@@ -21132,14 +21140,10 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>悅新艾玥</t>
-        </is>
-      </c>
-      <c r="E445" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>弘鼎金家園</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr"/>
       <c r="F445" s="2" t="inlineStr"/>
       <c r="G445" s="2" t="inlineStr"/>
       <c r="H445" s="2" t="inlineStr">
@@ -21176,7 +21180,7 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>憶聲智匯科技園區</t>
+          <t>悅新艾玥</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
@@ -21220,20 +21224,16 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>新大萃</t>
+          <t>憶聲智匯科技園區</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F447" s="2" t="inlineStr"/>
-      <c r="G447" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔五街</t>
-        </is>
-      </c>
+      <c r="G447" s="2" t="inlineStr"/>
       <c r="H447" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
@@ -21268,12 +21268,20 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>昆旺青茵悦</t>
-        </is>
-      </c>
-      <c r="E448" s="2" t="inlineStr"/>
+          <t>新大萃</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F448" s="2" t="inlineStr"/>
-      <c r="G448" s="2" t="inlineStr"/>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔五街</t>
+        </is>
+      </c>
       <c r="H448" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21281,7 +21289,7 @@
       </c>
       <c r="I448" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J448" s="2" t="inlineStr">
@@ -21308,28 +21316,20 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>昭揚天朗</t>
-        </is>
-      </c>
-      <c r="E449" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>昆旺青茵悦</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr"/>
       <c r="F449" s="2" t="inlineStr"/>
-      <c r="G449" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
-        </is>
-      </c>
+      <c r="G449" s="2" t="inlineStr"/>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr">
@@ -21356,20 +21356,28 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>晶采學</t>
-        </is>
-      </c>
-      <c r="E450" s="2" t="inlineStr"/>
+          <t>昭揚天朗</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F450" s="2" t="inlineStr"/>
-      <c r="G450" s="2" t="inlineStr"/>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
+        </is>
+      </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J450" s="2" t="inlineStr">
@@ -21396,7 +21404,7 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>柏宣天擎</t>
+          <t>晶采學</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr"/>
@@ -21436,20 +21444,12 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>樂MORE</t>
-        </is>
-      </c>
-      <c r="E452" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>柏宣天擎</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr"/>
       <c r="F452" s="2" t="inlineStr"/>
-      <c r="G452" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區民溪三路209巷25號</t>
-        </is>
-      </c>
+      <c r="G452" s="2" t="inlineStr"/>
       <c r="H452" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J452" s="2" t="inlineStr">
@@ -21484,12 +21484,20 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>正發廠王NO.3</t>
-        </is>
-      </c>
-      <c r="E453" s="2" t="inlineStr"/>
+          <t>樂MORE</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F453" s="2" t="inlineStr"/>
-      <c r="G453" s="2" t="inlineStr"/>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區民溪三路209巷25號</t>
+        </is>
+      </c>
       <c r="H453" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21497,7 +21505,7 @@
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J453" s="2" t="inlineStr">
@@ -21524,20 +21532,12 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>深耕17</t>
-        </is>
-      </c>
-      <c r="E454" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>正發廠王NO.3</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr"/>
       <c r="F454" s="2" t="inlineStr"/>
-      <c r="G454" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區啟文路二段176巷21號對面</t>
-        </is>
-      </c>
+      <c r="G454" s="2" t="inlineStr"/>
       <c r="H454" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J454" s="2" t="inlineStr">
@@ -21572,16 +21572,20 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>湘榭別墅</t>
+          <t>深耕17</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F455" s="2" t="inlineStr"/>
-      <c r="G455" s="2" t="inlineStr"/>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區啟文路二段176巷21號對面</t>
+        </is>
+      </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21589,7 +21593,7 @@
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr">
@@ -21616,20 +21620,16 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>澍之丘</t>
+          <t>湘榭別墅</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F456" s="2" t="inlineStr"/>
-      <c r="G456" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區月桃路615巷</t>
-        </is>
-      </c>
+      <c r="G456" s="2" t="inlineStr"/>
       <c r="H456" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J456" s="2" t="inlineStr">
@@ -21664,16 +21664,20 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>璟城A22</t>
+          <t>澍之丘</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr"/>
-      <c r="G457" s="2" t="inlineStr"/>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區月桃路615巷</t>
+        </is>
+      </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21681,7 +21685,7 @@
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J457" s="2" t="inlineStr">
@@ -21708,7 +21712,7 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>皇普園首之道</t>
+          <t>璟城A22</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
@@ -21752,20 +21756,16 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>皇普賦隱</t>
+          <t>皇普園首之道</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr"/>
-      <c r="G459" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔二街</t>
-        </is>
-      </c>
+      <c r="G459" s="2" t="inlineStr"/>
       <c r="H459" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21773,7 +21773,7 @@
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr">
@@ -21800,16 +21800,20 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>益展有福</t>
+          <t>皇普賦隱</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr"/>
-      <c r="G460" s="2" t="inlineStr"/>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔二街</t>
+        </is>
+      </c>
       <c r="H460" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21817,7 +21821,7 @@
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J460" s="2" t="inlineStr">
@@ -21844,7 +21848,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>立信悦榕</t>
+          <t>益展有福</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -21866,7 +21870,7 @@
       </c>
       <c r="J461" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21892,7 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>站前新鋭</t>
+          <t>立信悦榕</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -21910,7 +21914,7 @@
       </c>
       <c r="J462" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -21932,7 +21936,7 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>綠意領航1號</t>
+          <t>站前新鋭</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
@@ -21976,20 +21980,16 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>聚泰雲藝</t>
+          <t>綠意領航1號</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F464" s="2" t="inlineStr"/>
-      <c r="G464" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區元生三街</t>
-        </is>
-      </c>
+      <c r="G464" s="2" t="inlineStr"/>
       <c r="H464" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21997,7 +21997,7 @@
       </c>
       <c r="I464" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J464" s="2" t="inlineStr">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>聯懋杉苑</t>
+          <t>聚泰雲藝</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
@@ -22035,7 +22035,7 @@
       <c r="F465" s="2" t="inlineStr"/>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區靠近興西二路及興北二路</t>
+          <t>桃園市中壢區元生三街</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -22072,16 +22072,20 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>聯懋杉苑</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr"/>
-      <c r="G466" s="2" t="inlineStr"/>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區靠近興西二路及興北二路</t>
+        </is>
+      </c>
       <c r="H466" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22089,7 +22093,7 @@
       </c>
       <c r="I466" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J466" s="2" t="inlineStr">
@@ -22116,7 +22120,7 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>菁美學</t>
+          <t>荷沐莊園</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
@@ -22160,7 +22164,7 @@
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-THE ONE</t>
+          <t>菁美學</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
@@ -22204,7 +22208,7 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-綠景苑</t>
+          <t>藍海帝國-THE ONE</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
@@ -22248,10 +22252,14 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>誠鑫19</t>
-        </is>
-      </c>
-      <c r="E470" s="2" t="inlineStr"/>
+          <t>藍海帝國-綠景苑</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F470" s="2" t="inlineStr"/>
       <c r="G470" s="2" t="inlineStr"/>
       <c r="H470" s="2" t="inlineStr">
@@ -22288,14 +22296,10 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>路易威登</t>
-        </is>
-      </c>
-      <c r="E471" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>誠鑫19</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr"/>
       <c r="F471" s="2" t="inlineStr"/>
       <c r="G471" s="2" t="inlineStr"/>
       <c r="H471" s="2" t="inlineStr">
@@ -22332,7 +22336,7 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>鑫利川-三城</t>
+          <t>路易威登</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
@@ -22376,7 +22380,7 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>閣美學</t>
+          <t>鑫利川-三城</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
@@ -22420,7 +22424,7 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>青城之愛3</t>
+          <t>閣美學</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -22464,7 +22468,7 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>鴻廣川湛</t>
+          <t>青城之愛3</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
@@ -22508,20 +22512,16 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>鴻踞樸藝</t>
+          <t>鴻廣川湛</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr"/>
-      <c r="G476" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區興北一路及興東路 交叉口</t>
-        </is>
-      </c>
+      <c r="G476" s="2" t="inlineStr"/>
       <c r="H476" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22529,7 +22529,7 @@
       </c>
       <c r="I476" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J476" s="2" t="inlineStr">
@@ -22551,21 +22551,25 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>三鶯澤苑</t>
+          <t>鴻踞樸藝</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr"/>
-      <c r="G477" s="2" t="inlineStr"/>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興北一路及興東路 交叉口</t>
+        </is>
+      </c>
       <c r="H477" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22573,7 +22577,7 @@
       </c>
       <c r="I477" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J477" s="2" t="inlineStr">
@@ -22600,20 +22604,16 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>上順麗</t>
+          <t>三鶯澤苑</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr"/>
-      <c r="G478" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區客運一段340地號</t>
-        </is>
-      </c>
+      <c r="G478" s="2" t="inlineStr"/>
       <c r="H478" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22621,7 +22621,7 @@
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr">
@@ -22648,16 +22648,20 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>中麗北極星</t>
+          <t>上順麗</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr"/>
-      <c r="G479" s="2" t="inlineStr"/>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區客運一段340地號</t>
+        </is>
+      </c>
       <c r="H479" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22665,7 +22669,7 @@
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J479" s="2" t="inlineStr">
@@ -22692,7 +22696,7 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>京懋敦和</t>
+          <t>中麗北極星</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
@@ -22736,7 +22740,7 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>佳暘青見</t>
+          <t>京懋敦和</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
@@ -22780,20 +22784,16 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>偉築新豐州</t>
+          <t>佳暘青見</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr"/>
-      <c r="G482" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區青峰路二段117~129號</t>
-        </is>
-      </c>
+      <c r="G482" s="2" t="inlineStr"/>
       <c r="H482" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22801,7 +22801,7 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr">
@@ -22828,16 +22828,20 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>傳佳樂</t>
+          <t>偉築新豐州</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F483" s="2" t="inlineStr"/>
-      <c r="G483" s="2" t="inlineStr"/>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區青峰路二段117~129號</t>
+        </is>
+      </c>
       <c r="H483" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22845,7 +22849,7 @@
       </c>
       <c r="I483" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J483" s="2" t="inlineStr">
@@ -22872,7 +22876,7 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>元基至善2</t>
+          <t>傳佳樂</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
@@ -22916,7 +22920,7 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>力璞翔-豐禾</t>
+          <t>元基至善2</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
@@ -22938,7 +22942,7 @@
       </c>
       <c r="J485" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -22960,20 +22964,16 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>合展悦恬</t>
+          <t>力璞翔-豐禾</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr"/>
-      <c r="G486" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G486" s="2" t="inlineStr"/>
       <c r="H486" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22981,12 +22981,12 @@
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J486" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -23008,18 +23008,18 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>合陽逸境</t>
+          <t>合展悦恬</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F487" s="2" t="inlineStr"/>
       <c r="G487" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區青峰段273號地號</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H487" s="2" t="inlineStr">
@@ -23056,18 +23056,18 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>名川琢域</t>
+          <t>合陽逸境</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr"/>
       <c r="G488" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
+          <t>桃園市大園區青峰段273號地號</t>
         </is>
       </c>
       <c r="H488" s="2" t="inlineStr">
@@ -23104,18 +23104,18 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅</t>
+          <t>名川琢域</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr"/>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區內海墘段 110-84</t>
+          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -23152,12 +23152,20 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅Villa</t>
-        </is>
-      </c>
-      <c r="E490" s="2" t="inlineStr"/>
+          <t>垽赫海漾星墅</t>
+        </is>
+      </c>
+      <c r="E490" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F490" s="2" t="inlineStr"/>
-      <c r="G490" s="2" t="inlineStr"/>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區內海墘段 110-84</t>
+        </is>
+      </c>
       <c r="H490" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23165,7 +23173,7 @@
       </c>
       <c r="I490" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J490" s="2" t="inlineStr">
@@ -23192,14 +23200,10 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
-        </is>
-      </c>
-      <c r="E491" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>垽赫海漾星墅Villa</t>
+        </is>
+      </c>
+      <c r="E491" s="2" t="inlineStr"/>
       <c r="F491" s="2" t="inlineStr"/>
       <c r="G491" s="2" t="inlineStr"/>
       <c r="H491" s="2" t="inlineStr">
@@ -23236,7 +23240,7 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>大地玥</t>
+          <t>大地昕</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
@@ -23280,7 +23284,7 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>大地．呈</t>
+          <t>大地玥</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
@@ -23324,7 +23328,7 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>大禾苑</t>
+          <t>大地．呈</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
@@ -23368,7 +23372,7 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>威均帝璽</t>
+          <t>大禾苑</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
@@ -23412,20 +23416,16 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>宗佳領御</t>
+          <t>威均帝璽</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F496" s="2" t="inlineStr"/>
-      <c r="G496" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區中路與科七街</t>
-        </is>
-      </c>
+      <c r="G496" s="2" t="inlineStr"/>
       <c r="H496" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="I496" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J496" s="2" t="inlineStr">
@@ -23460,16 +23460,20 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>宜誠玉環</t>
+          <t>宗佳領御</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F497" s="2" t="inlineStr"/>
-      <c r="G497" s="2" t="inlineStr"/>
+      <c r="G497" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區中路與科七街</t>
+        </is>
+      </c>
       <c r="H497" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23477,7 +23481,7 @@
       </c>
       <c r="I497" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J497" s="2" t="inlineStr">
@@ -23504,7 +23508,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>家綻</t>
+          <t>宜誠玉環</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -23548,7 +23552,7 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>家綻2</t>
+          <t>家綻</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
@@ -23592,7 +23596,7 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>富總日日</t>
+          <t>家綻2</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
@@ -23636,10 +23640,14 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>山榆.柏悅</t>
-        </is>
-      </c>
-      <c r="E501" s="2" t="inlineStr"/>
+          <t>富總日日</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F501" s="2" t="inlineStr"/>
       <c r="G501" s="2" t="inlineStr"/>
       <c r="H501" s="2" t="inlineStr">
@@ -23654,7 +23662,7 @@
       </c>
       <c r="J501" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -23676,20 +23684,12 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>山榆柏悅</t>
-        </is>
-      </c>
-      <c r="E502" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>山榆.柏悅</t>
+        </is>
+      </c>
+      <c r="E502" s="2" t="inlineStr"/>
       <c r="F502" s="2" t="inlineStr"/>
-      <c r="G502" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區永園路二段152號旁</t>
-        </is>
-      </c>
+      <c r="G502" s="2" t="inlineStr"/>
       <c r="H502" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23697,12 +23697,12 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -23724,16 +23724,20 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>川洋青勻</t>
+          <t>山榆柏悅</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr"/>
-      <c r="G503" s="2" t="inlineStr"/>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區永園路二段152號旁</t>
+        </is>
+      </c>
       <c r="H503" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23741,7 +23745,7 @@
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J503" s="2" t="inlineStr">
@@ -23768,7 +23772,7 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>御禾院</t>
+          <t>川洋青勻</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
@@ -23812,20 +23816,16 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>悦恬</t>
+          <t>御禾院</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr"/>
-      <c r="G505" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G505" s="2" t="inlineStr"/>
       <c r="H505" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23833,7 +23833,7 @@
       </c>
       <c r="I505" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J505" s="2" t="inlineStr">
@@ -23860,7 +23860,7 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>日勝好日子</t>
+          <t>悦恬</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
@@ -23871,7 +23871,7 @@
       <c r="F506" s="2" t="inlineStr"/>
       <c r="G506" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區後館路1巷旁</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H506" s="2" t="inlineStr">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>日青悠</t>
+          <t>日勝好日子</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
@@ -23919,7 +23919,7 @@
       <c r="F507" s="2" t="inlineStr"/>
       <c r="G507" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區五青路63巷257號旁</t>
+          <t>桃園市大園區後館路1巷旁</t>
         </is>
       </c>
       <c r="H507" s="2" t="inlineStr">
@@ -23956,12 +23956,20 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>松合苑5</t>
-        </is>
-      </c>
-      <c r="E508" s="2" t="inlineStr"/>
+          <t>日青悠</t>
+        </is>
+      </c>
+      <c r="E508" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F508" s="2" t="inlineStr"/>
-      <c r="G508" s="2" t="inlineStr"/>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區五青路63巷257號旁</t>
+        </is>
+      </c>
       <c r="H508" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23969,7 +23977,7 @@
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr">
@@ -23996,20 +24004,12 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>璟都新世界</t>
-        </is>
-      </c>
-      <c r="E509" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>松合苑5</t>
+        </is>
+      </c>
+      <c r="E509" s="2" t="inlineStr"/>
       <c r="F509" s="2" t="inlineStr"/>
-      <c r="G509" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區大觀路及環區北路口</t>
-        </is>
-      </c>
+      <c r="G509" s="2" t="inlineStr"/>
       <c r="H509" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24017,7 +24017,7 @@
       </c>
       <c r="I509" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J509" s="2" t="inlineStr">
@@ -24044,16 +24044,20 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>福興豐璟</t>
+          <t>璟都新世界</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F510" s="2" t="inlineStr"/>
-      <c r="G510" s="2" t="inlineStr"/>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區大觀路及環區北路口</t>
+        </is>
+      </c>
       <c r="H510" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24061,7 +24065,7 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr">
@@ -24088,7 +24092,7 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>立程·晴美</t>
+          <t>福興豐璟</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
@@ -24132,20 +24136,16 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>立程‧晴美</t>
+          <t>立程·晴美</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr"/>
-      <c r="G512" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區學七街69-1號</t>
-        </is>
-      </c>
+      <c r="G512" s="2" t="inlineStr"/>
       <c r="H512" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24153,7 +24153,7 @@
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J512" s="2" t="inlineStr">
@@ -24180,23 +24180,23 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>立程建設客運二段案</t>
+          <t>立程‧晴美</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr"/>
       <c r="G513" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區學七街69-1號旁</t>
+          <t>桃園市大園區學七街69-1號</t>
         </is>
       </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I513" s="2" t="inlineStr">
@@ -24228,29 +24228,33 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>立鴻晶硯</t>
+          <t>立程建設客運二段案</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F514" s="2" t="inlineStr"/>
-      <c r="G514" s="2" t="inlineStr"/>
+      <c r="G514" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區學七街69-1號旁</t>
+        </is>
+      </c>
       <c r="H514" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J514" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -24272,7 +24276,7 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>臥墨池</t>
+          <t>立鴻晶硯</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
@@ -24294,7 +24298,7 @@
       </c>
       <c r="J515" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24316,7 +24320,7 @@
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>臻璞</t>
+          <t>臥墨池</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -24360,7 +24364,7 @@
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>興禾  築美學</t>
+          <t>臻璞</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
@@ -24404,20 +24408,16 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>航綻甜心</t>
+          <t>興禾  築美學</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F518" s="2" t="inlineStr"/>
-      <c r="G518" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路與科五路交叉口</t>
-        </is>
-      </c>
+      <c r="G518" s="2" t="inlineStr"/>
       <c r="H518" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24425,7 +24425,7 @@
       </c>
       <c r="I518" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J518" s="2" t="inlineStr">
@@ -24452,16 +24452,20 @@
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>英堡日朗</t>
+          <t>航綻甜心</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F519" s="2" t="inlineStr"/>
-      <c r="G519" s="2" t="inlineStr"/>
+      <c r="G519" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路與科五路交叉口</t>
+        </is>
+      </c>
       <c r="H519" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24469,7 +24473,7 @@
       </c>
       <c r="I519" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J519" s="2" t="inlineStr">
@@ -24496,20 +24500,16 @@
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>薪成家II</t>
+          <t>英堡日朗</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr"/>
-      <c r="G520" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路597號</t>
-        </is>
-      </c>
+      <c r="G520" s="2" t="inlineStr"/>
       <c r="H520" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24517,7 +24517,7 @@
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J520" s="2" t="inlineStr">
@@ -24544,16 +24544,20 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>逸偉A+</t>
+          <t>薪成家II</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr"/>
-      <c r="G521" s="2" t="inlineStr"/>
+      <c r="G521" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路597號</t>
+        </is>
+      </c>
       <c r="H521" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24561,7 +24565,7 @@
       </c>
       <c r="I521" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J521" s="2" t="inlineStr">
@@ -24588,10 +24592,14 @@
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>遠雄仰森</t>
-        </is>
-      </c>
-      <c r="E522" s="2" t="inlineStr"/>
+          <t>逸偉A+</t>
+        </is>
+      </c>
+      <c r="E522" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F522" s="2" t="inlineStr"/>
       <c r="G522" s="2" t="inlineStr"/>
       <c r="H522" s="2" t="inlineStr">
@@ -24628,14 +24636,10 @@
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>鈞貴極美II</t>
-        </is>
-      </c>
-      <c r="E523" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>遠雄仰森</t>
+        </is>
+      </c>
+      <c r="E523" s="2" t="inlineStr"/>
       <c r="F523" s="2" t="inlineStr"/>
       <c r="G523" s="2" t="inlineStr"/>
       <c r="H523" s="2" t="inlineStr">
@@ -24672,7 +24676,7 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>高誠君品</t>
+          <t>鈞貴極美II</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
@@ -24716,10 +24720,14 @@
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>龍築靜玥</t>
-        </is>
-      </c>
-      <c r="E525" s="2" t="inlineStr"/>
+          <t>高誠君品</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F525" s="2" t="inlineStr"/>
       <c r="G525" s="2" t="inlineStr"/>
       <c r="H525" s="2" t="inlineStr">
@@ -24738,15 +24746,55 @@
         </is>
       </c>
     </row>
-    <row r="527">
-      <c r="A527" s="3" t="inlineStr">
-        <is>
-          <t>最後更新：2026-09-27 13:28（台灣時間）　共 524 筆　資料來源：好房網、樂屋網</t>
+    <row r="526">
+      <c r="A526" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B526" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C526" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D526" s="2" t="inlineStr">
+        <is>
+          <t>龍築靜玥</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr"/>
+      <c r="F526" s="2" t="inlineStr"/>
+      <c r="G526" s="2" t="inlineStr"/>
+      <c r="H526" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I526" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J526" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="3" t="inlineStr">
+        <is>
+          <t>最後更新：2026-09-28 13:36（台灣時間）　共 525 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J525"/>
+  <autoFilter ref="A1:J526"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24789,7 +24789,7 @@
     <row r="528">
       <c r="A528" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-28 13:36（台灣時間）　共 525 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-09-29 13:54（台灣時間）　共 525 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-09-30 13:44（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-01 14:10（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-01 14:10（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-02 13:53（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-02 13:53（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-03 13:29（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-03 13:29（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-04 14:05（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-04 14:05（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-05 13:55（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-05 13:55（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-06 14:34（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-06 14:34（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-07 14:13（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-07 14:13（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-08 14:19（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-08 14:19（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-09 14:22（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-09 14:22（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-10 14:03（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-10 14:03（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-11 14:02（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-11 14:02（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-12 14:12（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-12 14:12（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-13 14:56（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-13 14:56（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-14 13:05（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-14 13:05（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-15 12:53（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-15 12:53（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-16 12:44（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-16 12:44（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-17 12:41（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-17 12:41（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-18 12:47（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-18 12:47（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-19 12:55（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-19 12:55（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-20 13:03（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24861,7 +24861,7 @@
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-20 13:03（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-21 13:02（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預售案清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$527</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$528</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J529"/>
+  <dimension ref="A1:J530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18028,12 +18028,20 @@
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>友座豐禾</t>
-        </is>
-      </c>
-      <c r="E377" s="2" t="inlineStr"/>
+          <t>冠輝永萃</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F377" s="2" t="inlineStr"/>
-      <c r="G377" s="2" t="inlineStr"/>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區永和路一段45號</t>
+        </is>
+      </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18041,12 +18049,12 @@
       </c>
       <c r="I377" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J377" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -18068,20 +18076,12 @@
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>家格綻綻</t>
-        </is>
-      </c>
-      <c r="E378" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>友座豐禾</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr"/>
       <c r="F378" s="2" t="inlineStr"/>
-      <c r="G378" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區中正路607號</t>
-        </is>
-      </c>
+      <c r="G378" s="2" t="inlineStr"/>
       <c r="H378" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="I378" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J378" s="2" t="inlineStr">
@@ -18116,23 +18116,23 @@
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>敦南宴</t>
+          <t>家格綻綻</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F379" s="2" t="inlineStr"/>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區永利路216巷</t>
+          <t>新北市永和區中正路607號</t>
         </is>
       </c>
       <c r="H379" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I379" s="2" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>新碩永傳</t>
+          <t>敦南宴</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -18175,12 +18175,12 @@
       <c r="F380" s="2" t="inlineStr"/>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中正路388號旁</t>
+          <t>新北市永和區永利路216巷</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I380" s="2" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>漢寶臺大苑</t>
+          <t>新碩永傳</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
@@ -18223,12 +18223,12 @@
       <c r="F381" s="2" t="inlineStr"/>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區成功路一段132號</t>
+          <t>新北市永和區中正路388號旁</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I381" s="2" t="inlineStr">
@@ -18260,20 +18260,28 @@
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>漢皇River Sky</t>
-        </is>
-      </c>
-      <c r="E382" s="2" t="inlineStr"/>
+          <t>漢寶臺大苑</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F382" s="2" t="inlineStr"/>
-      <c r="G382" s="2" t="inlineStr"/>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區成功路一段132號</t>
+        </is>
+      </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I382" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J382" s="2" t="inlineStr">
@@ -18300,28 +18308,20 @@
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>蒲陽建設復興街案(尚未取得建照)</t>
-        </is>
-      </c>
-      <c r="E383" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>漢皇River Sky</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr"/>
       <c r="F383" s="2" t="inlineStr"/>
-      <c r="G383" s="2" t="inlineStr">
-        <is>
-          <t>新北市永和區復興街</t>
-        </is>
-      </c>
+      <c r="G383" s="2" t="inlineStr"/>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I383" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J383" s="2" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>頂溪大苑</t>
+          <t>蒲陽建設復興街案(尚未取得建照)</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -18359,12 +18359,12 @@
       <c r="F384" s="2" t="inlineStr"/>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區中山路一段28巷口旁</t>
+          <t>新北市永和區復興街</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I384" s="2" t="inlineStr">
@@ -18396,16 +18396,20 @@
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>頂溪捷運站~黃金綠建築,1~2房</t>
+          <t>頂溪大苑</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F385" s="2" t="inlineStr"/>
-      <c r="G385" s="2" t="inlineStr"/>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>新北市永和區中山路一段28巷口旁</t>
+        </is>
+      </c>
       <c r="H385" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18413,7 +18417,7 @@
       </c>
       <c r="I385" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J385" s="2" t="inlineStr">
@@ -18430,38 +18434,34 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>淡水汐止線</t>
+          <t>板橋雙和線</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>汐止區</t>
+          <t>永和區</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>富都康莊</t>
+          <t>頂溪捷運站~黃金綠建築,1~2房</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr"/>
-      <c r="G386" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區康寧街</t>
-        </is>
-      </c>
+      <c r="G386" s="2" t="inlineStr"/>
       <c r="H386" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I386" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J386" s="2" t="inlineStr">
@@ -18488,20 +18488,28 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>文心慕慕</t>
-        </is>
-      </c>
-      <c r="E387" s="2" t="inlineStr"/>
+          <t>富都康莊</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F387" s="2" t="inlineStr"/>
-      <c r="G387" s="2" t="inlineStr"/>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區康寧街</t>
+        </is>
+      </c>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I387" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J387" s="2" t="inlineStr">
@@ -18528,14 +18536,10 @@
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>東煒大局</t>
-        </is>
-      </c>
-      <c r="E388" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>文心慕慕</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr"/>
       <c r="F388" s="2" t="inlineStr"/>
       <c r="G388" s="2" t="inlineStr"/>
       <c r="H388" s="2" t="inlineStr">
@@ -18572,28 +18576,24 @@
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>汐止華品</t>
+          <t>東煒大局</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr"/>
-      <c r="G389" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區保一街與保一街8巷交叉口</t>
-        </is>
-      </c>
+      <c r="G389" s="2" t="inlineStr"/>
       <c r="H389" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I389" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J389" s="2" t="inlineStr">
@@ -18620,23 +18620,23 @@
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>汐科爵鼎</t>
+          <t>汐止華品</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr"/>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區水源路二段190號旁</t>
+          <t>新北市汐止區保一街與保一街8巷交叉口</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I390" s="2" t="inlineStr">
@@ -18668,16 +18668,20 @@
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>美麗山林</t>
+          <t>汐科爵鼎</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr"/>
-      <c r="G391" s="2" t="inlineStr"/>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區水源路二段190號旁</t>
+        </is>
+      </c>
       <c r="H391" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18685,7 +18689,7 @@
       </c>
       <c r="I391" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J391" s="2" t="inlineStr">
@@ -18712,28 +18716,24 @@
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>美麗山林-華廈區</t>
+          <t>美麗山林</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr"/>
-      <c r="G392" s="2" t="inlineStr">
-        <is>
-          <t>新北市汐止區水源路二段125巷</t>
-        </is>
-      </c>
+      <c r="G392" s="2" t="inlineStr"/>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I392" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J392" s="2" t="inlineStr">
@@ -18760,7 +18760,7 @@
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>金湖漾</t>
+          <t>美麗山林-華廈區</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
@@ -18771,12 +18771,12 @@
       <c r="F393" s="2" t="inlineStr"/>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區民族二街30巷22號</t>
+          <t>新北市汐止區水源路二段125巷</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I393" s="2" t="inlineStr">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>雄鷹天映湖</t>
+          <t>金湖漾</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -18819,12 +18819,12 @@
       <c r="F394" s="2" t="inlineStr"/>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>新北市汐止區湖東街5巷50號</t>
+          <t>新北市汐止區民族二街30巷22號</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I394" s="2" t="inlineStr">
@@ -18856,24 +18856,28 @@
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>雲禾月</t>
+          <t>雄鷹天映湖</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr"/>
-      <c r="G395" s="2" t="inlineStr"/>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>新北市汐止區湖東街5巷50號</t>
+        </is>
+      </c>
       <c r="H395" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I395" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J395" s="2" t="inlineStr">
@@ -18895,12 +18899,12 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>淡水區</t>
+          <t>汐止區</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>京美晴朗</t>
+          <t>雲禾月</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -18944,20 +18948,16 @@
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>兆美萬海</t>
+          <t>京美晴朗</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr"/>
-      <c r="G397" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區望高樓段535、535-1地號</t>
-        </is>
-      </c>
+      <c r="G397" s="2" t="inlineStr"/>
       <c r="H397" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -18965,7 +18965,7 @@
       </c>
       <c r="I397" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J397" s="2" t="inlineStr">
@@ -18992,12 +18992,20 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>光全御苑</t>
-        </is>
-      </c>
-      <c r="E398" s="2" t="inlineStr"/>
+          <t>兆美萬海</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F398" s="2" t="inlineStr"/>
-      <c r="G398" s="2" t="inlineStr"/>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區望高樓段535、535-1地號</t>
+        </is>
+      </c>
       <c r="H398" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19005,12 +19013,12 @@
       </c>
       <c r="I398" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J398" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -19032,20 +19040,12 @@
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>台北別墅</t>
-        </is>
-      </c>
-      <c r="E399" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>光全御苑</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr"/>
       <c r="F399" s="2" t="inlineStr"/>
-      <c r="G399" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區尚頂一街</t>
-        </is>
-      </c>
+      <c r="G399" s="2" t="inlineStr"/>
       <c r="H399" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19053,12 +19053,12 @@
       </c>
       <c r="I399" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J399" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>合康植芯</t>
+          <t>台北別墅</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
@@ -19091,7 +19091,7 @@
       <c r="F400" s="2" t="inlineStr"/>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路三段202巷65弄</t>
+          <t>新北市淡水區尚頂一街</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -19128,12 +19128,20 @@
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>合謙劃時代</t>
-        </is>
-      </c>
-      <c r="E401" s="2" t="inlineStr"/>
+          <t>合康植芯</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F401" s="2" t="inlineStr"/>
-      <c r="G401" s="2" t="inlineStr"/>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區濱海路三段202巷65弄</t>
+        </is>
+      </c>
       <c r="H401" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19141,7 +19149,7 @@
       </c>
       <c r="I401" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J401" s="2" t="inlineStr">
@@ -19168,20 +19176,12 @@
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>合謙耀時代</t>
-        </is>
-      </c>
-      <c r="E402" s="2" t="inlineStr">
-        <is>
-          <t>售價未定</t>
-        </is>
-      </c>
+          <t>合謙劃時代</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr"/>
       <c r="F402" s="2" t="inlineStr"/>
-      <c r="G402" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市段185地號</t>
-        </is>
-      </c>
+      <c r="G402" s="2" t="inlineStr"/>
       <c r="H402" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="I402" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J402" s="2" t="inlineStr">
@@ -19216,7 +19216,7 @@
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>向陽</t>
+          <t>合謙耀時代</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -19227,7 +19227,7 @@
       <c r="F403" s="2" t="inlineStr"/>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
+          <t>新北市淡水區新市段185地號</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>員邦徊</t>
+          <t>向陽</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -19275,7 +19275,7 @@
       <c r="F404" s="2" t="inlineStr"/>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路72巷</t>
+          <t>新北市淡水區濱海路一段、濱海路111巷口</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
@@ -19312,23 +19312,23 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>嘉潤家泰氧之森</t>
+          <t>員邦徊</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr"/>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路88號</t>
+          <t>新北市淡水區坪頂路72巷</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I405" s="2" t="inlineStr">
@@ -19360,23 +19360,23 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>富麗ONE</t>
+          <t>嘉潤家泰氧之森</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr"/>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區新市段118地號</t>
+          <t>新北市淡水區坪頂路88號</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I406" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>將捷建設紅樹林案</t>
+          <t>富麗ONE</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -19419,12 +19419,12 @@
       <c r="F407" s="2" t="inlineStr"/>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
+          <t>新北市淡水區新市段118地號</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I407" s="2" t="inlineStr">
@@ -19456,23 +19456,23 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>山河帝寶</t>
+          <t>將捷建設紅樹林案</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr"/>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
+          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I408" s="2" t="inlineStr">
@@ -19504,18 +19504,18 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>新海城</t>
+          <t>山河帝寶</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr"/>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路二段、新市二路</t>
+          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -19552,16 +19552,20 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>新海城2夢想市</t>
+          <t>新海城</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr"/>
-      <c r="G410" s="2" t="inlineStr"/>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區沙崙路二段、新市二路</t>
+        </is>
+      </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19569,7 +19573,7 @@
       </c>
       <c r="I410" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J410" s="2" t="inlineStr">
@@ -19596,28 +19600,24 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>村泉蒔美</t>
+          <t>新海城2夢想市</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr"/>
-      <c r="G411" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區中正東路二段143巷12弄</t>
-        </is>
-      </c>
+      <c r="G411" s="2" t="inlineStr"/>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J411" s="2" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>水問山</t>
+          <t>村泉蒔美</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -19655,7 +19655,7 @@
       <c r="F412" s="2" t="inlineStr"/>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段143巷2弄</t>
+          <t>新北市淡水區中正東路二段143巷12弄</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -19692,23 +19692,23 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>水美慕河</t>
+          <t>水問山</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr"/>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路一段47號</t>
+          <t>新北市淡水區中正東路二段143巷2弄</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I413" s="2" t="inlineStr">
@@ -19740,18 +19740,18 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>湯泉紅樹林</t>
+          <t>水美慕河</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr"/>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段5巷35號</t>
+          <t>新北市淡水區中正東路一段47號</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>石上青</t>
+          <t>湯泉紅樹林</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
@@ -19799,7 +19799,7 @@
       <c r="F415" s="2" t="inlineStr"/>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區八勢一街36號</t>
+          <t>新北市淡水區中正東路二段5巷35號</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>致茂橋豐</t>
+          <t>石上青</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -19847,7 +19847,7 @@
       <c r="F416" s="2" t="inlineStr"/>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路一段</t>
+          <t>新北市淡水區八勢一街36號</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -19884,18 +19884,18 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>藝沐汀</t>
+          <t>致茂橋豐</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F417" s="2" t="inlineStr"/>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區民族路、自強路305巷</t>
+          <t>新北市淡水區沙崙路一段</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -19932,16 +19932,20 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>馥人灣-新濠門</t>
+          <t>藝沐汀</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr"/>
-      <c r="G418" s="2" t="inlineStr"/>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區民族路、自強路305巷</t>
+        </is>
+      </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19949,7 +19953,7 @@
       </c>
       <c r="I418" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J418" s="2" t="inlineStr">
@@ -19976,20 +19980,16 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>鴻灃COMO</t>
+          <t>馥人灣-新濠門</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr"/>
-      <c r="G419" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
-        </is>
-      </c>
+      <c r="G419" s="2" t="inlineStr"/>
       <c r="H419" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19997,7 +19997,7 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J419" s="2" t="inlineStr">
@@ -20009,33 +20009,33 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>A20-合磊天沐</t>
+          <t>鴻灃COMO</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr"/>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -20072,16 +20072,20 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>The Nexus 新識界</t>
+          <t>A20-合磊天沐</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr"/>
-      <c r="G421" s="2" t="inlineStr"/>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+        </is>
+      </c>
       <c r="H421" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20089,7 +20093,7 @@
       </c>
       <c r="I421" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J421" s="2" t="inlineStr">
@@ -20116,7 +20120,7 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>一品閣</t>
+          <t>The Nexus 新識界</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -20160,20 +20164,16 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>中麗若隱</t>
+          <t>一品閣</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F423" s="2" t="inlineStr"/>
-      <c r="G423" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
-        </is>
-      </c>
+      <c r="G423" s="2" t="inlineStr"/>
       <c r="H423" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20181,7 +20181,7 @@
       </c>
       <c r="I423" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J423" s="2" t="inlineStr">
@@ -20208,7 +20208,7 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>享JIA</t>
+          <t>中麗若隱</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
@@ -20219,7 +20219,7 @@
       <c r="F424" s="2" t="inlineStr"/>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區青山一路157號旁</t>
+          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
@@ -20256,18 +20256,18 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>保利首綻</t>
+          <t>享JIA</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr"/>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐路225號對面</t>
+          <t>桃園市中壢區青山一路157號旁</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -20304,16 +20304,20 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>勤樸悅圓</t>
+          <t>保利首綻</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr"/>
-      <c r="G426" s="2" t="inlineStr"/>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐路225號對面</t>
+        </is>
+      </c>
       <c r="H426" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20321,7 +20325,7 @@
       </c>
       <c r="I426" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J426" s="2" t="inlineStr">
@@ -20348,20 +20352,16 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>君臨塘詩-慕荷</t>
+          <t>勤樸悅圓</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr"/>
-      <c r="G427" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
-        </is>
-      </c>
+      <c r="G427" s="2" t="inlineStr"/>
       <c r="H427" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20369,7 +20369,7 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J427" s="2" t="inlineStr">
@@ -20396,18 +20396,18 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>和發采采</t>
+          <t>君臨塘詩-慕荷</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr"/>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區新生路二段378之2號對面</t>
+          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
@@ -20444,18 +20444,18 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>品坤學</t>
+          <t>和發采采</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr"/>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區環西路二段25巷11號旁</t>
+          <t>桃園市中壢區新生路二段378之2號對面</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -20492,18 +20492,18 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>大亮FIKA</t>
+          <t>品坤學</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr"/>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區永順一街30號旁</t>
+          <t>桃園市中壢區環西路二段25巷11號旁</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
@@ -20540,12 +20540,20 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>大清上景</t>
-        </is>
-      </c>
-      <c r="E431" s="2" t="inlineStr"/>
+          <t>大亮FIKA</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F431" s="2" t="inlineStr"/>
-      <c r="G431" s="2" t="inlineStr"/>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區永順一街30號旁</t>
+        </is>
+      </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20553,7 +20561,7 @@
       </c>
       <c r="I431" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J431" s="2" t="inlineStr">
@@ -20580,20 +20588,12 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>大清星湛-璞樂</t>
-        </is>
-      </c>
-      <c r="E432" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>大清上景</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr"/>
       <c r="F432" s="2" t="inlineStr"/>
-      <c r="G432" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區水青路520號對面</t>
-        </is>
-      </c>
+      <c r="G432" s="2" t="inlineStr"/>
       <c r="H432" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20601,7 +20601,7 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J432" s="2" t="inlineStr">
@@ -20628,16 +20628,20 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>大清璞樂</t>
+          <t>大清星湛-璞樂</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F433" s="2" t="inlineStr"/>
-      <c r="G433" s="2" t="inlineStr"/>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區水青路520號對面</t>
+        </is>
+      </c>
       <c r="H433" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20645,7 +20649,7 @@
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J433" s="2" t="inlineStr">
@@ -20672,7 +20676,7 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>大睦I-CITY(A19)</t>
+          <t>大清璞樂</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
@@ -20716,10 +20720,14 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>大睦站前首席</t>
-        </is>
-      </c>
-      <c r="E435" s="2" t="inlineStr"/>
+          <t>大睦I-CITY(A19)</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F435" s="2" t="inlineStr"/>
       <c r="G435" s="2" t="inlineStr"/>
       <c r="H435" s="2" t="inlineStr">
@@ -20756,14 +20764,10 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>大華畔</t>
-        </is>
-      </c>
-      <c r="E436" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>大睦站前首席</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr"/>
       <c r="F436" s="2" t="inlineStr"/>
       <c r="G436" s="2" t="inlineStr"/>
       <c r="H436" s="2" t="inlineStr">
@@ -20800,20 +20804,16 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>威均君藏</t>
+          <t>大華畔</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F437" s="2" t="inlineStr"/>
-      <c r="G437" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
-        </is>
-      </c>
+      <c r="G437" s="2" t="inlineStr"/>
       <c r="H437" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20821,7 +20821,7 @@
       </c>
       <c r="I437" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J437" s="2" t="inlineStr">
@@ -20848,7 +20848,7 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>威均天璽</t>
+          <t>威均君藏</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
@@ -20859,7 +20859,7 @@
       <c r="F438" s="2" t="inlineStr"/>
       <c r="G438" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區領航北路二段、永春路口</t>
+          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
         </is>
       </c>
       <c r="H438" s="2" t="inlineStr">
@@ -20896,12 +20896,20 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>宇惠曦</t>
-        </is>
-      </c>
-      <c r="E439" s="2" t="inlineStr"/>
+          <t>威均天璽</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F439" s="2" t="inlineStr"/>
-      <c r="G439" s="2" t="inlineStr"/>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區領航北路二段、永春路口</t>
+        </is>
+      </c>
       <c r="H439" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20909,7 +20917,7 @@
       </c>
       <c r="I439" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J439" s="2" t="inlineStr">
@@ -20936,20 +20944,12 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>宜誠丽左岸</t>
-        </is>
-      </c>
-      <c r="E440" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>宇惠曦</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr"/>
       <c r="F440" s="2" t="inlineStr"/>
-      <c r="G440" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區豐興段235地號</t>
-        </is>
-      </c>
+      <c r="G440" s="2" t="inlineStr"/>
       <c r="H440" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20957,7 +20957,7 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J440" s="2" t="inlineStr">
@@ -20984,16 +20984,20 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>宜誠泱</t>
+          <t>宜誠丽左岸</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F441" s="2" t="inlineStr"/>
-      <c r="G441" s="2" t="inlineStr"/>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區豐興段235地號</t>
+        </is>
+      </c>
       <c r="H441" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21001,7 +21005,7 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J441" s="2" t="inlineStr">
@@ -21028,10 +21032,14 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>宜雄湛</t>
-        </is>
-      </c>
-      <c r="E442" s="2" t="inlineStr"/>
+          <t>宜誠泱</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F442" s="2" t="inlineStr"/>
       <c r="G442" s="2" t="inlineStr"/>
       <c r="H442" s="2" t="inlineStr">
@@ -21068,7 +21076,7 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>宜雄湛</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr"/>
@@ -21108,20 +21116,12 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>寶台天馳</t>
-        </is>
-      </c>
-      <c r="E444" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>家瑞No.2</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr"/>
       <c r="F444" s="2" t="inlineStr"/>
-      <c r="G444" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青溪段450地號</t>
-        </is>
-      </c>
+      <c r="G444" s="2" t="inlineStr"/>
       <c r="H444" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21129,7 +21129,7 @@
       </c>
       <c r="I444" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J444" s="2" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>廣川市</t>
+          <t>寶台天馳</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
@@ -21167,7 +21167,7 @@
       <c r="F445" s="2" t="inlineStr"/>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+          <t>桃園市中壢區青溪段450地號</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -21204,12 +21204,20 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>弘鼎金家園</t>
-        </is>
-      </c>
-      <c r="E446" s="2" t="inlineStr"/>
+          <t>廣川市</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F446" s="2" t="inlineStr"/>
-      <c r="G446" s="2" t="inlineStr"/>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+        </is>
+      </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21217,7 +21225,7 @@
       </c>
       <c r="I446" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J446" s="2" t="inlineStr">
@@ -21244,14 +21252,10 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>悅新艾玥</t>
-        </is>
-      </c>
-      <c r="E447" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>弘鼎金家園</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr"/>
       <c r="F447" s="2" t="inlineStr"/>
       <c r="G447" s="2" t="inlineStr"/>
       <c r="H447" s="2" t="inlineStr">
@@ -21288,7 +21292,7 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>憶聲智匯科技園區</t>
+          <t>悅新艾玥</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
@@ -21332,20 +21336,16 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>新大萃</t>
+          <t>憶聲智匯科技園區</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr"/>
-      <c r="G449" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔五街</t>
-        </is>
-      </c>
+      <c r="G449" s="2" t="inlineStr"/>
       <c r="H449" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21353,7 +21353,7 @@
       </c>
       <c r="I449" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J449" s="2" t="inlineStr">
@@ -21380,12 +21380,20 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>昆旺青茵悦</t>
-        </is>
-      </c>
-      <c r="E450" s="2" t="inlineStr"/>
+          <t>新大萃</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F450" s="2" t="inlineStr"/>
-      <c r="G450" s="2" t="inlineStr"/>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔五街</t>
+        </is>
+      </c>
       <c r="H450" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21393,7 +21401,7 @@
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J450" s="2" t="inlineStr">
@@ -21420,28 +21428,20 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>昭揚天朗</t>
-        </is>
-      </c>
-      <c r="E451" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>昆旺青茵悦</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr"/>
       <c r="F451" s="2" t="inlineStr"/>
-      <c r="G451" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
-        </is>
-      </c>
+      <c r="G451" s="2" t="inlineStr"/>
       <c r="H451" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I451" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J451" s="2" t="inlineStr">
@@ -21468,20 +21468,28 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>晶采學</t>
-        </is>
-      </c>
-      <c r="E452" s="2" t="inlineStr"/>
+          <t>昭揚天朗</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F452" s="2" t="inlineStr"/>
-      <c r="G452" s="2" t="inlineStr"/>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
+        </is>
+      </c>
       <c r="H452" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J452" s="2" t="inlineStr">
@@ -21508,7 +21516,7 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>柏宣天擎</t>
+          <t>晶采學</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr"/>
@@ -21548,20 +21556,12 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>樂MORE</t>
-        </is>
-      </c>
-      <c r="E454" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>柏宣天擎</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr"/>
       <c r="F454" s="2" t="inlineStr"/>
-      <c r="G454" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區民溪三路209巷25號</t>
-        </is>
-      </c>
+      <c r="G454" s="2" t="inlineStr"/>
       <c r="H454" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21569,7 +21569,7 @@
       </c>
       <c r="I454" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J454" s="2" t="inlineStr">
@@ -21596,12 +21596,20 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>正發廠王NO.3</t>
-        </is>
-      </c>
-      <c r="E455" s="2" t="inlineStr"/>
+          <t>樂MORE</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F455" s="2" t="inlineStr"/>
-      <c r="G455" s="2" t="inlineStr"/>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區民溪三路209巷25號</t>
+        </is>
+      </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21609,7 +21617,7 @@
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr">
@@ -21636,20 +21644,12 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>深耕17</t>
-        </is>
-      </c>
-      <c r="E456" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>正發廠王NO.3</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr"/>
       <c r="F456" s="2" t="inlineStr"/>
-      <c r="G456" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區啟文路二段176巷21號對面</t>
-        </is>
-      </c>
+      <c r="G456" s="2" t="inlineStr"/>
       <c r="H456" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21657,7 +21657,7 @@
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J456" s="2" t="inlineStr">
@@ -21684,16 +21684,20 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>湘榭別墅</t>
+          <t>深耕17</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F457" s="2" t="inlineStr"/>
-      <c r="G457" s="2" t="inlineStr"/>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區啟文路二段176巷21號對面</t>
+        </is>
+      </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21701,7 +21705,7 @@
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J457" s="2" t="inlineStr">
@@ -21728,20 +21732,16 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>澍之丘</t>
+          <t>湘榭別墅</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr"/>
-      <c r="G458" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區月桃路615巷</t>
-        </is>
-      </c>
+      <c r="G458" s="2" t="inlineStr"/>
       <c r="H458" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21749,7 +21749,7 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">
@@ -21776,16 +21776,20 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>璟城A22</t>
+          <t>澍之丘</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr"/>
-      <c r="G459" s="2" t="inlineStr"/>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區月桃路615巷</t>
+        </is>
+      </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21793,7 +21797,7 @@
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr">
@@ -21820,7 +21824,7 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>皇普園首之道</t>
+          <t>璟城A22</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
@@ -21864,20 +21868,16 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>皇普賦隱</t>
+          <t>皇普園首之道</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F461" s="2" t="inlineStr"/>
-      <c r="G461" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔二街</t>
-        </is>
-      </c>
+      <c r="G461" s="2" t="inlineStr"/>
       <c r="H461" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21885,7 +21885,7 @@
       </c>
       <c r="I461" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J461" s="2" t="inlineStr">
@@ -21912,16 +21912,20 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>益展有福</t>
+          <t>皇普賦隱</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr"/>
-      <c r="G462" s="2" t="inlineStr"/>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔二街</t>
+        </is>
+      </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21929,7 +21933,7 @@
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J462" s="2" t="inlineStr">
@@ -21956,7 +21960,7 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>立信悦榕</t>
+          <t>益展有福</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
@@ -21978,7 +21982,7 @@
       </c>
       <c r="J463" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -22000,7 +22004,7 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>站前新鋭</t>
+          <t>立信悦榕</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
@@ -22022,7 +22026,7 @@
       </c>
       <c r="J464" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -22044,7 +22048,7 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>綠意領航1號</t>
+          <t>站前新鋭</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
@@ -22088,20 +22092,16 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>聚泰雲藝</t>
+          <t>綠意領航1號</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F466" s="2" t="inlineStr"/>
-      <c r="G466" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區元生三街</t>
-        </is>
-      </c>
+      <c r="G466" s="2" t="inlineStr"/>
       <c r="H466" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="I466" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J466" s="2" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>聯懋杉苑</t>
+          <t>聚泰雲藝</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
@@ -22147,7 +22147,7 @@
       <c r="F467" s="2" t="inlineStr"/>
       <c r="G467" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區靠近興西二路及興北二路</t>
+          <t>桃園市中壢區元生三街</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
@@ -22184,16 +22184,20 @@
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>聯懋杉苑</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F468" s="2" t="inlineStr"/>
-      <c r="G468" s="2" t="inlineStr"/>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區靠近興西二路及興北二路</t>
+        </is>
+      </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22201,7 +22205,7 @@
       </c>
       <c r="I468" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J468" s="2" t="inlineStr">
@@ -22228,7 +22232,7 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>菁美學</t>
+          <t>荷沐莊園</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
@@ -22272,7 +22276,7 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-THE ONE</t>
+          <t>菁美學</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
@@ -22316,7 +22320,7 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-綠景苑</t>
+          <t>藍海帝國-THE ONE</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
@@ -22360,10 +22364,14 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>誠鑫19</t>
-        </is>
-      </c>
-      <c r="E472" s="2" t="inlineStr"/>
+          <t>藍海帝國-綠景苑</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F472" s="2" t="inlineStr"/>
       <c r="G472" s="2" t="inlineStr"/>
       <c r="H472" s="2" t="inlineStr">
@@ -22400,14 +22408,10 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>路易威登</t>
-        </is>
-      </c>
-      <c r="E473" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>誠鑫19</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr"/>
       <c r="F473" s="2" t="inlineStr"/>
       <c r="G473" s="2" t="inlineStr"/>
       <c r="H473" s="2" t="inlineStr">
@@ -22444,7 +22448,7 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>鑫利川-三城</t>
+          <t>路易威登</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -22488,7 +22492,7 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>閣美學</t>
+          <t>鑫利川-三城</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
@@ -22532,7 +22536,7 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>青城之愛3</t>
+          <t>閣美學</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
@@ -22576,7 +22580,7 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>鴻廣川湛</t>
+          <t>青城之愛3</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
@@ -22620,20 +22624,16 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>鴻踞樸藝</t>
+          <t>鴻廣川湛</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr"/>
-      <c r="G478" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區興北一路及興東路 交叉口</t>
-        </is>
-      </c>
+      <c r="G478" s="2" t="inlineStr"/>
       <c r="H478" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22641,7 +22641,7 @@
       </c>
       <c r="I478" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J478" s="2" t="inlineStr">
@@ -22663,21 +22663,25 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>三鶯澤苑</t>
+          <t>鴻踞樸藝</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr"/>
-      <c r="G479" s="2" t="inlineStr"/>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興北一路及興東路 交叉口</t>
+        </is>
+      </c>
       <c r="H479" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22685,7 +22689,7 @@
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J479" s="2" t="inlineStr">
@@ -22712,20 +22716,16 @@
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>上順麗</t>
+          <t>三鶯澤苑</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr"/>
-      <c r="G480" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區客運一段340地號</t>
-        </is>
-      </c>
+      <c r="G480" s="2" t="inlineStr"/>
       <c r="H480" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22733,7 +22733,7 @@
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J480" s="2" t="inlineStr">
@@ -22760,16 +22760,20 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>中麗北極星</t>
+          <t>上順麗</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr"/>
-      <c r="G481" s="2" t="inlineStr"/>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區客運一段340地號</t>
+        </is>
+      </c>
       <c r="H481" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22777,7 +22781,7 @@
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J481" s="2" t="inlineStr">
@@ -22804,7 +22808,7 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>京懋敦和</t>
+          <t>中麗北極星</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
@@ -22848,7 +22852,7 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>佳暘青見</t>
+          <t>京懋敦和</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
@@ -22892,20 +22896,16 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>偉築新豐州</t>
+          <t>佳暘青見</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F484" s="2" t="inlineStr"/>
-      <c r="G484" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區青峰路二段117~129號</t>
-        </is>
-      </c>
+      <c r="G484" s="2" t="inlineStr"/>
       <c r="H484" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="I484" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J484" s="2" t="inlineStr">
@@ -22940,16 +22940,20 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>傳佳樂</t>
+          <t>偉築新豐州</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr"/>
-      <c r="G485" s="2" t="inlineStr"/>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區青峰路二段117~129號</t>
+        </is>
+      </c>
       <c r="H485" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22957,7 +22961,7 @@
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr">
@@ -22984,7 +22988,7 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>元基至善2</t>
+          <t>傳佳樂</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
@@ -23028,7 +23032,7 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>力璞翔-豐禾</t>
+          <t>元基至善2</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
@@ -23050,7 +23054,7 @@
       </c>
       <c r="J487" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -23072,20 +23076,16 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>合展悦恬</t>
+          <t>力璞翔-豐禾</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F488" s="2" t="inlineStr"/>
-      <c r="G488" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G488" s="2" t="inlineStr"/>
       <c r="H488" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23093,12 +23093,12 @@
       </c>
       <c r="I488" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J488" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -23120,18 +23120,18 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>合陽逸境</t>
+          <t>合展悦恬</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr"/>
       <c r="G489" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區青峰段273號地號</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H489" s="2" t="inlineStr">
@@ -23168,18 +23168,18 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>名川琢域</t>
+          <t>合陽逸境</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr"/>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
+          <t>桃園市大園區青峰段273號地號</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -23216,18 +23216,18 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅</t>
+          <t>名川琢域</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr"/>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區內海墘段 110-84</t>
+          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -23264,12 +23264,20 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅Villa</t>
-        </is>
-      </c>
-      <c r="E492" s="2" t="inlineStr"/>
+          <t>垽赫海漾星墅</t>
+        </is>
+      </c>
+      <c r="E492" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F492" s="2" t="inlineStr"/>
-      <c r="G492" s="2" t="inlineStr"/>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區內海墘段 110-84</t>
+        </is>
+      </c>
       <c r="H492" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23277,7 +23285,7 @@
       </c>
       <c r="I492" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J492" s="2" t="inlineStr">
@@ -23304,20 +23312,12 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
-        </is>
-      </c>
-      <c r="E493" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>垽赫海漾星墅Villa</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr"/>
       <c r="F493" s="2" t="inlineStr"/>
-      <c r="G493" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園七街9號對面</t>
-        </is>
-      </c>
+      <c r="G493" s="2" t="inlineStr"/>
       <c r="H493" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23325,7 +23325,7 @@
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J493" s="2" t="inlineStr">
@@ -23352,16 +23352,20 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>大地玥</t>
+          <t>大地昕</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F494" s="2" t="inlineStr"/>
-      <c r="G494" s="2" t="inlineStr"/>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區園七街9號對面</t>
+        </is>
+      </c>
       <c r="H494" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23369,7 +23373,7 @@
       </c>
       <c r="I494" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J494" s="2" t="inlineStr">
@@ -23396,7 +23400,7 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>大地．呈</t>
+          <t>大地玥</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
@@ -23440,7 +23444,7 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>大禾苑</t>
+          <t>大地．呈</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
@@ -23484,7 +23488,7 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>威均帝璽</t>
+          <t>大禾苑</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
@@ -23528,20 +23532,16 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>宗佳領御</t>
+          <t>威均帝璽</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F498" s="2" t="inlineStr"/>
-      <c r="G498" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區中路與科七街</t>
-        </is>
-      </c>
+      <c r="G498" s="2" t="inlineStr"/>
       <c r="H498" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23549,7 +23549,7 @@
       </c>
       <c r="I498" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J498" s="2" t="inlineStr">
@@ -23576,16 +23576,20 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>宜誠玉環</t>
+          <t>宗佳領御</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr"/>
-      <c r="G499" s="2" t="inlineStr"/>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區中路與科七街</t>
+        </is>
+      </c>
       <c r="H499" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23593,7 +23597,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr">
@@ -23620,7 +23624,7 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>家綻</t>
+          <t>宜誠玉環</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
@@ -23664,20 +23668,16 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>家綻2</t>
+          <t>家綻</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F501" s="2" t="inlineStr"/>
-      <c r="G501" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區柴梳崙路268巷</t>
-        </is>
-      </c>
+      <c r="G501" s="2" t="inlineStr"/>
       <c r="H501" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="I501" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J501" s="2" t="inlineStr">
@@ -23712,16 +23712,20 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>富總日日</t>
+          <t>家綻2</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr"/>
-      <c r="G502" s="2" t="inlineStr"/>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區柴梳崙路268巷</t>
+        </is>
+      </c>
       <c r="H502" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23729,7 +23733,7 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
@@ -23756,10 +23760,14 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>山榆.柏悅</t>
-        </is>
-      </c>
-      <c r="E503" s="2" t="inlineStr"/>
+          <t>富總日日</t>
+        </is>
+      </c>
+      <c r="E503" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F503" s="2" t="inlineStr"/>
       <c r="G503" s="2" t="inlineStr"/>
       <c r="H503" s="2" t="inlineStr">
@@ -23774,7 +23782,7 @@
       </c>
       <c r="J503" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -23796,20 +23804,12 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>山榆柏悅</t>
-        </is>
-      </c>
-      <c r="E504" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>山榆.柏悅</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr"/>
       <c r="F504" s="2" t="inlineStr"/>
-      <c r="G504" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區永園路二段152號旁</t>
-        </is>
-      </c>
+      <c r="G504" s="2" t="inlineStr"/>
       <c r="H504" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23817,12 +23817,12 @@
       </c>
       <c r="I504" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J504" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -23844,16 +23844,20 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>川洋青勻</t>
+          <t>山榆柏悅</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F505" s="2" t="inlineStr"/>
-      <c r="G505" s="2" t="inlineStr"/>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區永園路二段152號旁</t>
+        </is>
+      </c>
       <c r="H505" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23861,7 +23865,7 @@
       </c>
       <c r="I505" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J505" s="2" t="inlineStr">
@@ -23888,7 +23892,7 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>御禾院</t>
+          <t>川洋青勻</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
@@ -23932,20 +23936,16 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>悦恬</t>
+          <t>御禾院</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F507" s="2" t="inlineStr"/>
-      <c r="G507" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G507" s="2" t="inlineStr"/>
       <c r="H507" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23953,7 +23953,7 @@
       </c>
       <c r="I507" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J507" s="2" t="inlineStr">
@@ -23980,7 +23980,7 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>日勝好日子</t>
+          <t>悦恬</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
@@ -23991,7 +23991,7 @@
       <c r="F508" s="2" t="inlineStr"/>
       <c r="G508" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區後館路1巷旁</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H508" s="2" t="inlineStr">
@@ -24028,7 +24028,7 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>日青悠</t>
+          <t>日勝好日子</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
@@ -24039,7 +24039,7 @@
       <c r="F509" s="2" t="inlineStr"/>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區五青路63巷257號旁</t>
+          <t>桃園市大園區後館路1巷旁</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
@@ -24076,12 +24076,20 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>松合苑5</t>
-        </is>
-      </c>
-      <c r="E510" s="2" t="inlineStr"/>
+          <t>日青悠</t>
+        </is>
+      </c>
+      <c r="E510" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F510" s="2" t="inlineStr"/>
-      <c r="G510" s="2" t="inlineStr"/>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區五青路63巷257號旁</t>
+        </is>
+      </c>
       <c r="H510" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24089,7 +24097,7 @@
       </c>
       <c r="I510" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J510" s="2" t="inlineStr">
@@ -24116,20 +24124,12 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>璟都新世界</t>
-        </is>
-      </c>
-      <c r="E511" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>松合苑5</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr"/>
       <c r="F511" s="2" t="inlineStr"/>
-      <c r="G511" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區大觀路及環區北路口</t>
-        </is>
-      </c>
+      <c r="G511" s="2" t="inlineStr"/>
       <c r="H511" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24137,7 +24137,7 @@
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J511" s="2" t="inlineStr">
@@ -24164,16 +24164,20 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>福興豐璟</t>
+          <t>璟都新世界</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F512" s="2" t="inlineStr"/>
-      <c r="G512" s="2" t="inlineStr"/>
+      <c r="G512" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區大觀路及環區北路口</t>
+        </is>
+      </c>
       <c r="H512" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24181,7 +24185,7 @@
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J512" s="2" t="inlineStr">
@@ -24208,7 +24212,7 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>立程·晴美</t>
+          <t>福興豐璟</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
@@ -24252,20 +24256,16 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>立程‧晴美</t>
+          <t>立程·晴美</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F514" s="2" t="inlineStr"/>
-      <c r="G514" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區學七街69-1號</t>
-        </is>
-      </c>
+      <c r="G514" s="2" t="inlineStr"/>
       <c r="H514" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24273,7 +24273,7 @@
       </c>
       <c r="I514" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J514" s="2" t="inlineStr">
@@ -24300,23 +24300,23 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>立程建設客運二段案</t>
+          <t>立程‧晴美</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F515" s="2" t="inlineStr"/>
       <c r="G515" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區學七街69-1號旁</t>
+          <t>桃園市大園區學七街69-1號</t>
         </is>
       </c>
       <c r="H515" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I515" s="2" t="inlineStr">
@@ -24348,29 +24348,33 @@
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>立鴻晶硯</t>
+          <t>立程建設客運二段案</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F516" s="2" t="inlineStr"/>
-      <c r="G516" s="2" t="inlineStr"/>
+      <c r="G516" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區學七街69-1號旁</t>
+        </is>
+      </c>
       <c r="H516" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I516" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J516" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -24392,7 +24396,7 @@
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>臥墨池</t>
+          <t>立鴻晶硯</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
@@ -24414,7 +24418,7 @@
       </c>
       <c r="J517" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24436,7 +24440,7 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>臻璞</t>
+          <t>臥墨池</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
@@ -24480,7 +24484,7 @@
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>興禾  築美學</t>
+          <t>臻璞</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
@@ -24524,20 +24528,16 @@
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>航綻甜心</t>
+          <t>興禾  築美學</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F520" s="2" t="inlineStr"/>
-      <c r="G520" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路與科五路交叉口</t>
-        </is>
-      </c>
+      <c r="G520" s="2" t="inlineStr"/>
       <c r="H520" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24545,7 +24545,7 @@
       </c>
       <c r="I520" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J520" s="2" t="inlineStr">
@@ -24572,16 +24572,20 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>英堡日朗</t>
+          <t>航綻甜心</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr"/>
-      <c r="G521" s="2" t="inlineStr"/>
+      <c r="G521" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路與科五路交叉口</t>
+        </is>
+      </c>
       <c r="H521" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24589,7 +24593,7 @@
       </c>
       <c r="I521" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J521" s="2" t="inlineStr">
@@ -24616,20 +24620,16 @@
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>薪成家II</t>
+          <t>英堡日朗</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr"/>
-      <c r="G522" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路597號</t>
-        </is>
-      </c>
+      <c r="G522" s="2" t="inlineStr"/>
       <c r="H522" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24637,7 +24637,7 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J522" s="2" t="inlineStr">
@@ -24664,16 +24664,20 @@
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>逸偉A+</t>
+          <t>薪成家II</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr"/>
-      <c r="G523" s="2" t="inlineStr"/>
+      <c r="G523" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路597號</t>
+        </is>
+      </c>
       <c r="H523" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24681,7 +24685,7 @@
       </c>
       <c r="I523" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J523" s="2" t="inlineStr">
@@ -24708,10 +24712,14 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>遠雄仰森</t>
-        </is>
-      </c>
-      <c r="E524" s="2" t="inlineStr"/>
+          <t>逸偉A+</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F524" s="2" t="inlineStr"/>
       <c r="G524" s="2" t="inlineStr"/>
       <c r="H524" s="2" t="inlineStr">
@@ -24748,14 +24756,10 @@
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>鈞貴極美II</t>
-        </is>
-      </c>
-      <c r="E525" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>遠雄仰森</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr"/>
       <c r="F525" s="2" t="inlineStr"/>
       <c r="G525" s="2" t="inlineStr"/>
       <c r="H525" s="2" t="inlineStr">
@@ -24792,7 +24796,7 @@
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>高誠君品</t>
+          <t>鈞貴極美II</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
@@ -24836,10 +24840,14 @@
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>龍築靜玥</t>
-        </is>
-      </c>
-      <c r="E527" s="2" t="inlineStr"/>
+          <t>高誠君品</t>
+        </is>
+      </c>
+      <c r="E527" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F527" s="2" t="inlineStr"/>
       <c r="G527" s="2" t="inlineStr"/>
       <c r="H527" s="2" t="inlineStr">
@@ -24858,15 +24866,55 @@
         </is>
       </c>
     </row>
-    <row r="529">
-      <c r="A529" s="3" t="inlineStr">
-        <is>
-          <t>最後更新：2026-10-21 13:02（台灣時間）　共 526 筆　資料來源：好房網、樂屋網</t>
+    <row r="528">
+      <c r="A528" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B528" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C528" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D528" s="2" t="inlineStr">
+        <is>
+          <t>龍築靜玥</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr"/>
+      <c r="F528" s="2" t="inlineStr"/>
+      <c r="G528" s="2" t="inlineStr"/>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I528" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J528" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="3" t="inlineStr">
+        <is>
+          <t>最後更新：2026-10-22 13:03（台灣時間）　共 527 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J527"/>
+  <autoFilter ref="A1:J528"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24909,7 +24909,7 @@
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-22 13:03（台灣時間）　共 527 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-23 13:04（台灣時間）　共 527 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24909,7 +24909,7 @@
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-23 13:04（台灣時間）　共 527 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-24 12:49（台灣時間）　共 527 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24909,7 +24909,7 @@
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-24 12:49（台灣時間）　共 527 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-25 12:56（台灣時間）　共 527 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預售案清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$528</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'預售案清單'!$A$1:$J$529</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J530"/>
+  <dimension ref="A1:J531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18039,12 +18039,12 @@
       <c r="F377" s="2" t="inlineStr"/>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>新北市永和區永和路一段45號</t>
+          <t>新北市永和區永和路一段</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I377" s="2" t="inlineStr">
@@ -19312,23 +19312,23 @@
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>員邦徊</t>
+          <t>和光富邑</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr"/>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路72巷</t>
+          <t>新北市淡水區新市二路三段36巷8~38號</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I405" s="2" t="inlineStr">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="J405" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -19360,23 +19360,23 @@
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>嘉潤家泰氧之森</t>
+          <t>員邦徊</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr"/>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區坪頂路88號</t>
+          <t>新北市淡水區坪頂路72巷</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I406" s="2" t="inlineStr">
@@ -19408,23 +19408,23 @@
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>富麗ONE</t>
+          <t>嘉潤家泰氧之森</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr"/>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區新市段118地號</t>
+          <t>新北市淡水區坪頂路88號</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I407" s="2" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>將捷建設紅樹林案</t>
+          <t>富麗ONE</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -19467,12 +19467,12 @@
       <c r="F408" s="2" t="inlineStr"/>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
+          <t>新北市淡水區新市段118地號</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I408" s="2" t="inlineStr">
@@ -19504,23 +19504,23 @@
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>山河帝寶</t>
+          <t>將捷建設紅樹林案</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
         <is>
-          <t>萬/戶</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F409" s="2" t="inlineStr"/>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
+          <t>新北市淡水區淡金路、中正東路一段交叉口</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I409" s="2" t="inlineStr">
@@ -19552,18 +19552,18 @@
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>新海城</t>
+          <t>山河帝寶</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬/戶</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr"/>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路二段、新市二路</t>
+          <t>新北市淡水區紅樹林路與中正東路二段5巷口</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -19600,16 +19600,20 @@
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>新海城2夢想市</t>
+          <t>新海城</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr"/>
-      <c r="G411" s="2" t="inlineStr"/>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區沙崙路二段、新市二路</t>
+        </is>
+      </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19617,7 +19621,7 @@
       </c>
       <c r="I411" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J411" s="2" t="inlineStr">
@@ -19644,28 +19648,24 @@
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>村泉蒔美</t>
+          <t>新海城2夢想市</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr"/>
-      <c r="G412" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區中正東路二段143巷12弄</t>
-        </is>
-      </c>
+      <c r="G412" s="2" t="inlineStr"/>
       <c r="H412" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I412" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J412" s="2" t="inlineStr">
@@ -19692,7 +19692,7 @@
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>水問山</t>
+          <t>村泉蒔美</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
@@ -19703,7 +19703,7 @@
       <c r="F413" s="2" t="inlineStr"/>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段143巷2弄</t>
+          <t>新北市淡水區中正東路二段143巷12弄</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -19740,23 +19740,23 @@
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>水美慕河</t>
+          <t>水問山</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr"/>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路一段47號</t>
+          <t>新北市淡水區中正東路二段143巷2弄</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I414" s="2" t="inlineStr">
@@ -19788,18 +19788,18 @@
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>湯泉紅樹林</t>
+          <t>水美慕河</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr"/>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區中正東路二段5巷35號</t>
+          <t>新北市淡水區中正東路一段47號</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>石上青</t>
+          <t>湯泉紅樹林</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -19847,7 +19847,7 @@
       <c r="F416" s="2" t="inlineStr"/>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區八勢一街36號</t>
+          <t>新北市淡水區中正東路二段5巷35號</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -19884,7 +19884,7 @@
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>致茂橋豐</t>
+          <t>石上青</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
@@ -19895,7 +19895,7 @@
       <c r="F417" s="2" t="inlineStr"/>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區沙崙路一段</t>
+          <t>新北市淡水區八勢一街36號</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -19932,18 +19932,18 @@
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>藝沐汀</t>
+          <t>致茂橋豐</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr"/>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>新北市淡水區民族路、自強路305巷</t>
+          <t>新北市淡水區沙崙路一段</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -19980,16 +19980,20 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>馥人灣-新濠門</t>
+          <t>藝沐汀</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr"/>
-      <c r="G419" s="2" t="inlineStr"/>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>新北市淡水區民族路、自強路305巷</t>
+        </is>
+      </c>
       <c r="H419" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -19997,7 +20001,7 @@
       </c>
       <c r="I419" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J419" s="2" t="inlineStr">
@@ -20024,20 +20028,16 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>鴻灃COMO</t>
+          <t>馥人灣-新濠門</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr"/>
-      <c r="G420" s="2" t="inlineStr">
-        <is>
-          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
-        </is>
-      </c>
+      <c r="G420" s="2" t="inlineStr"/>
       <c r="H420" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20045,7 +20045,7 @@
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J420" s="2" t="inlineStr">
@@ -20057,33 +20057,33 @@
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>桃園市（青埔）</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>青埔周邊（中壢/大園）</t>
+          <t>淡水汐止線</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>中壢區</t>
+          <t>淡水區</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>A20-合磊天沐</t>
+          <t>鴻灃COMO</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr"/>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+          <t>新北市淡水區新市二路一段與崁頂五路交叉口</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -20120,16 +20120,20 @@
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>The Nexus 新識界</t>
+          <t>A20-合磊天沐</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F422" s="2" t="inlineStr"/>
-      <c r="G422" s="2" t="inlineStr"/>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐北路一段、興北一路口</t>
+        </is>
+      </c>
       <c r="H422" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20137,7 +20141,7 @@
       </c>
       <c r="I422" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J422" s="2" t="inlineStr">
@@ -20164,7 +20168,7 @@
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>一品閣</t>
+          <t>The Nexus 新識界</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
@@ -20208,20 +20212,16 @@
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>中麗若隱</t>
+          <t>一品閣</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr"/>
-      <c r="G424" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
-        </is>
-      </c>
+      <c r="G424" s="2" t="inlineStr"/>
       <c r="H424" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20229,7 +20229,7 @@
       </c>
       <c r="I424" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J424" s="2" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>享JIA</t>
+          <t>中麗若隱</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
@@ -20267,7 +20267,7 @@
       <c r="F425" s="2" t="inlineStr"/>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區青山一路157號旁</t>
+          <t>桃園市中壢區高鐵南路三段＆文康二路口</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -20304,18 +20304,18 @@
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>保利首綻</t>
+          <t>享JIA</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr"/>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區中豐路225號對面</t>
+          <t>桃園市中壢區青山一路157號旁</t>
         </is>
       </c>
       <c r="H426" s="2" t="inlineStr">
@@ -20352,16 +20352,20 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>勤樸悅圓</t>
+          <t>保利首綻</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr"/>
-      <c r="G427" s="2" t="inlineStr"/>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區中豐路225號對面</t>
+        </is>
+      </c>
       <c r="H427" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20369,7 +20373,7 @@
       </c>
       <c r="I427" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J427" s="2" t="inlineStr">
@@ -20396,20 +20400,16 @@
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>君臨塘詩-慕荷</t>
+          <t>勤樸悅圓</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F428" s="2" t="inlineStr"/>
-      <c r="G428" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
-        </is>
-      </c>
+      <c r="G428" s="2" t="inlineStr"/>
       <c r="H428" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20417,7 +20417,7 @@
       </c>
       <c r="I428" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J428" s="2" t="inlineStr">
@@ -20444,18 +20444,18 @@
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>和發采采</t>
+          <t>君臨塘詩-慕荷</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
         <is>
-          <t>萬/坪起</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F429" s="2" t="inlineStr"/>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區新生路二段378之2號對面</t>
+          <t>桃園市中壢區福嶺路一段＆福祥路458巷路口</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -20492,18 +20492,18 @@
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>品坤學</t>
+          <t>和發采采</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪起</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr"/>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區環西路二段25巷11號旁</t>
+          <t>桃園市中壢區新生路二段378之2號對面</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
@@ -20540,18 +20540,18 @@
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>大亮FIKA</t>
+          <t>品坤學</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr"/>
       <c r="G431" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區永順一街30號旁</t>
+          <t>桃園市中壢區環西路二段25巷11號旁</t>
         </is>
       </c>
       <c r="H431" s="2" t="inlineStr">
@@ -20588,12 +20588,20 @@
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>大清上景</t>
-        </is>
-      </c>
-      <c r="E432" s="2" t="inlineStr"/>
+          <t>大亮FIKA</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F432" s="2" t="inlineStr"/>
-      <c r="G432" s="2" t="inlineStr"/>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區永順一街30號旁</t>
+        </is>
+      </c>
       <c r="H432" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20601,7 +20609,7 @@
       </c>
       <c r="I432" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J432" s="2" t="inlineStr">
@@ -20628,20 +20636,12 @@
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>大清星湛-璞樂</t>
-        </is>
-      </c>
-      <c r="E433" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>大清上景</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr"/>
       <c r="F433" s="2" t="inlineStr"/>
-      <c r="G433" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區水青路520號對面</t>
-        </is>
-      </c>
+      <c r="G433" s="2" t="inlineStr"/>
       <c r="H433" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20649,7 +20649,7 @@
       </c>
       <c r="I433" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J433" s="2" t="inlineStr">
@@ -20676,16 +20676,20 @@
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>大清璞樂</t>
+          <t>大清星湛-璞樂</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F434" s="2" t="inlineStr"/>
-      <c r="G434" s="2" t="inlineStr"/>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區水青路520號對面</t>
+        </is>
+      </c>
       <c r="H434" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20693,7 +20697,7 @@
       </c>
       <c r="I434" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J434" s="2" t="inlineStr">
@@ -20720,7 +20724,7 @@
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>大睦I-CITY(A19)</t>
+          <t>大清璞樂</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
@@ -20764,10 +20768,14 @@
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>大睦站前首席</t>
-        </is>
-      </c>
-      <c r="E436" s="2" t="inlineStr"/>
+          <t>大睦I-CITY(A19)</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F436" s="2" t="inlineStr"/>
       <c r="G436" s="2" t="inlineStr"/>
       <c r="H436" s="2" t="inlineStr">
@@ -20804,14 +20812,10 @@
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>大華畔</t>
-        </is>
-      </c>
-      <c r="E437" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>大睦站前首席</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr"/>
       <c r="F437" s="2" t="inlineStr"/>
       <c r="G437" s="2" t="inlineStr"/>
       <c r="H437" s="2" t="inlineStr">
@@ -20848,20 +20852,16 @@
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>威均君藏</t>
+          <t>大華畔</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr"/>
-      <c r="G438" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
-        </is>
-      </c>
+      <c r="G438" s="2" t="inlineStr"/>
       <c r="H438" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20869,7 +20869,7 @@
       </c>
       <c r="I438" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J438" s="2" t="inlineStr">
@@ -20896,7 +20896,7 @@
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>威均天璽</t>
+          <t>威均君藏</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
@@ -20907,7 +20907,7 @@
       <c r="F439" s="2" t="inlineStr"/>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區領航北路二段、永春路口</t>
+          <t>桃園市中壢區領航北路二段、永信路交叉口</t>
         </is>
       </c>
       <c r="H439" s="2" t="inlineStr">
@@ -20944,12 +20944,20 @@
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>宇惠曦</t>
-        </is>
-      </c>
-      <c r="E440" s="2" t="inlineStr"/>
+          <t>威均天璽</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F440" s="2" t="inlineStr"/>
-      <c r="G440" s="2" t="inlineStr"/>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區領航北路二段、永春路口</t>
+        </is>
+      </c>
       <c r="H440" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -20957,7 +20965,7 @@
       </c>
       <c r="I440" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J440" s="2" t="inlineStr">
@@ -20984,20 +20992,12 @@
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>宜誠丽左岸</t>
-        </is>
-      </c>
-      <c r="E441" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>宇惠曦</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr"/>
       <c r="F441" s="2" t="inlineStr"/>
-      <c r="G441" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區豐興段235地號</t>
-        </is>
-      </c>
+      <c r="G441" s="2" t="inlineStr"/>
       <c r="H441" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21005,7 +21005,7 @@
       </c>
       <c r="I441" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J441" s="2" t="inlineStr">
@@ -21032,16 +21032,20 @@
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>宜誠泱</t>
+          <t>宜誠丽左岸</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr"/>
-      <c r="G442" s="2" t="inlineStr"/>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區豐興段235地號</t>
+        </is>
+      </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21049,7 +21053,7 @@
       </c>
       <c r="I442" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J442" s="2" t="inlineStr">
@@ -21076,10 +21080,14 @@
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>宜雄湛</t>
-        </is>
-      </c>
-      <c r="E443" s="2" t="inlineStr"/>
+          <t>宜誠泱</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F443" s="2" t="inlineStr"/>
       <c r="G443" s="2" t="inlineStr"/>
       <c r="H443" s="2" t="inlineStr">
@@ -21116,7 +21124,7 @@
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>家瑞No.2</t>
+          <t>宜雄湛</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr"/>
@@ -21156,20 +21164,12 @@
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>寶台天馳</t>
-        </is>
-      </c>
-      <c r="E445" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>家瑞No.2</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr"/>
       <c r="F445" s="2" t="inlineStr"/>
-      <c r="G445" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青溪段450地號</t>
-        </is>
-      </c>
+      <c r="G445" s="2" t="inlineStr"/>
       <c r="H445" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21177,7 +21177,7 @@
       </c>
       <c r="I445" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J445" s="2" t="inlineStr">
@@ -21204,7 +21204,7 @@
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>廣川市</t>
+          <t>寶台天馳</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
@@ -21215,7 +21215,7 @@
       <c r="F446" s="2" t="inlineStr"/>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+          <t>桃園市中壢區青溪段450地號</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
@@ -21252,12 +21252,20 @@
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>弘鼎金家園</t>
-        </is>
-      </c>
-      <c r="E447" s="2" t="inlineStr"/>
+          <t>廣川市</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F447" s="2" t="inlineStr"/>
-      <c r="G447" s="2" t="inlineStr"/>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區聖德路一段、崇德二路口</t>
+        </is>
+      </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21265,7 +21273,7 @@
       </c>
       <c r="I447" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J447" s="2" t="inlineStr">
@@ -21292,14 +21300,10 @@
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>悅新艾玥</t>
-        </is>
-      </c>
-      <c r="E448" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>弘鼎金家園</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr"/>
       <c r="F448" s="2" t="inlineStr"/>
       <c r="G448" s="2" t="inlineStr"/>
       <c r="H448" s="2" t="inlineStr">
@@ -21336,7 +21340,7 @@
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>憶聲智匯科技園區</t>
+          <t>悅新艾玥</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
@@ -21380,20 +21384,16 @@
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>新大萃</t>
+          <t>憶聲智匯科技園區</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr"/>
-      <c r="G450" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔五街</t>
-        </is>
-      </c>
+      <c r="G450" s="2" t="inlineStr"/>
       <c r="H450" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21401,7 +21401,7 @@
       </c>
       <c r="I450" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J450" s="2" t="inlineStr">
@@ -21428,12 +21428,20 @@
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>昆旺青茵悦</t>
-        </is>
-      </c>
-      <c r="E451" s="2" t="inlineStr"/>
+          <t>新大萃</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F451" s="2" t="inlineStr"/>
-      <c r="G451" s="2" t="inlineStr"/>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔五街</t>
+        </is>
+      </c>
       <c r="H451" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21441,7 +21449,7 @@
       </c>
       <c r="I451" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J451" s="2" t="inlineStr">
@@ -21468,28 +21476,20 @@
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>昭揚天朗</t>
-        </is>
-      </c>
-      <c r="E452" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>昆旺青茵悦</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr"/>
       <c r="F452" s="2" t="inlineStr"/>
-      <c r="G452" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
-        </is>
-      </c>
+      <c r="G452" s="2" t="inlineStr"/>
       <c r="H452" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I452" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J452" s="2" t="inlineStr">
@@ -21516,20 +21516,28 @@
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>晶采學</t>
-        </is>
-      </c>
-      <c r="E453" s="2" t="inlineStr"/>
+          <t>昭揚天朗</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F453" s="2" t="inlineStr"/>
-      <c r="G453" s="2" t="inlineStr"/>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區和豐街、興東路、10米計畫道路</t>
+        </is>
+      </c>
       <c r="H453" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I453" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J453" s="2" t="inlineStr">
@@ -21556,7 +21564,7 @@
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>柏宣天擎</t>
+          <t>晶采學</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr"/>
@@ -21596,20 +21604,12 @@
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>樂MORE</t>
-        </is>
-      </c>
-      <c r="E455" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>柏宣天擎</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr"/>
       <c r="F455" s="2" t="inlineStr"/>
-      <c r="G455" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區民溪三路209巷25號</t>
-        </is>
-      </c>
+      <c r="G455" s="2" t="inlineStr"/>
       <c r="H455" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="I455" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J455" s="2" t="inlineStr">
@@ -21644,12 +21644,20 @@
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>正發廠王NO.3</t>
-        </is>
-      </c>
-      <c r="E456" s="2" t="inlineStr"/>
+          <t>樂MORE</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F456" s="2" t="inlineStr"/>
-      <c r="G456" s="2" t="inlineStr"/>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區民溪三路209巷25號</t>
+        </is>
+      </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21657,7 +21665,7 @@
       </c>
       <c r="I456" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J456" s="2" t="inlineStr">
@@ -21684,20 +21692,12 @@
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>深耕17</t>
-        </is>
-      </c>
-      <c r="E457" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>正發廠王NO.3</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr"/>
       <c r="F457" s="2" t="inlineStr"/>
-      <c r="G457" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區啟文路二段176巷21號對面</t>
-        </is>
-      </c>
+      <c r="G457" s="2" t="inlineStr"/>
       <c r="H457" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21705,7 +21705,7 @@
       </c>
       <c r="I457" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J457" s="2" t="inlineStr">
@@ -21732,16 +21732,20 @@
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>湘榭別墅</t>
+          <t>深耕17</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F458" s="2" t="inlineStr"/>
-      <c r="G458" s="2" t="inlineStr"/>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區啟文路二段176巷21號對面</t>
+        </is>
+      </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21749,7 +21753,7 @@
       </c>
       <c r="I458" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J458" s="2" t="inlineStr">
@@ -21776,20 +21780,16 @@
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>澍之丘</t>
+          <t>湘榭別墅</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F459" s="2" t="inlineStr"/>
-      <c r="G459" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區月桃路615巷</t>
-        </is>
-      </c>
+      <c r="G459" s="2" t="inlineStr"/>
       <c r="H459" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21797,7 +21797,7 @@
       </c>
       <c r="I459" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J459" s="2" t="inlineStr">
@@ -21824,16 +21824,20 @@
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>璟城A22</t>
+          <t>澍之丘</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F460" s="2" t="inlineStr"/>
-      <c r="G460" s="2" t="inlineStr"/>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區月桃路615巷</t>
+        </is>
+      </c>
       <c r="H460" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21841,7 +21845,7 @@
       </c>
       <c r="I460" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J460" s="2" t="inlineStr">
@@ -21868,7 +21872,7 @@
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>皇普園首之道</t>
+          <t>璟城A22</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -21912,20 +21916,16 @@
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>皇普賦隱</t>
+          <t>皇普園首之道</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F462" s="2" t="inlineStr"/>
-      <c r="G462" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區青埔二街</t>
-        </is>
-      </c>
+      <c r="G462" s="2" t="inlineStr"/>
       <c r="H462" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21933,7 +21933,7 @@
       </c>
       <c r="I462" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J462" s="2" t="inlineStr">
@@ -21960,16 +21960,20 @@
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>益展有福</t>
+          <t>皇普賦隱</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F463" s="2" t="inlineStr"/>
-      <c r="G463" s="2" t="inlineStr"/>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區青埔二街</t>
+        </is>
+      </c>
       <c r="H463" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -21977,7 +21981,7 @@
       </c>
       <c r="I463" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J463" s="2" t="inlineStr">
@@ -22004,7 +22008,7 @@
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>立信悦榕</t>
+          <t>益展有福</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
@@ -22026,7 +22030,7 @@
       </c>
       <c r="J464" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -22048,7 +22052,7 @@
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>站前新鋭</t>
+          <t>立信悦榕</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
@@ -22070,7 +22074,7 @@
       </c>
       <c r="J465" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22096,7 @@
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>綠意領航1號</t>
+          <t>站前新鋭</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
@@ -22136,20 +22140,16 @@
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>聚泰雲藝</t>
+          <t>綠意領航1號</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F467" s="2" t="inlineStr"/>
-      <c r="G467" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區元生三街</t>
-        </is>
-      </c>
+      <c r="G467" s="2" t="inlineStr"/>
       <c r="H467" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22157,7 +22157,7 @@
       </c>
       <c r="I467" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J467" s="2" t="inlineStr">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>聯懋杉苑</t>
+          <t>聚泰雲藝</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
@@ -22195,7 +22195,7 @@
       <c r="F468" s="2" t="inlineStr"/>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>桃園市中壢區靠近興西二路及興北二路</t>
+          <t>桃園市中壢區元生三街</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -22232,16 +22232,20 @@
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>荷沐莊園</t>
+          <t>聯懋杉苑</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F469" s="2" t="inlineStr"/>
-      <c r="G469" s="2" t="inlineStr"/>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區靠近興西二路及興北二路</t>
+        </is>
+      </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22249,7 +22253,7 @@
       </c>
       <c r="I469" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J469" s="2" t="inlineStr">
@@ -22276,7 +22280,7 @@
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>菁美學</t>
+          <t>荷沐莊園</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
@@ -22320,7 +22324,7 @@
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-THE ONE</t>
+          <t>菁美學</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
@@ -22364,7 +22368,7 @@
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>藍海帝國-綠景苑</t>
+          <t>藍海帝國-THE ONE</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
@@ -22408,10 +22412,14 @@
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>誠鑫19</t>
-        </is>
-      </c>
-      <c r="E473" s="2" t="inlineStr"/>
+          <t>藍海帝國-綠景苑</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F473" s="2" t="inlineStr"/>
       <c r="G473" s="2" t="inlineStr"/>
       <c r="H473" s="2" t="inlineStr">
@@ -22448,14 +22456,10 @@
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>路易威登</t>
-        </is>
-      </c>
-      <c r="E474" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>誠鑫19</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr"/>
       <c r="F474" s="2" t="inlineStr"/>
       <c r="G474" s="2" t="inlineStr"/>
       <c r="H474" s="2" t="inlineStr">
@@ -22492,7 +22496,7 @@
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>鑫利川-三城</t>
+          <t>路易威登</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
@@ -22536,7 +22540,7 @@
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>閣美學</t>
+          <t>鑫利川-三城</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
@@ -22580,7 +22584,7 @@
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>青城之愛3</t>
+          <t>閣美學</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
@@ -22624,7 +22628,7 @@
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>鴻廣川湛</t>
+          <t>青城之愛3</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
@@ -22668,20 +22672,16 @@
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>鴻踞樸藝</t>
+          <t>鴻廣川湛</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr"/>
-      <c r="G479" s="2" t="inlineStr">
-        <is>
-          <t>桃園市中壢區興北一路及興東路 交叉口</t>
-        </is>
-      </c>
+      <c r="G479" s="2" t="inlineStr"/>
       <c r="H479" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22689,7 +22689,7 @@
       </c>
       <c r="I479" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J479" s="2" t="inlineStr">
@@ -22711,21 +22711,25 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>大園區</t>
+          <t>中壢區</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>三鶯澤苑</t>
+          <t>鴻踞樸藝</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F480" s="2" t="inlineStr"/>
-      <c r="G480" s="2" t="inlineStr"/>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興北一路及興東路 交叉口</t>
+        </is>
+      </c>
       <c r="H480" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22733,7 +22737,7 @@
       </c>
       <c r="I480" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J480" s="2" t="inlineStr">
@@ -22760,20 +22764,16 @@
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>上順麗</t>
+          <t>三鶯澤苑</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F481" s="2" t="inlineStr"/>
-      <c r="G481" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區客運一段340地號</t>
-        </is>
-      </c>
+      <c r="G481" s="2" t="inlineStr"/>
       <c r="H481" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22781,7 +22781,7 @@
       </c>
       <c r="I481" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J481" s="2" t="inlineStr">
@@ -22808,16 +22808,20 @@
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>中麗北極星</t>
+          <t>上順麗</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F482" s="2" t="inlineStr"/>
-      <c r="G482" s="2" t="inlineStr"/>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區客運一段340地號</t>
+        </is>
+      </c>
       <c r="H482" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22825,7 +22829,7 @@
       </c>
       <c r="I482" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J482" s="2" t="inlineStr">
@@ -22852,7 +22856,7 @@
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>京懋敦和</t>
+          <t>中麗北極星</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
@@ -22896,7 +22900,7 @@
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>佳暘青見</t>
+          <t>京懋敦和</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
@@ -22940,20 +22944,16 @@
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>偉築新豐州</t>
+          <t>佳暘青見</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F485" s="2" t="inlineStr"/>
-      <c r="G485" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區青峰路二段117~129號</t>
-        </is>
-      </c>
+      <c r="G485" s="2" t="inlineStr"/>
       <c r="H485" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -22961,7 +22961,7 @@
       </c>
       <c r="I485" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J485" s="2" t="inlineStr">
@@ -22988,16 +22988,20 @@
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>傳佳樂</t>
+          <t>偉築新豐州</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F486" s="2" t="inlineStr"/>
-      <c r="G486" s="2" t="inlineStr"/>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區青峰路二段117~129號</t>
+        </is>
+      </c>
       <c r="H486" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23005,7 +23009,7 @@
       </c>
       <c r="I486" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J486" s="2" t="inlineStr">
@@ -23032,7 +23036,7 @@
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>元基至善2</t>
+          <t>傳佳樂</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
@@ -23076,7 +23080,7 @@
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>力璞翔-豐禾</t>
+          <t>元基至善2</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
@@ -23098,7 +23102,7 @@
       </c>
       <c r="J488" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -23120,20 +23124,16 @@
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>合展悦恬</t>
+          <t>力璞翔-豐禾</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F489" s="2" t="inlineStr"/>
-      <c r="G489" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G489" s="2" t="inlineStr"/>
       <c r="H489" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23141,12 +23141,12 @@
       </c>
       <c r="I489" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J489" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -23168,18 +23168,18 @@
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>合陽逸境</t>
+          <t>合展悦恬</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F490" s="2" t="inlineStr"/>
       <c r="G490" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區青峰段273號地號</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H490" s="2" t="inlineStr">
@@ -23216,18 +23216,18 @@
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>名川琢域</t>
+          <t>合陽逸境</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F491" s="2" t="inlineStr"/>
       <c r="G491" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
+          <t>桃園市大園區青峰段273號地號</t>
         </is>
       </c>
       <c r="H491" s="2" t="inlineStr">
@@ -23264,18 +23264,18 @@
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅</t>
+          <t>名川琢域</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F492" s="2" t="inlineStr"/>
       <c r="G492" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區內海墘段 110-84</t>
+          <t>桃園市大園區致祥三街及致祥一街交叉口</t>
         </is>
       </c>
       <c r="H492" s="2" t="inlineStr">
@@ -23312,12 +23312,20 @@
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>垽赫海漾星墅Villa</t>
-        </is>
-      </c>
-      <c r="E493" s="2" t="inlineStr"/>
+          <t>垽赫海漾星墅</t>
+        </is>
+      </c>
+      <c r="E493" s="2" t="inlineStr">
+        <is>
+          <t>售價未定</t>
+        </is>
+      </c>
       <c r="F493" s="2" t="inlineStr"/>
-      <c r="G493" s="2" t="inlineStr"/>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區內海墘段 110-84</t>
+        </is>
+      </c>
       <c r="H493" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23325,7 +23333,7 @@
       </c>
       <c r="I493" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J493" s="2" t="inlineStr">
@@ -23352,20 +23360,12 @@
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>大地昕</t>
-        </is>
-      </c>
-      <c r="E494" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>垽赫海漾星墅Villa</t>
+        </is>
+      </c>
+      <c r="E494" s="2" t="inlineStr"/>
       <c r="F494" s="2" t="inlineStr"/>
-      <c r="G494" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園七街9號對面</t>
-        </is>
-      </c>
+      <c r="G494" s="2" t="inlineStr"/>
       <c r="H494" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23373,7 +23373,7 @@
       </c>
       <c r="I494" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J494" s="2" t="inlineStr">
@@ -23400,16 +23400,20 @@
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>大地玥</t>
+          <t>大地昕</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F495" s="2" t="inlineStr"/>
-      <c r="G495" s="2" t="inlineStr"/>
+      <c r="G495" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區園七街9號對面</t>
+        </is>
+      </c>
       <c r="H495" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23417,7 +23421,7 @@
       </c>
       <c r="I495" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J495" s="2" t="inlineStr">
@@ -23444,7 +23448,7 @@
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>大地．呈</t>
+          <t>大地玥</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
@@ -23488,7 +23492,7 @@
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>大禾苑</t>
+          <t>大地．呈</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
@@ -23532,7 +23536,7 @@
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>威均帝璽</t>
+          <t>大禾苑</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -23576,20 +23580,16 @@
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>宗佳領御</t>
+          <t>威均帝璽</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F499" s="2" t="inlineStr"/>
-      <c r="G499" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區中路與科七街</t>
-        </is>
-      </c>
+      <c r="G499" s="2" t="inlineStr"/>
       <c r="H499" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23597,7 +23597,7 @@
       </c>
       <c r="I499" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J499" s="2" t="inlineStr">
@@ -23624,16 +23624,20 @@
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>宜誠玉環</t>
+          <t>宗佳領御</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F500" s="2" t="inlineStr"/>
-      <c r="G500" s="2" t="inlineStr"/>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區中路與科七街</t>
+        </is>
+      </c>
       <c r="H500" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23641,7 +23645,7 @@
       </c>
       <c r="I500" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J500" s="2" t="inlineStr">
@@ -23668,7 +23672,7 @@
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>家綻</t>
+          <t>宜誠玉環</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
@@ -23712,20 +23716,16 @@
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>家綻2</t>
+          <t>家綻</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F502" s="2" t="inlineStr"/>
-      <c r="G502" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區柴梳崙路268巷</t>
-        </is>
-      </c>
+      <c r="G502" s="2" t="inlineStr"/>
       <c r="H502" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23733,7 +23733,7 @@
       </c>
       <c r="I502" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J502" s="2" t="inlineStr">
@@ -23760,16 +23760,20 @@
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>富總日日</t>
+          <t>家綻2</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F503" s="2" t="inlineStr"/>
-      <c r="G503" s="2" t="inlineStr"/>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區柴梳崙路268巷</t>
+        </is>
+      </c>
       <c r="H503" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23777,7 +23781,7 @@
       </c>
       <c r="I503" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J503" s="2" t="inlineStr">
@@ -23804,10 +23808,14 @@
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>山榆.柏悅</t>
-        </is>
-      </c>
-      <c r="E504" s="2" t="inlineStr"/>
+          <t>富總日日</t>
+        </is>
+      </c>
+      <c r="E504" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F504" s="2" t="inlineStr"/>
       <c r="G504" s="2" t="inlineStr"/>
       <c r="H504" s="2" t="inlineStr">
@@ -23822,7 +23830,7 @@
       </c>
       <c r="J504" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -23844,20 +23852,12 @@
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>山榆柏悅</t>
-        </is>
-      </c>
-      <c r="E505" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>山榆.柏悅</t>
+        </is>
+      </c>
+      <c r="E505" s="2" t="inlineStr"/>
       <c r="F505" s="2" t="inlineStr"/>
-      <c r="G505" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區永園路二段152號旁</t>
-        </is>
-      </c>
+      <c r="G505" s="2" t="inlineStr"/>
       <c r="H505" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23865,12 +23865,12 @@
       </c>
       <c r="I505" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J505" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -23892,16 +23892,20 @@
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>川洋青勻</t>
+          <t>山榆柏悅</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F506" s="2" t="inlineStr"/>
-      <c r="G506" s="2" t="inlineStr"/>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區永園路二段152號旁</t>
+        </is>
+      </c>
       <c r="H506" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -23909,7 +23913,7 @@
       </c>
       <c r="I506" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J506" s="2" t="inlineStr">
@@ -23936,7 +23940,7 @@
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>御禾院</t>
+          <t>川洋青勻</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
@@ -23980,20 +23984,16 @@
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>悦恬</t>
+          <t>御禾院</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F508" s="2" t="inlineStr"/>
-      <c r="G508" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區園學路、學六街口</t>
-        </is>
-      </c>
+      <c r="G508" s="2" t="inlineStr"/>
       <c r="H508" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24001,7 +24001,7 @@
       </c>
       <c r="I508" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J508" s="2" t="inlineStr">
@@ -24028,7 +24028,7 @@
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>日勝好日子</t>
+          <t>悦恬</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
@@ -24039,7 +24039,7 @@
       <c r="F509" s="2" t="inlineStr"/>
       <c r="G509" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區後館路1巷旁</t>
+          <t>桃園市大園區園學路、學六街口</t>
         </is>
       </c>
       <c r="H509" s="2" t="inlineStr">
@@ -24076,7 +24076,7 @@
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>日青悠</t>
+          <t>日勝好日子</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
@@ -24087,7 +24087,7 @@
       <c r="F510" s="2" t="inlineStr"/>
       <c r="G510" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區五青路63巷257號旁</t>
+          <t>桃園市大園區後館路1巷旁</t>
         </is>
       </c>
       <c r="H510" s="2" t="inlineStr">
@@ -24124,12 +24124,20 @@
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>松合苑5</t>
-        </is>
-      </c>
-      <c r="E511" s="2" t="inlineStr"/>
+          <t>日青悠</t>
+        </is>
+      </c>
+      <c r="E511" s="2" t="inlineStr">
+        <is>
+          <t>萬/坪</t>
+        </is>
+      </c>
       <c r="F511" s="2" t="inlineStr"/>
-      <c r="G511" s="2" t="inlineStr"/>
+      <c r="G511" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區五青路63巷257號旁</t>
+        </is>
+      </c>
       <c r="H511" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24137,7 +24145,7 @@
       </c>
       <c r="I511" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J511" s="2" t="inlineStr">
@@ -24164,20 +24172,12 @@
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>璟都新世界</t>
-        </is>
-      </c>
-      <c r="E512" s="2" t="inlineStr">
-        <is>
-          <t>萬/坪</t>
-        </is>
-      </c>
+          <t>松合苑5</t>
+        </is>
+      </c>
+      <c r="E512" s="2" t="inlineStr"/>
       <c r="F512" s="2" t="inlineStr"/>
-      <c r="G512" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區大觀路及環區北路口</t>
-        </is>
-      </c>
+      <c r="G512" s="2" t="inlineStr"/>
       <c r="H512" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="I512" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J512" s="2" t="inlineStr">
@@ -24212,16 +24212,20 @@
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>福興豐璟</t>
+          <t>璟都新世界</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F513" s="2" t="inlineStr"/>
-      <c r="G513" s="2" t="inlineStr"/>
+      <c r="G513" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區大觀路及環區北路口</t>
+        </is>
+      </c>
       <c r="H513" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24229,7 +24233,7 @@
       </c>
       <c r="I513" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J513" s="2" t="inlineStr">
@@ -24256,7 +24260,7 @@
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>立程·晴美</t>
+          <t>福興豐璟</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
@@ -24300,20 +24304,16 @@
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>立程‧晴美</t>
+          <t>立程·晴美</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F515" s="2" t="inlineStr"/>
-      <c r="G515" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區學七街69-1號</t>
-        </is>
-      </c>
+      <c r="G515" s="2" t="inlineStr"/>
       <c r="H515" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24321,7 +24321,7 @@
       </c>
       <c r="I515" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J515" s="2" t="inlineStr">
@@ -24348,23 +24348,23 @@
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>立程建設客運二段案</t>
+          <t>立程‧晴美</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F516" s="2" t="inlineStr"/>
       <c r="G516" s="2" t="inlineStr">
         <is>
-          <t>桃園市大園區學七街69-1號旁</t>
+          <t>桃園市大園區學七街69-1號</t>
         </is>
       </c>
       <c r="H516" s="2" t="inlineStr">
         <is>
-          <t>未標示</t>
+          <t>預售屋</t>
         </is>
       </c>
       <c r="I516" s="2" t="inlineStr">
@@ -24396,29 +24396,33 @@
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>立鴻晶硯</t>
+          <t>立程建設客運二段案</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F517" s="2" t="inlineStr"/>
-      <c r="G517" s="2" t="inlineStr"/>
+      <c r="G517" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區學七街69-1號旁</t>
+        </is>
+      </c>
       <c r="H517" s="2" t="inlineStr">
         <is>
-          <t>預售屋</t>
+          <t>未標示</t>
         </is>
       </c>
       <c r="I517" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J517" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -24440,7 +24444,7 @@
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>臥墨池</t>
+          <t>立鴻晶硯</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
@@ -24462,7 +24466,7 @@
       </c>
       <c r="J518" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -24484,7 +24488,7 @@
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>臻璞</t>
+          <t>臥墨池</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
@@ -24528,7 +24532,7 @@
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>興禾  築美學</t>
+          <t>臻璞</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
@@ -24572,20 +24576,16 @@
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>航綻甜心</t>
+          <t>興禾  築美學</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
         <is>
-          <t>萬/坪</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F521" s="2" t="inlineStr"/>
-      <c r="G521" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路與科五路交叉口</t>
-        </is>
-      </c>
+      <c r="G521" s="2" t="inlineStr"/>
       <c r="H521" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24593,7 +24593,7 @@
       </c>
       <c r="I521" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J521" s="2" t="inlineStr">
@@ -24620,16 +24620,20 @@
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>英堡日朗</t>
+          <t>航綻甜心</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>萬/坪</t>
         </is>
       </c>
       <c r="F522" s="2" t="inlineStr"/>
-      <c r="G522" s="2" t="inlineStr"/>
+      <c r="G522" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路與科五路交叉口</t>
+        </is>
+      </c>
       <c r="H522" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24637,7 +24641,7 @@
       </c>
       <c r="I522" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J522" s="2" t="inlineStr">
@@ -24664,20 +24668,16 @@
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>薪成家II</t>
+          <t>英堡日朗</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
         <is>
-          <t>售價未定</t>
+          <t>萬元/坪</t>
         </is>
       </c>
       <c r="F523" s="2" t="inlineStr"/>
-      <c r="G523" s="2" t="inlineStr">
-        <is>
-          <t>桃園市大園區環區西路597號</t>
-        </is>
-      </c>
+      <c r="G523" s="2" t="inlineStr"/>
       <c r="H523" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24685,7 +24685,7 @@
       </c>
       <c r="I523" s="2" t="inlineStr">
         <is>
-          <t>好房網</t>
+          <t>樂屋網</t>
         </is>
       </c>
       <c r="J523" s="2" t="inlineStr">
@@ -24712,16 +24712,20 @@
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>逸偉A+</t>
+          <t>薪成家II</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
         <is>
-          <t>萬元/坪</t>
+          <t>售價未定</t>
         </is>
       </c>
       <c r="F524" s="2" t="inlineStr"/>
-      <c r="G524" s="2" t="inlineStr"/>
+      <c r="G524" s="2" t="inlineStr">
+        <is>
+          <t>桃園市大園區環區西路597號</t>
+        </is>
+      </c>
       <c r="H524" s="2" t="inlineStr">
         <is>
           <t>預售屋</t>
@@ -24729,7 +24733,7 @@
       </c>
       <c r="I524" s="2" t="inlineStr">
         <is>
-          <t>樂屋網</t>
+          <t>好房網</t>
         </is>
       </c>
       <c r="J524" s="2" t="inlineStr">
@@ -24756,10 +24760,14 @@
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>遠雄仰森</t>
-        </is>
-      </c>
-      <c r="E525" s="2" t="inlineStr"/>
+          <t>逸偉A+</t>
+        </is>
+      </c>
+      <c r="E525" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F525" s="2" t="inlineStr"/>
       <c r="G525" s="2" t="inlineStr"/>
       <c r="H525" s="2" t="inlineStr">
@@ -24796,14 +24804,10 @@
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>鈞貴極美II</t>
-        </is>
-      </c>
-      <c r="E526" s="2" t="inlineStr">
-        <is>
-          <t>萬元/坪</t>
-        </is>
-      </c>
+          <t>遠雄仰森</t>
+        </is>
+      </c>
+      <c r="E526" s="2" t="inlineStr"/>
       <c r="F526" s="2" t="inlineStr"/>
       <c r="G526" s="2" t="inlineStr"/>
       <c r="H526" s="2" t="inlineStr">
@@ -24840,7 +24844,7 @@
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>高誠君品</t>
+          <t>鈞貴極美II</t>
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr">
@@ -24884,10 +24888,14 @@
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>龍築靜玥</t>
-        </is>
-      </c>
-      <c r="E528" s="2" t="inlineStr"/>
+          <t>高誠君品</t>
+        </is>
+      </c>
+      <c r="E528" s="2" t="inlineStr">
+        <is>
+          <t>萬元/坪</t>
+        </is>
+      </c>
       <c r="F528" s="2" t="inlineStr"/>
       <c r="G528" s="2" t="inlineStr"/>
       <c r="H528" s="2" t="inlineStr">
@@ -24906,15 +24914,55 @@
         </is>
       </c>
     </row>
-    <row r="530">
-      <c r="A530" s="3" t="inlineStr">
-        <is>
-          <t>最後更新：2026-10-25 12:56（台灣時間）　共 527 筆　資料來源：好房網、樂屋網</t>
+    <row r="529">
+      <c r="A529" s="2" t="inlineStr">
+        <is>
+          <t>桃園市（青埔）</t>
+        </is>
+      </c>
+      <c r="B529" s="2" t="inlineStr">
+        <is>
+          <t>青埔周邊（中壢/大園）</t>
+        </is>
+      </c>
+      <c r="C529" s="2" t="inlineStr">
+        <is>
+          <t>大園區</t>
+        </is>
+      </c>
+      <c r="D529" s="2" t="inlineStr">
+        <is>
+          <t>龍築靜玥</t>
+        </is>
+      </c>
+      <c r="E529" s="2" t="inlineStr"/>
+      <c r="F529" s="2" t="inlineStr"/>
+      <c r="G529" s="2" t="inlineStr"/>
+      <c r="H529" s="2" t="inlineStr">
+        <is>
+          <t>預售屋</t>
+        </is>
+      </c>
+      <c r="I529" s="2" t="inlineStr">
+        <is>
+          <t>樂屋網</t>
+        </is>
+      </c>
+      <c r="J529" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="3" t="inlineStr">
+        <is>
+          <t>最後更新：2026-10-26 13:00（台灣時間）　共 528 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J528"/>
+  <autoFilter ref="A1:J529"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24957,7 +24957,7 @@
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-26 13:00（台灣時間）　共 528 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-27 13:18（台灣時間）　共 528 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24957,7 +24957,7 @@
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-27 13:18（台灣時間）　共 528 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-28 13:57（台灣時間）　共 528 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24957,7 +24957,7 @@
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-28 13:57（台灣時間）　共 528 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-29 14:01（台灣時間）　共 528 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24957,7 +24957,7 @@
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-29 14:01（台灣時間）　共 528 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-30 14:02（台灣時間）　共 528 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>

--- a/listings.xlsx
+++ b/listings.xlsx
@@ -24957,7 +24957,7 @@
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
         <is>
-          <t>最後更新：2026-10-30 14:02（台灣時間）　共 528 筆　資料來源：好房網、樂屋網</t>
+          <t>最後更新：2026-10-31 13:58（台灣時間）　共 528 筆　資料來源：好房網、樂屋網</t>
         </is>
       </c>
     </row>
